--- a/docs/EAA_Bang_nang_luc.xlsx
+++ b/docs/EAA_Bang_nang_luc.xlsx
@@ -16,8 +16,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Năng lực nền'!$A$1:$G$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Năng lực nhúng'!$A$1:$G$87</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Khoảng trống'!$A$1:$F$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Bản đồ lệnh'!$A$1:$E$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Khoảng trống'!$A$1:$F$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Bản đồ lệnh'!$A$1:$E$74</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -50,7 +50,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -92,11 +92,6 @@
         <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9999"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -124,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -154,25 +149,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -912,22 +904,18 @@
       </c>
       <c r="D3" s="11" t="inlineStr">
         <is>
-          <t>MỘT PHẦN</t>
+          <t>ĐỦ</t>
         </is>
       </c>
       <c r="E3" s="10" t="inlineStr">
         <is>
-          <t>eaa/agent.py AgentLoop chọn công cụ theo từng lượt; eaa/decompose.py + `eaa plan propose` phân rã bài toán thành module</t>
-        </is>
-      </c>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t>Phân rã vẫn trong danh mục công cụ, NHƯNG từ SL-77 Agent tự VIẾT được công cụ mới khi việc cần làm không có lệnh nào sẵn (`tool propose`). Còn thiếu: nó chưa tự NHẬN RA lúc nào nên viết</t>
-        </is>
-      </c>
+          <t>eaa/agent.py chọn công cụ theo lượt; eaa/decompose.py phân rã module; từ SL-77 tự VIẾT được công cụ mới, từ SL-81 tự RÚT được kỹ năng từ chuỗi đã lặp</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr"/>
       <c r="G3" s="12" t="inlineStr">
         <is>
-          <t>Vừa</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -947,7 +935,7 @@
           <t>Lập kế hoạch &amp; theo dõi tiến độ; dừng hỏi khi thiếu thông tin quyết định</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>ĐỦ</t>
         </is>
@@ -958,7 +946,7 @@
         </is>
       </c>
       <c r="F4" s="10" t="inlineStr"/>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -980,7 +968,7 @@
           <t>Suy luận có kiểm chứng — phân biệt 'tôi tin là' với 'tôi đã xác minh'</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>ĐỦ</t>
         </is>
@@ -995,7 +983,7 @@
           <t>Mạnh hơn khung yêu cầu: 4 mức thay vì 2, và có test chặn đầu ra nào quên gắn nhãn</t>
         </is>
       </c>
-      <c r="G5" s="14" t="inlineStr">
+      <c r="G5" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1017,7 +1005,7 @@
           <t>Quản lý ngữ cảnh — tóm tắt log dài, bỏ output thừa, không tràn context</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>ĐỦ</t>
         </is>
@@ -1028,7 +1016,7 @@
         </is>
       </c>
       <c r="F6" s="10" t="inlineStr"/>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1050,7 +1038,7 @@
           <t>An toàn &amp; xin phép — phân loại hành động, hỏi trước việc không hoàn tác được</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>ĐỦ</t>
         </is>
@@ -1065,7 +1053,7 @@
           <t>Mạnh hơn khung: ranh giới nằm ở DANH MỤC công cụ, không ở lời dặn trong prompt — Agent không có đường gọi chứ không phải được dặn đừng gọi</t>
         </is>
       </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="G7" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1094,7 +1082,7 @@
           <t>Liệt kê tool đã đăng ký (tên, mô tả, phiên bản, trạng thái)</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>ĐỦ</t>
         </is>
@@ -1105,7 +1093,7 @@
         </is>
       </c>
       <c r="F9" s="10" t="inlineStr"/>
-      <c r="G9" s="14" t="inlineStr">
+      <c r="G9" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1127,7 +1115,7 @@
           <t>Dò môi trường: hệ điều hành</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>ĐỦ</t>
         </is>
@@ -1138,7 +1126,7 @@
         </is>
       </c>
       <c r="F10" s="10" t="inlineStr"/>
-      <c r="G10" s="14" t="inlineStr">
+      <c r="G10" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1160,7 +1148,7 @@
           <t>Dò môi trường: kiến trúc CPU, quyền root, mạng ra ngoài, domain bị chặn</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>ĐỦ</t>
         </is>
@@ -1171,7 +1159,7 @@
         </is>
       </c>
       <c r="F11" s="10" t="inlineStr"/>
-      <c r="G11" s="14" t="inlineStr">
+      <c r="G11" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1193,7 +1181,7 @@
           <t>Dò runtime: python --version, pip list, npm ls, which, docker ps</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>MỘT PHẦN</t>
         </is>
@@ -1208,7 +1196,7 @@
           <t>Vẫn chưa liệt kê được gói đã cài (pip list / npm ls)</t>
         </is>
       </c>
-      <c r="G12" s="14" t="inlineStr">
+      <c r="G12" s="12" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
@@ -1230,7 +1218,7 @@
           <t>Dò tài nguyên: dung lượng đĩa, RAM, GPU</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>ĐỦ</t>
         </is>
@@ -1241,7 +1229,7 @@
         </is>
       </c>
       <c r="F13" s="10" t="inlineStr"/>
-      <c r="G13" s="14" t="inlineStr">
+      <c r="G13" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1263,7 +1251,7 @@
           <t>Kiểm tool THỰC SỰ chạy được (smoke test), không chỉ tin registry</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>ĐỦ</t>
         </is>
@@ -1278,7 +1266,7 @@
           <t>Đúng đúng ý khung: registry nói 'có' không được tính là bằng chứng</t>
         </is>
       </c>
-      <c r="G14" s="14" t="inlineStr">
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1300,7 +1288,7 @@
           <t>So khớp năng lực ↔ nhu cầu, phát hiện khoảng trống năng lực</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>ĐỦ</t>
         </is>
@@ -1315,7 +1303,7 @@
           <t>Nhu cầu suy ra từ pack chứ không chép tay — nên không lệch khi pack đổi lệnh</t>
         </is>
       </c>
-      <c r="G15" s="14" t="inlineStr">
+      <c r="G15" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1337,7 +1325,7 @@
           <t>Kiểm phiên bản / tương thích</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>ĐỦ</t>
         </is>
@@ -1348,7 +1336,7 @@
         </is>
       </c>
       <c r="F16" s="10" t="inlineStr"/>
-      <c r="G16" s="14" t="inlineStr">
+      <c r="G16" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1370,7 +1358,7 @@
           <t>Phát hiện xung đột phụ thuộc</t>
         </is>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="D17" s="14" t="inlineStr">
         <is>
           <t>CHƯA</t>
         </is>
@@ -1385,7 +1373,7 @@
           <t>Chưa gặp vấn đề thật vì công cụ nhúng là binary độc lập, ít phụ thuộc chéo</t>
         </is>
       </c>
-      <c r="G17" s="14" t="inlineStr">
+      <c r="G17" s="12" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
@@ -1414,7 +1402,7 @@
           <t>Chuyển khoảng trống năng lực thành truy vấn tìm kiếm</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>ĐỦ</t>
         </is>
@@ -1429,7 +1417,7 @@
           <t>ĐO ĐƯỢC: model chỉ thật sự đi tìm khi được RA LỆNH tìm — câu lệnh ấy nằm trong adapter</t>
         </is>
       </c>
-      <c r="G19" s="14" t="inlineStr">
+      <c r="G19" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1451,7 +1439,7 @@
           <t>Đọc tài liệu chính thống (docs, README, PyPI) bằng web_fetch</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr">
+      <c r="D20" s="11" t="inlineStr">
         <is>
           <t>ĐỦ</t>
         </is>
@@ -1462,7 +1450,7 @@
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr"/>
-      <c r="G20" s="14" t="inlineStr">
+      <c r="G20" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1484,7 +1472,7 @@
           <t>Đánh giá &amp; chọn công cụ: còn bảo trì, license, độ phổ biến, phụ thuộc hệ thống</t>
         </is>
       </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>MỘT PHẦN</t>
         </is>
@@ -1499,7 +1487,7 @@
           <t>Chưa tự đọc chỉ số bảo trì / license / độ phổ biến từ kho gói</t>
         </is>
       </c>
-      <c r="G21" s="12" t="inlineStr">
+      <c r="G21" s="15" t="inlineStr">
         <is>
           <t>Vừa</t>
         </is>
@@ -1521,7 +1509,7 @@
           <t>Kiểm bảo mật nguồn cài</t>
         </is>
       </c>
-      <c r="D22" s="13" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>ĐỦ</t>
         </is>
@@ -1536,7 +1524,7 @@
           <t>Chưa chống typosquatting theo TÊN GÓI (avr-gcc vs avrgcc). Bù lại: mọi đề xuất đều phải qua người duyệt tại gate</t>
         </is>
       </c>
-      <c r="G22" s="12" t="inlineStr">
+      <c r="G22" s="15" t="inlineStr">
         <is>
           <t>Vừa</t>
         </is>
@@ -1558,7 +1546,7 @@
           <t>Xác định lệnh cài chính xác theo OS, kèm cờ đặc thù</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
+      <c r="D23" s="11" t="inlineStr">
         <is>
           <t>ĐỦ</t>
         </is>
@@ -1569,7 +1557,7 @@
         </is>
       </c>
       <c r="F23" s="10" t="inlineStr"/>
-      <c r="G23" s="14" t="inlineStr">
+      <c r="G23" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1591,7 +1579,7 @@
           <t>Nhận biết giới hạn mạng, tìm phương án thay thế</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr">
+      <c r="D24" s="11" t="inlineStr">
         <is>
           <t>ĐỦ</t>
         </is>
@@ -1602,7 +1590,7 @@
         </is>
       </c>
       <c r="F24" s="10" t="inlineStr"/>
-      <c r="G24" s="14" t="inlineStr">
+      <c r="G24" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1631,7 +1619,7 @@
           <t>Chọn cơ chế cài phù hợp</t>
         </is>
       </c>
-      <c r="D26" s="11" t="inlineStr">
+      <c r="D26" s="13" t="inlineStr">
         <is>
           <t>MỘT PHẦN</t>
         </is>
@@ -1646,7 +1634,7 @@
           <t>Không build từ nguồn, không chạy container. Đủ cho toolchain nhúng phổ biến, thiếu cho công cụ lạ</t>
         </is>
       </c>
-      <c r="G26" s="14" t="inlineStr">
+      <c r="G26" s="12" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
@@ -1668,7 +1656,7 @@
           <t>Cô lập môi trường (venv riêng cho tool mới)</t>
         </is>
       </c>
-      <c r="D27" s="11" t="inlineStr">
+      <c r="D27" s="13" t="inlineStr">
         <is>
           <t>MỘT PHẦN</t>
         </is>
@@ -1683,7 +1671,7 @@
           <t>Chưa có venv riêng cho công cụ NGOÀI (avr-gcc, cppcheck…)</t>
         </is>
       </c>
-      <c r="G27" s="14" t="inlineStr">
+      <c r="G27" s="12" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
@@ -1705,7 +1693,7 @@
           <t>Cài theo thứ tự phụ thuộc (system lib trước, runtime package sau)</t>
         </is>
       </c>
-      <c r="D28" s="15" t="inlineStr">
+      <c r="D28" s="14" t="inlineStr">
         <is>
           <t>CHƯA</t>
         </is>
@@ -1720,7 +1708,7 @@
           <t>Hiện mỗi Tool Card độc lập, không khai phụ thuộc lẫn nhau</t>
         </is>
       </c>
-      <c r="G28" s="14" t="inlineStr">
+      <c r="G28" s="12" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
@@ -1742,7 +1730,7 @@
           <t>Xác minh sau cài: chạy --version, chạy test nhỏ với input thật</t>
         </is>
       </c>
-      <c r="D29" s="13" t="inlineStr">
+      <c r="D29" s="11" t="inlineStr">
         <is>
           <t>ĐỦ</t>
         </is>
@@ -1753,7 +1741,7 @@
         </is>
       </c>
       <c r="F29" s="10" t="inlineStr"/>
-      <c r="G29" s="14" t="inlineStr">
+      <c r="G29" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1775,7 +1763,7 @@
           <t>Ghi lại quá trình để tái tạo và rollback</t>
         </is>
       </c>
-      <c r="D30" s="13" t="inlineStr">
+      <c r="D30" s="11" t="inlineStr">
         <is>
           <t>ĐỦ</t>
         </is>
@@ -1786,7 +1774,7 @@
         </is>
       </c>
       <c r="F30" s="10" t="inlineStr"/>
-      <c r="G30" s="14" t="inlineStr">
+      <c r="G30" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1823,7 +1811,7 @@
           <t>Cố ý: cài phần mềm là thay đổi máy của người dùng (N-022 ở mức tự chủ T2). Đây KHÔNG phải khoảng trống cần lấp</t>
         </is>
       </c>
-      <c r="G31" s="14" t="inlineStr">
+      <c r="G31" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1852,7 +1840,7 @@
           <t>Đọc và phân loại lỗi (mạng / quyền / phụ thuộc / build / runtime)</t>
         </is>
       </c>
-      <c r="D33" s="13" t="inlineStr">
+      <c r="D33" s="11" t="inlineStr">
         <is>
           <t>ĐỦ</t>
         </is>
@@ -1863,7 +1851,7 @@
         </is>
       </c>
       <c r="F33" s="10" t="inlineStr"/>
-      <c r="G33" s="14" t="inlineStr">
+      <c r="G33" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1885,7 +1873,7 @@
           <t>Thử lại có kiểm soát (retry + backoff) cho lỗi mạng</t>
         </is>
       </c>
-      <c r="D34" s="13" t="inlineStr">
+      <c r="D34" s="11" t="inlineStr">
         <is>
           <t>ĐỦ</t>
         </is>
@@ -1896,7 +1884,7 @@
         </is>
       </c>
       <c r="F34" s="10" t="inlineStr"/>
-      <c r="G34" s="14" t="inlineStr">
+      <c r="G34" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1918,7 +1906,7 @@
           <t>Đổi tham số: ghim phiên bản cũ hơn, cờ khác, mirror khác</t>
         </is>
       </c>
-      <c r="D35" s="13" t="inlineStr">
+      <c r="D35" s="11" t="inlineStr">
         <is>
           <t>ĐỦ</t>
         </is>
@@ -1929,7 +1917,7 @@
         </is>
       </c>
       <c r="F35" s="10" t="inlineStr"/>
-      <c r="G35" s="14" t="inlineStr">
+      <c r="G35" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1951,7 +1939,7 @@
           <t>Tìm thông báo lỗi trên web (GitHub issues, StackOverflow)</t>
         </is>
       </c>
-      <c r="D36" s="13" t="inlineStr">
+      <c r="D36" s="11" t="inlineStr">
         <is>
           <t>ĐỦ</t>
         </is>
@@ -1962,7 +1950,7 @@
         </is>
       </c>
       <c r="F36" s="10" t="inlineStr"/>
-      <c r="G36" s="14" t="inlineStr">
+      <c r="G36" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1984,7 +1972,7 @@
           <t>Đổi sang công cụ thay thế tương đương</t>
         </is>
       </c>
-      <c r="D37" s="13" t="inlineStr">
+      <c r="D37" s="11" t="inlineStr">
         <is>
           <t>ĐỦ</t>
         </is>
@@ -1995,7 +1983,7 @@
         </is>
       </c>
       <c r="F37" s="10" t="inlineStr"/>
-      <c r="G37" s="14" t="inlineStr">
+      <c r="G37" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2017,7 +2005,7 @@
           <t>Tự viết giải pháp tối thiểu thay thế</t>
         </is>
       </c>
-      <c r="D38" s="11" t="inlineStr">
+      <c r="D38" s="13" t="inlineStr">
         <is>
           <t>MỘT PHẦN</t>
         </is>
@@ -2032,7 +2020,7 @@
           <t>Chưa nối tự động vào thang gỡ lỗi cài đặt</t>
         </is>
       </c>
-      <c r="G38" s="14" t="inlineStr">
+      <c r="G38" s="12" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
@@ -2054,7 +2042,7 @@
           <t>Báo cáo người dùng: lỗi cụ thể + đã thử gì + gợi ý</t>
         </is>
       </c>
-      <c r="D39" s="13" t="inlineStr">
+      <c r="D39" s="11" t="inlineStr">
         <is>
           <t>ĐỦ</t>
         </is>
@@ -2069,7 +2057,7 @@
           <t>Đủ cho vòng sinh mã. Với lỗi cài đặt thì mỏng hơn vì C5.1–C5.5 còn trống</t>
         </is>
       </c>
-      <c r="G39" s="14" t="inlineStr">
+      <c r="G39" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2091,7 +2079,7 @@
           <t>Giới hạn vòng lặp, đặt ngân sách số lần thử</t>
         </is>
       </c>
-      <c r="D40" s="13" t="inlineStr">
+      <c r="D40" s="11" t="inlineStr">
         <is>
           <t>ĐỦ</t>
         </is>
@@ -2106,7 +2094,7 @@
           <t>Mạnh hơn khung: giới hạn là bất biến có test chặn, không phải một hằng số ai cũng sửa được</t>
         </is>
       </c>
-      <c r="G40" s="14" t="inlineStr">
+      <c r="G40" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2128,7 +2116,7 @@
           <t>Rollback về trạng thái trước</t>
         </is>
       </c>
-      <c r="D41" s="13" t="inlineStr">
+      <c r="D41" s="11" t="inlineStr">
         <is>
           <t>ĐỦ</t>
         </is>
@@ -2139,7 +2127,7 @@
         </is>
       </c>
       <c r="F41" s="10" t="inlineStr"/>
-      <c r="G41" s="14" t="inlineStr">
+      <c r="G41" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2161,7 +2149,7 @@
           <t>Phân biệt lỗi của tool với lỗi do input</t>
         </is>
       </c>
-      <c r="D42" s="13" t="inlineStr">
+      <c r="D42" s="11" t="inlineStr">
         <is>
           <t>ĐỦ</t>
         </is>
@@ -2172,7 +2160,7 @@
         </is>
       </c>
       <c r="F42" s="10" t="inlineStr"/>
-      <c r="G42" s="14" t="inlineStr">
+      <c r="G42" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2201,7 +2189,7 @@
           <t>Nhận diện khi nào nên tự viết thay vì đi tìm</t>
         </is>
       </c>
-      <c r="D44" s="11" t="inlineStr">
+      <c r="D44" s="13" t="inlineStr">
         <is>
           <t>MỘT PHẦN</t>
         </is>
@@ -2216,7 +2204,7 @@
           <t>Agent chưa tự NHẬN RA lúc nào nên viết — vẫn cần người gợi ý</t>
         </is>
       </c>
-      <c r="G44" s="12" t="inlineStr">
+      <c r="G44" s="15" t="inlineStr">
         <is>
           <t>Vừa</t>
         </is>
@@ -2238,7 +2226,7 @@
           <t>Sinh tool đúng chuẩn: chữ ký rõ, type hints, docstring</t>
         </is>
       </c>
-      <c r="D45" s="13" t="inlineStr">
+      <c r="D45" s="11" t="inlineStr">
         <is>
           <t>ĐỦ</t>
         </is>
@@ -2249,7 +2237,7 @@
         </is>
       </c>
       <c r="F45" s="10" t="inlineStr"/>
-      <c r="G45" s="14" t="inlineStr">
+      <c r="G45" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2271,7 +2259,7 @@
           <t>Sinh JSON schema tham số để đăng ký vào registry</t>
         </is>
       </c>
-      <c r="D46" s="13" t="inlineStr">
+      <c r="D46" s="11" t="inlineStr">
         <is>
           <t>ĐỦ</t>
         </is>
@@ -2282,7 +2270,7 @@
         </is>
       </c>
       <c r="F46" s="10" t="inlineStr"/>
-      <c r="G46" s="14" t="inlineStr">
+      <c r="G46" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2304,7 +2292,7 @@
           <t>Input validation, ngoại lệ có nghĩa, timeout, không side-effect ẩn</t>
         </is>
       </c>
-      <c r="D47" s="13" t="inlineStr">
+      <c r="D47" s="11" t="inlineStr">
         <is>
           <t>ĐỦ</t>
         </is>
@@ -2315,7 +2303,7 @@
         </is>
       </c>
       <c r="F47" s="10" t="inlineStr"/>
-      <c r="G47" s="14" t="inlineStr">
+      <c r="G47" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2337,7 +2325,7 @@
           <t>Viết test tối thiểu, chạy trước khi đăng ký</t>
         </is>
       </c>
-      <c r="D48" s="13" t="inlineStr">
+      <c r="D48" s="11" t="inlineStr">
         <is>
           <t>ĐỦ</t>
         </is>
@@ -2348,7 +2336,7 @@
         </is>
       </c>
       <c r="F48" s="10" t="inlineStr"/>
-      <c r="G48" s="14" t="inlineStr">
+      <c r="G48" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2370,7 +2358,7 @@
           <t>Chạy trong sandbox, giới hạn quyền file/mạng</t>
         </is>
       </c>
-      <c r="D49" s="13" t="inlineStr">
+      <c r="D49" s="11" t="inlineStr">
         <is>
           <t>ĐỦ</t>
         </is>
@@ -2381,7 +2369,7 @@
         </is>
       </c>
       <c r="F49" s="10" t="inlineStr"/>
-      <c r="G49" s="14" t="inlineStr">
+      <c r="G49" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2403,7 +2391,7 @@
           <t>Kiểm bảo mật mã tự sinh: không hard-code secret, không eval input</t>
         </is>
       </c>
-      <c r="D50" s="13" t="inlineStr">
+      <c r="D50" s="11" t="inlineStr">
         <is>
           <t>ĐỦ</t>
         </is>
@@ -2414,7 +2402,7 @@
         </is>
       </c>
       <c r="F50" s="10" t="inlineStr"/>
-      <c r="G50" s="14" t="inlineStr">
+      <c r="G50" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2436,7 +2424,7 @@
           <t>Tài liệu hoá tool mới: README ngắn, ví dụ, giới hạn đã biết</t>
         </is>
       </c>
-      <c r="D51" s="11" t="inlineStr">
+      <c r="D51" s="13" t="inlineStr">
         <is>
           <t>MỘT PHẦN</t>
         </is>
@@ -2451,7 +2439,7 @@
           <t>Chưa sinh README riêng cho từng công cụ</t>
         </is>
       </c>
-      <c r="G51" s="14" t="inlineStr">
+      <c r="G51" s="12" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
@@ -2480,7 +2468,7 @@
           <t>Nạp động tool vào registry (hot-reload, không khởi động lại)</t>
         </is>
       </c>
-      <c r="D53" s="13" t="inlineStr">
+      <c r="D53" s="11" t="inlineStr">
         <is>
           <t>ĐỦ</t>
         </is>
@@ -2491,7 +2479,7 @@
         </is>
       </c>
       <c r="F53" s="10" t="inlineStr"/>
-      <c r="G53" s="14" t="inlineStr">
+      <c r="G53" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2513,7 +2501,7 @@
           <t>Cập nhật bản đồ năng lực để lần sau không tìm lại</t>
         </is>
       </c>
-      <c r="D54" s="13" t="inlineStr">
+      <c r="D54" s="11" t="inlineStr">
         <is>
           <t>ĐỦ</t>
         </is>
@@ -2524,7 +2512,7 @@
         </is>
       </c>
       <c r="F54" s="10" t="inlineStr"/>
-      <c r="G54" s="14" t="inlineStr">
+      <c r="G54" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2546,7 +2534,7 @@
           <t>Versioning tool, giữ bản cũ nếu bản mới hỏng</t>
         </is>
       </c>
-      <c r="D55" s="11" t="inlineStr">
+      <c r="D55" s="13" t="inlineStr">
         <is>
           <t>MỘT PHẦN</t>
         </is>
@@ -2561,7 +2549,7 @@
           <t>Không giữ song song hai bản để quay lui</t>
         </is>
       </c>
-      <c r="G55" s="14" t="inlineStr">
+      <c r="G55" s="12" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
@@ -2583,7 +2571,7 @@
           <t>Đánh giá chất lượng sau khi dùng thật (hay hỏng? chậm?)</t>
         </is>
       </c>
-      <c r="D56" s="11" t="inlineStr">
+      <c r="D56" s="13" t="inlineStr">
         <is>
           <t>MỘT PHẦN</t>
         </is>
@@ -2598,7 +2586,7 @@
           <t>Chưa đo độ tin cậy từng công cụ tự sinh sau khi dùng thật</t>
         </is>
       </c>
-      <c r="G56" s="12" t="inlineStr">
+      <c r="G56" s="15" t="inlineStr">
         <is>
           <t>Vừa</t>
         </is>
@@ -2620,24 +2608,20 @@
           <t>Gộp chuỗi tool hay dùng thành tool cấp cao hơn (skill/workflow)</t>
         </is>
       </c>
-      <c r="D57" s="15" t="inlineStr">
-        <is>
-          <t>CHƯA</t>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
         </is>
       </c>
       <c r="E57" s="10" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F57" s="10" t="inlineStr">
-        <is>
-          <t>Hiện chuỗi ấy được đóng cứng trong quy trình G0→G10 thay vì được rút ra thành skill — xem C10.1</t>
-        </is>
-      </c>
-      <c r="G57" s="17" t="inlineStr">
-        <is>
-          <t>Cao</t>
+          <t>eaa/skills.py: rút chuỗi việc đã lặp từ chat_log thành kỹ năng đặt tên được; ba cổng (quyền, tham số, chạy khô) rồi người duyệt · lệnh eaa skill list/add/mine/verify/approve/run · TC-71</t>
+        </is>
+      </c>
+      <c r="F57" s="10" t="inlineStr"/>
+      <c r="G57" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2648,7 @@
           <t>Bộ nhớ dài hạn TRONG một dự án</t>
         </is>
       </c>
-      <c r="D59" s="13" t="inlineStr">
+      <c r="D59" s="11" t="inlineStr">
         <is>
           <t>ĐỦ</t>
         </is>
@@ -2675,7 +2659,7 @@
         </is>
       </c>
       <c r="F59" s="10" t="inlineStr"/>
-      <c r="G59" s="14" t="inlineStr">
+      <c r="G59" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2697,7 +2681,7 @@
           <t>Bộ nhớ LIÊN dự án</t>
         </is>
       </c>
-      <c r="D60" s="13" t="inlineStr">
+      <c r="D60" s="11" t="inlineStr">
         <is>
           <t>ĐỦ</t>
         </is>
@@ -2708,7 +2692,7 @@
         </is>
       </c>
       <c r="F60" s="10" t="inlineStr"/>
-      <c r="G60" s="14" t="inlineStr">
+      <c r="G60" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2730,7 +2714,7 @@
           <t>Sổ tay lỗi (playbook): lỗi X → cách sửa Y, tra trước khi tìm web</t>
         </is>
       </c>
-      <c r="D61" s="13" t="inlineStr">
+      <c r="D61" s="11" t="inlineStr">
         <is>
           <t>ĐỦ</t>
         </is>
@@ -2741,7 +2725,7 @@
         </is>
       </c>
       <c r="F61" s="10" t="inlineStr"/>
-      <c r="G61" s="14" t="inlineStr">
+      <c r="G61" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2763,7 +2747,7 @@
           <t>Cache kết quả tìm kiếm / đánh giá tool</t>
         </is>
       </c>
-      <c r="D62" s="13" t="inlineStr">
+      <c r="D62" s="11" t="inlineStr">
         <is>
           <t>ĐỦ</t>
         </is>
@@ -2774,7 +2758,7 @@
         </is>
       </c>
       <c r="F62" s="10" t="inlineStr"/>
-      <c r="G62" s="14" t="inlineStr">
+      <c r="G62" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2798,22 +2782,18 @@
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>MỘT PHẦN</t>
+          <t>ĐỦ</t>
         </is>
       </c>
       <c r="E63" s="10" t="inlineStr">
         <is>
-          <t>`eaa report kpi` + sổ tay lỗi tích luỹ</t>
-        </is>
-      </c>
-      <c r="F63" s="10" t="inlineStr">
-        <is>
-          <t>Chưa tự đề xuất 'nên tạo công cụ mới cho việc này'</t>
-        </is>
-      </c>
+          <t>`eaa report kpi` + sổ tay lỗi + `eaa skill mine` đọc nhật ký thật và đề xuất rút chuỗi hay lặp thành kỹ năng</t>
+        </is>
+      </c>
+      <c r="F63" s="10" t="inlineStr"/>
       <c r="G63" s="12" t="inlineStr">
         <is>
-          <t>Vừa</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2840,7 +2820,7 @@
           <t>Báo cáo ngắn theo mốc, không dội log thô</t>
         </is>
       </c>
-      <c r="D65" s="13" t="inlineStr">
+      <c r="D65" s="11" t="inlineStr">
         <is>
           <t>ĐỦ</t>
         </is>
@@ -2851,7 +2831,7 @@
         </is>
       </c>
       <c r="F65" s="10" t="inlineStr"/>
-      <c r="G65" s="14" t="inlineStr">
+      <c r="G65" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2873,7 +2853,7 @@
           <t>Hỏi đúng lúc: thiếu quyền, cần quyết định giữa các phương án</t>
         </is>
       </c>
-      <c r="D66" s="13" t="inlineStr">
+      <c r="D66" s="11" t="inlineStr">
         <is>
           <t>ĐỦ</t>
         </is>
@@ -2884,7 +2864,7 @@
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr"/>
-      <c r="G66" s="14" t="inlineStr">
+      <c r="G66" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2906,7 +2886,7 @@
           <t>Giải thích rủi ro trước khi cài thứ ảnh hưởng hệ thống</t>
         </is>
       </c>
-      <c r="D67" s="13" t="inlineStr">
+      <c r="D67" s="11" t="inlineStr">
         <is>
           <t>ĐỦ</t>
         </is>
@@ -2917,7 +2897,7 @@
         </is>
       </c>
       <c r="F67" s="10" t="inlineStr"/>
-      <c r="G67" s="14" t="inlineStr">
+      <c r="G67" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2939,7 +2919,7 @@
           <t>Tổng kết cuối: có gì mới, dùng ra sao, chú ý gì</t>
         </is>
       </c>
-      <c r="D68" s="13" t="inlineStr">
+      <c r="D68" s="11" t="inlineStr">
         <is>
           <t>ĐỦ</t>
         </is>
@@ -2950,7 +2930,7 @@
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr"/>
-      <c r="G68" s="14" t="inlineStr">
+      <c r="G68" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2979,14 +2959,14 @@
           <t>Dùng được cho việc NHỎ mà không bắt đi hết vòng đời</t>
         </is>
       </c>
-      <c r="D70" s="11" t="inlineStr">
+      <c r="D70" s="13" t="inlineStr">
         <is>
           <t>MỘT PHẦN</t>
         </is>
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>`eaa scratch` sinh sẵn constraints + hardware_profile; 4 lệnh mới (environ/research/read + memory/playbook/tool) chạy KHÔNG cần dự án nào</t>
+          <t>`eaa scratch` sinh sẵn hồ sơ; 7 lệnh mới chạy không cần dự án; `eaa focus` nói rõ còn chặng nào</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
@@ -2994,7 +2974,7 @@
           <t>Vẫn phải `eaa init` trước khi vào `eaa chat`</t>
         </is>
       </c>
-      <c r="G70" s="12" t="inlineStr">
+      <c r="G70" s="15" t="inlineStr">
         <is>
           <t>Vừa</t>
         </is>
@@ -3018,22 +2998,18 @@
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>MỘT PHẦN</t>
+          <t>ĐỦ</t>
         </is>
       </c>
       <c r="E71" s="10" t="inlineStr">
         <is>
-          <t>`eaa resume` khôi phục sau gián đoạn (N-907)</t>
-        </is>
-      </c>
-      <c r="F71" s="10" t="inlineStr">
-        <is>
-          <t>Khôi phục ≠ bắt đầu giữa chừng. Không có đường vào thẳng G5 mà bỏ G0–G4</t>
-        </is>
-      </c>
-      <c r="G71" s="17" t="inlineStr">
-        <is>
-          <t>Cao</t>
+          <t>eaa/focus.py: tính TOÀN BỘ tiền điều kiện tới eaa gen thay vì báo cái chặn đầu tiên; nói rõ chặng nào Agent lo được, --run dừng ở chặng đầu tiên của người · TC-72</t>
+        </is>
+      </c>
+      <c r="F71" s="10" t="inlineStr"/>
+      <c r="G71" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3029,7 @@
           <t>Chế độ không cần toolchain / không cần phần cứng</t>
         </is>
       </c>
-      <c r="D72" s="11" t="inlineStr">
+      <c r="D72" s="13" t="inlineStr">
         <is>
           <t>MỘT PHẦN</t>
         </is>
@@ -3068,7 +3044,7 @@
           <t>Cổng compile/static vẫn đòi toolchain — đúng thiết kế cho bản bàn giao</t>
         </is>
       </c>
-      <c r="G72" s="14" t="inlineStr">
+      <c r="G72" s="12" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
@@ -3090,7 +3066,7 @@
           <t>Người dùng tự chọn cổng nào bật, cổng nào tắt</t>
         </is>
       </c>
-      <c r="D73" s="15" t="inlineStr">
+      <c r="D73" s="14" t="inlineStr">
         <is>
           <t>CHƯA</t>
         </is>
@@ -3105,7 +3081,7 @@
           <t>Cẩn trọng: cổng tắt được thì bất biến 'merge chỉ khi TOÀN BỘ passed' mất nghĩa. Nếu làm thì phải là 'chế độ nháp, không bao giờ merge được'</t>
         </is>
       </c>
-      <c r="G73" s="12" t="inlineStr">
+      <c r="G73" s="15" t="inlineStr">
         <is>
           <t>Vừa</t>
         </is>
@@ -3207,12 +3183,12 @@
           <t>Tiếp nhận yêu cầu bằng lời của người dùng</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E3" s="14" t="inlineStr">
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
@@ -3244,12 +3220,12 @@
           <t>Dò phần cứng đang cắm vào máy</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
@@ -3281,12 +3257,12 @@
           <t>Nhận dạng bo/MCU từ dấu hiệu dò được</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E5" s="14" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
@@ -3318,12 +3294,12 @@
           <t>Thu thập tài liệu gốc</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
@@ -3355,12 +3331,12 @@
           <t>Lập danh mục giả định ban đầu</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
@@ -3392,12 +3368,12 @@
           <t>Xác định phạm vi và cái KHÔNG làm</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
@@ -3436,12 +3412,12 @@
           <t>Chốt ràng buộc cứng</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
@@ -3473,12 +3449,12 @@
           <t>Định nghĩa tiêu chí nghiệm thu ĐO ĐƯỢC</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
@@ -3510,12 +3486,12 @@
           <t>Chọn kiến trúc phần mềm</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E12" s="14" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
@@ -3547,12 +3523,12 @@
           <t>Phân bổ tài nguyên phần cứng</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
@@ -3584,12 +3560,12 @@
           <t>Chốt sơ đồ chân</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
@@ -3621,12 +3597,12 @@
           <t>Lập ngân sách tài nguyên</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
@@ -3658,12 +3634,12 @@
           <t>Phân tích hỏng hóc và hệ quả</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E16" s="14" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
@@ -3695,12 +3671,12 @@
           <t>Xác định chế độ an toàn</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
@@ -3739,12 +3715,12 @@
           <t>Kiểm công cụ đã có trên máy</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
@@ -3776,12 +3752,12 @@
           <t>Tìm công cụ chưa biết cách cài</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E20" s="14" t="inlineStr">
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
@@ -3813,12 +3789,12 @@
           <t>Cài công cụ</t>
         </is>
       </c>
-      <c r="D21" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
@@ -3850,12 +3826,12 @@
           <t>Khóa phiên bản môi trường</t>
         </is>
       </c>
-      <c r="D22" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E22" s="14" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
@@ -3887,12 +3863,12 @@
           <t>Dựng kho mã và quy ước commit</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E23" s="14" t="inlineStr">
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
@@ -3931,12 +3907,12 @@
           <t>Chọn trang tài liệu cần trích</t>
         </is>
       </c>
-      <c r="D25" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E25" s="14" t="inlineStr">
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
@@ -3968,12 +3944,12 @@
           <t>Chưng cất trích đoạn thành bảng thanh ghi–bit</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E26" s="14" t="inlineStr">
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
@@ -4005,12 +3981,12 @@
           <t>Dựng đồ thị tri thức</t>
         </is>
       </c>
-      <c r="D27" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E27" s="14" t="inlineStr">
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
@@ -4042,12 +4018,12 @@
           <t>Phát hiện mâu thuẫn nguồn</t>
         </is>
       </c>
-      <c r="D28" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E28" s="14" t="inlineStr">
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
@@ -4079,12 +4055,12 @@
           <t>Tự đánh giá đủ thông tin trước khi sinh mã</t>
         </is>
       </c>
-      <c r="D29" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E29" s="14" t="inlineStr">
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
@@ -4116,12 +4092,12 @@
           <t>Đi tìm thứ còn thiếu (leo thang 3 bậc)</t>
         </is>
       </c>
-      <c r="D30" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E30" s="14" t="inlineStr">
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
@@ -4153,12 +4129,12 @@
           <t>Quản lý vòng đời tri thức</t>
         </is>
       </c>
-      <c r="D31" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E31" s="14" t="inlineStr">
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
@@ -4190,12 +4166,12 @@
           <t>Theo dõi errata của nhà sản xuất</t>
         </is>
       </c>
-      <c r="D32" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E32" s="14" t="inlineStr">
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
@@ -4234,12 +4210,12 @@
           <t>Phân rã bài toán thành module</t>
         </is>
       </c>
-      <c r="D34" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E34" s="14" t="inlineStr">
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
@@ -4271,12 +4247,12 @@
           <t>Định nghĩa giao diện giữa module</t>
         </is>
       </c>
-      <c r="D35" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E35" s="14" t="inlineStr">
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
@@ -4308,12 +4284,12 @@
           <t>Xếp thứ tự làm theo phụ thuộc</t>
         </is>
       </c>
-      <c r="D36" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E36" s="14" t="inlineStr">
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E36" s="12" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
@@ -4345,12 +4321,12 @@
           <t>Thiết kế lịch chạy</t>
         </is>
       </c>
-      <c r="D37" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E37" s="14" t="inlineStr">
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
@@ -4389,12 +4365,12 @@
           <t>Sinh mã một module</t>
         </is>
       </c>
-      <c r="D39" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E39" s="14" t="inlineStr">
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
@@ -4426,12 +4402,12 @@
           <t>Biên dịch</t>
         </is>
       </c>
-      <c r="D40" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E40" s="14" t="inlineStr">
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
@@ -4463,12 +4439,12 @@
           <t>Phân tích tĩnh theo ràng buộc dự án</t>
         </is>
       </c>
-      <c r="D41" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E41" s="14" t="inlineStr">
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E41" s="12" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
@@ -4500,12 +4476,12 @@
           <t>Kiểm thử đơn vị trên máy chủ</t>
         </is>
       </c>
-      <c r="D42" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E42" s="14" t="inlineStr">
+      <c r="D42" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E42" s="12" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
@@ -4537,12 +4513,12 @@
           <t>Đo chiếm dụng bộ nhớ</t>
         </is>
       </c>
-      <c r="D43" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E43" s="14" t="inlineStr">
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
@@ -4574,12 +4550,12 @@
           <t>Vòng tự sửa khi cổng không đạt</t>
         </is>
       </c>
-      <c r="D44" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E44" s="14" t="inlineStr">
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E44" s="12" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
@@ -4611,12 +4587,12 @@
           <t>Review và hợp nhất</t>
         </is>
       </c>
-      <c r="D45" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E45" s="14" t="inlineStr">
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E45" s="12" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
@@ -4648,12 +4624,12 @@
           <t>Ghi nhận lỗi mô hình bịa ra</t>
         </is>
       </c>
-      <c r="D46" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E46" s="14" t="inlineStr">
+      <c r="D46" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E46" s="12" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
@@ -4692,12 +4668,12 @@
           <t>Dựng mô hình đối tượng điều khiển</t>
         </is>
       </c>
-      <c r="D48" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E48" s="14" t="inlineStr">
+      <c r="D48" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E48" s="12" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
@@ -4729,12 +4705,12 @@
           <t>Chạy mô phỏng vòng kín</t>
         </is>
       </c>
-      <c r="D49" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E49" s="14" t="inlineStr">
+      <c r="D49" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E49" s="12" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
@@ -4766,12 +4742,12 @@
           <t>Quét tham số và đề xuất bộ tham số</t>
         </is>
       </c>
-      <c r="D50" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E50" s="14" t="inlineStr">
+      <c r="D50" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E50" s="12" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
@@ -4803,12 +4779,12 @@
           <t>Tiêm lỗi trong mô phỏng</t>
         </is>
       </c>
-      <c r="D51" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E51" s="14" t="inlineStr">
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E51" s="12" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
@@ -4845,7 +4821,7 @@
           <t>CỐ Ý KHÔNG</t>
         </is>
       </c>
-      <c r="E52" s="14" t="inlineStr">
+      <c r="E52" s="12" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
@@ -4884,12 +4860,12 @@
           <t>Ráp firmware hoàn chỉnh</t>
         </is>
       </c>
-      <c r="D54" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E54" s="14" t="inlineStr">
+      <c r="D54" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E54" s="12" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
@@ -4921,12 +4897,12 @@
           <t>Kiểm bộ nhớ ở tầm firmware</t>
         </is>
       </c>
-      <c r="D55" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E55" s="14" t="inlineStr">
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E55" s="12" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
@@ -4958,12 +4934,12 @@
           <t>Kiểm trước khi nạp</t>
         </is>
       </c>
-      <c r="D56" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E56" s="14" t="inlineStr">
+      <c r="D56" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E56" s="12" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
@@ -4995,12 +4971,12 @@
           <t>Chọn đúng thiết bị để nạp</t>
         </is>
       </c>
-      <c r="D57" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E57" s="14" t="inlineStr">
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E57" s="12" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
@@ -5032,12 +5008,12 @@
           <t>Nạp và ghi nhật ký</t>
         </is>
       </c>
-      <c r="D58" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E58" s="14" t="inlineStr">
+      <c r="D58" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E58" s="12" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
@@ -5069,12 +5045,12 @@
           <t>Kiểm sau khi nạp</t>
         </is>
       </c>
-      <c r="D59" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E59" s="14" t="inlineStr">
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E59" s="12" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
@@ -5113,12 +5089,12 @@
           <t>Thiết lập kênh đo</t>
         </is>
       </c>
-      <c r="D61" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E61" s="14" t="inlineStr">
+      <c r="D61" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E61" s="12" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
@@ -5150,12 +5126,12 @@
           <t>Sinh firmware đo cho từng kịch bản chẩn đoán</t>
         </is>
       </c>
-      <c r="D62" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E62" s="14" t="inlineStr">
+      <c r="D62" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E62" s="12" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
@@ -5187,12 +5163,12 @@
           <t>Chẩn đoán hai kênh</t>
         </is>
       </c>
-      <c r="D63" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E63" s="14" t="inlineStr">
+      <c r="D63" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E63" s="12" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
@@ -5224,12 +5200,12 @@
           <t>Đo đặc tính thời gian thực</t>
         </is>
       </c>
-      <c r="D64" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E64" s="14" t="inlineStr">
+      <c r="D64" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E64" s="12" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
@@ -5261,12 +5237,12 @@
           <t>Đo điện và nhiệt</t>
         </is>
       </c>
-      <c r="D65" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E65" s="14" t="inlineStr">
+      <c r="D65" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E65" s="12" t="inlineStr">
         <is>
           <t>T0</t>
         </is>
@@ -5298,12 +5274,12 @@
           <t>Chẩn đoán sâu bằng công cụ gỡ lỗi</t>
         </is>
       </c>
-      <c r="D66" s="15" t="inlineStr">
+      <c r="D66" s="14" t="inlineStr">
         <is>
           <t>CHƯA</t>
         </is>
       </c>
-      <c r="E66" s="14" t="inlineStr">
+      <c r="E66" s="12" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
@@ -5335,12 +5311,12 @@
           <t>Kiểm độ bền dài hạn</t>
         </is>
       </c>
-      <c r="D67" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E67" s="14" t="inlineStr">
+      <c r="D67" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E67" s="12" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
@@ -5379,12 +5355,12 @@
           <t>Đối chiếu tiêu chí nghiệm thu</t>
         </is>
       </c>
-      <c r="D69" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E69" s="14" t="inlineStr">
+      <c r="D69" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E69" s="12" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
@@ -5416,12 +5392,12 @@
           <t>Phong hạng chất lượng bản mã</t>
         </is>
       </c>
-      <c r="D70" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E70" s="14" t="inlineStr">
+      <c r="D70" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E70" s="12" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
@@ -5453,12 +5429,12 @@
           <t>Giữ bản chạy tốt và quay lui</t>
         </is>
       </c>
-      <c r="D71" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E71" s="14" t="inlineStr">
+      <c r="D71" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E71" s="12" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
@@ -5490,12 +5466,12 @@
           <t>Xuất báo cáo và dấu vết</t>
         </is>
       </c>
-      <c r="D72" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E72" s="14" t="inlineStr">
+      <c r="D72" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E72" s="12" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
@@ -5527,12 +5503,12 @@
           <t>Bàn giao tài liệu vận hành</t>
         </is>
       </c>
-      <c r="D73" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E73" s="14" t="inlineStr">
+      <c r="D73" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E73" s="12" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
@@ -5571,12 +5547,12 @@
           <t>Đánh giá ảnh hưởng khi tài liệu đổi</t>
         </is>
       </c>
-      <c r="D75" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E75" s="14" t="inlineStr">
+      <c r="D75" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E75" s="12" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
@@ -5608,12 +5584,12 @@
           <t>Đánh giá ảnh hưởng khi linh kiện đổi</t>
         </is>
       </c>
-      <c r="D76" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E76" s="14" t="inlineStr">
+      <c r="D76" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E76" s="12" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
@@ -5645,12 +5621,12 @@
           <t>Chẩn đoán sự cố ngoài hiện trường</t>
         </is>
       </c>
-      <c r="D77" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E77" s="14" t="inlineStr">
+      <c r="D77" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E77" s="12" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
@@ -5682,12 +5658,12 @@
           <t>Cập nhật firmware cho thiết bị đã triển khai</t>
         </is>
       </c>
-      <c r="D78" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E78" s="14" t="inlineStr">
+      <c r="D78" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E78" s="12" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
@@ -5726,12 +5702,12 @@
           <t>Giữ ranh giới tổng quát / nền tảng / dự án</t>
         </is>
       </c>
-      <c r="D80" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E80" s="14" t="inlineStr">
+      <c r="D80" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E80" s="12" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
@@ -5763,12 +5739,12 @@
           <t>Bảo vệ khóa và bí mật</t>
         </is>
       </c>
-      <c r="D81" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E81" s="14" t="inlineStr">
+      <c r="D81" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E81" s="12" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
@@ -5800,12 +5776,12 @@
           <t>Không bao giờ hành động ngoài ý muốn người</t>
         </is>
       </c>
-      <c r="D82" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E82" s="14" t="inlineStr">
+      <c r="D82" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E82" s="12" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
@@ -5837,12 +5813,12 @@
           <t>Nói rõ mức tin cậy của mọi điều mình nói</t>
         </is>
       </c>
-      <c r="D83" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E83" s="14" t="inlineStr">
+      <c r="D83" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E83" s="12" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
@@ -5874,12 +5850,12 @@
           <t>Quản lý chi phí gọi mô hình</t>
         </is>
       </c>
-      <c r="D84" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E84" s="14" t="inlineStr">
+      <c r="D84" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E84" s="12" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
@@ -5911,12 +5887,12 @@
           <t>Ghi nhận mọi sai lệch so với thiết kế</t>
         </is>
       </c>
-      <c r="D85" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E85" s="14" t="inlineStr">
+      <c r="D85" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E85" s="12" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
@@ -5948,12 +5924,12 @@
           <t>Tự đánh giá và cải tiến quy trình</t>
         </is>
       </c>
-      <c r="D86" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E86" s="14" t="inlineStr">
+      <c r="D86" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E86" s="12" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
@@ -5985,12 +5961,12 @@
           <t>Khôi phục sau gián đoạn</t>
         </is>
       </c>
-      <c r="D87" s="13" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E87" s="14" t="inlineStr">
+      <c r="D87" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E87" s="12" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
@@ -6032,7 +6008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -6076,14 +6052,14 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>Cao</t>
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>Vừa</t>
         </is>
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>C10.2</t>
+          <t>C10.1</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
@@ -6093,29 +6069,29 @@
       </c>
       <c r="D2" s="10" t="inlineStr">
         <is>
-          <t>Vào giữa quy trình, bỏ qua giai đoạn không cần</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="inlineStr">
+          <t>Dùng được cho việc NHỎ mà không bắt đi hết vòng đời</t>
+        </is>
+      </c>
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>MỘT PHẦN</t>
         </is>
       </c>
       <c r="F2" s="10" t="inlineStr">
         <is>
-          <t>Khôi phục ≠ bắt đầu giữa chừng. Không có đường vào thẳng G5 mà bỏ G0–G4</t>
+          <t>Vẫn phải `eaa init` trước khi vào `eaa chat`</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="inlineStr">
-        <is>
-          <t>Cao</t>
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>Vừa</t>
         </is>
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>C7.5</t>
+          <t>C10.4</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
@@ -6125,29 +6101,29 @@
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>Gộp chuỗi tool hay dùng thành tool cấp cao hơn (skill/workflow)</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
+          <t>Người dùng tự chọn cổng nào bật, cổng nào tắt</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
         <is>
           <t>CHƯA</t>
         </is>
       </c>
       <c r="F3" s="10" t="inlineStr">
         <is>
-          <t>Hiện chuỗi ấy được đóng cứng trong quy trình G0→G10 thay vì được rút ra thành skill — xem C10.1</t>
+          <t>Cẩn trọng: cổng tắt được thì bất biến 'merge chỉ khi TOÀN BỘ passed' mất nghĩa. Nếu làm thì phải là 'chế độ nháp, không bao giờ merge được'</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Vừa</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>C1.1</t>
+          <t>C3.3</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
@@ -6157,29 +6133,29 @@
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>Hiểu và phân rã nhiệm vụ thành bước con, xác định mỗi bước cần loại công cụ gì</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
+          <t>Đánh giá &amp; chọn công cụ: còn bảo trì, license, độ phổ biến, phụ thuộc hệ thống</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>MỘT PHẦN</t>
         </is>
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
-          <t>Phân rã vẫn trong danh mục công cụ, NHƯNG từ SL-77 Agent tự VIẾT được công cụ mới khi việc cần làm không có lệnh nào sẵn (`tool propose`). Còn thiếu: nó chưa tự NHẬN RA lúc nào nên viết</t>
+          <t>Chưa tự đọc chỉ số bảo trì / license / độ phổ biến từ kho gói</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Vừa</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>C10.1</t>
+          <t>C6.1</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
@@ -6189,29 +6165,29 @@
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>Dùng được cho việc NHỎ mà không bắt đi hết vòng đời</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
+          <t>Nhận diện khi nào nên tự viết thay vì đi tìm</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>MỘT PHẦN</t>
         </is>
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
-          <t>Vẫn phải `eaa init` trước khi vào `eaa chat`</t>
+          <t>Agent chưa tự NHẬN RA lúc nào nên viết — vẫn cần người gợi ý</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Vừa</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>C10.4</t>
+          <t>C7.4</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -6221,61 +6197,61 @@
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>Người dùng tự chọn cổng nào bật, cổng nào tắt</t>
-        </is>
-      </c>
-      <c r="E6" s="15" t="inlineStr">
+          <t>Đánh giá chất lượng sau khi dùng thật (hay hỏng? chậm?)</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>MỘT PHẦN</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>Chưa đo độ tin cậy từng công cụ tự sinh sau khi dùng thật</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>Vừa</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>N-085</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>nhúng</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Chẩn đoán sâu bằng công cụ gỡ lỗi</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>CHƯA</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>Cẩn trọng: cổng tắt được thì bất biến 'merge chỉ khi TOÀN BỘ passed' mất nghĩa. Nếu làm thì phải là 'chế độ nháp, không bao giờ merge được'</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>Vừa</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>C3.3</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>nền</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>Đánh giá &amp; chọn công cụ: còn bảo trì, license, độ phổ biến, phụ thuộc hệ thống</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
-        </is>
-      </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
-          <t>Chưa tự đọc chỉ số bảo trì / license / độ phổ biến từ kho gói</t>
+          <t>Ngoài phạm vi đề án (đã ghi từ trước).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>Vừa</t>
+          <t>Thấp</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>C6.1</t>
+          <t>C10.3</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -6285,29 +6261,29 @@
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>Nhận diện khi nào nên tự viết thay vì đi tìm</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
+          <t>Chế độ không cần toolchain / không cần phần cứng</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>MỘT PHẦN</t>
         </is>
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>Agent chưa tự NHẬN RA lúc nào nên viết — vẫn cần người gợi ý</t>
+          <t>Cổng compile/static vẫn đòi toolchain — đúng thiết kế cho bản bàn giao</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>Vừa</t>
+          <t>Thấp</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>C7.4</t>
+          <t>C2.4</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
@@ -6317,29 +6293,29 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>Đánh giá chất lượng sau khi dùng thật (hay hỏng? chậm?)</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
+          <t>Dò runtime: python --version, pip list, npm ls, which, docker ps</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>MỘT PHẦN</t>
         </is>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
-          <t>Chưa đo độ tin cậy từng công cụ tự sinh sau khi dùng thật</t>
+          <t>Vẫn chưa liệt kê được gói đã cài (pip list / npm ls)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>Vừa</t>
+          <t>Thấp</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>C8.5</t>
+          <t>C2.9</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -6349,342 +6325,214 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>Tự đánh giá cuối nhiệm vụ, đề xuất tạo tool/skill mới</t>
-        </is>
-      </c>
-      <c r="E10" s="11" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
+          <t>Phát hiện xung đột phụ thuộc</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>CHƯA</t>
         </is>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
-          <t>Chưa tự đề xuất 'nên tạo công cụ mới cho việc này'</t>
+          <t>Chưa gặp vấn đề thật vì công cụ nhúng là binary độc lập, ít phụ thuộc chéo</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>Vừa</t>
+          <t>Thấp</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>N-085</t>
+          <t>C4.1</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>nhúng</t>
+          <t>nền</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>Chẩn đoán sâu bằng công cụ gỡ lỗi</t>
-        </is>
-      </c>
-      <c r="E11" s="15" t="inlineStr">
+          <t>Chọn cơ chế cài phù hợp</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>MỘT PHẦN</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>Không build từ nguồn, không chạy container. Đủ cho toolchain nhúng phổ biến, thiếu cho công cụ lạ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>Thấp</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>C4.2</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>nền</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Cô lập môi trường (venv riêng cho tool mới)</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>MỘT PHẦN</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có venv riêng cho công cụ NGOÀI (avr-gcc, cppcheck…)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Thấp</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>C4.3</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>nền</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>Cài theo thứ tự phụ thuộc (system lib trước, runtime package sau)</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
         <is>
           <t>CHƯA</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
-        <is>
-          <t>Ngoài phạm vi đề án (đã ghi từ trước).</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>Hiện mỗi Tool Card độc lập, không khai phụ thuộc lẫn nhau</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>C10.3</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>C5.6</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>nền</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>Chế độ không cần toolchain / không cần phần cứng</t>
-        </is>
-      </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>Tự viết giải pháp tối thiểu thay thế</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>MỘT PHẦN</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>Cổng compile/static vẫn đòi toolchain — đúng thiết kế cho bản bàn giao</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>Chưa nối tự động vào thang gỡ lỗi cài đặt</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>C2.4</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>C6.8</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>nền</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>Dò runtime: python --version, pip list, npm ls, which, docker ps</t>
-        </is>
-      </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>Tài liệu hoá tool mới: README ngắn, ví dụ, giới hạn đã biết</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>MỘT PHẦN</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t>Vẫn chưa liệt kê được gói đã cài (pip list / npm ls)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>Chưa sinh README riêng cho từng công cụ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>Thấp</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>C2.9</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>C7.3</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>nền</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>Phát hiện xung đột phụ thuộc</t>
-        </is>
-      </c>
-      <c r="E14" s="15" t="inlineStr">
-        <is>
-          <t>CHƯA</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>Chưa gặp vấn đề thật vì công cụ nhúng là binary độc lập, ít phụ thuộc chéo</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>Thấp</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>C4.1</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>nền</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>Chọn cơ chế cài phù hợp</t>
-        </is>
-      </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>Versioning tool, giữ bản cũ nếu bản mới hỏng</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>MỘT PHẦN</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
-        <is>
-          <t>Không build từ nguồn, không chạy container. Đủ cho toolchain nhúng phổ biến, thiếu cho công cụ lạ</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>Thấp</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>C4.2</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>nền</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>Cô lập môi trường (venv riêng cho tool mới)</t>
-        </is>
-      </c>
-      <c r="E16" s="11" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
-        </is>
-      </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>Chưa có venv riêng cho công cụ NGOÀI (avr-gcc, cppcheck…)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>Thấp</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>C4.3</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>nền</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>Cài theo thứ tự phụ thuộc (system lib trước, runtime package sau)</t>
-        </is>
-      </c>
-      <c r="E17" s="15" t="inlineStr">
-        <is>
-          <t>CHƯA</t>
-        </is>
-      </c>
-      <c r="F17" s="10" t="inlineStr">
-        <is>
-          <t>Hiện mỗi Tool Card độc lập, không khai phụ thuộc lẫn nhau</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t>Thấp</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>C5.6</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>nền</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>Tự viết giải pháp tối thiểu thay thế</t>
-        </is>
-      </c>
-      <c r="E18" s="11" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
-        <is>
-          <t>Chưa nối tự động vào thang gỡ lỗi cài đặt</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>Thấp</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>C6.8</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>nền</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>Tài liệu hoá tool mới: README ngắn, ví dụ, giới hạn đã biết</t>
-        </is>
-      </c>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
-        </is>
-      </c>
-      <c r="F19" s="10" t="inlineStr">
-        <is>
-          <t>Chưa sinh README riêng cho từng công cụ</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="14" t="inlineStr">
-        <is>
-          <t>Thấp</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>C7.3</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>nền</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>Versioning tool, giữ bản cũ nếu bản mới hỏng</t>
-        </is>
-      </c>
-      <c r="E20" s="11" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
-        </is>
-      </c>
-      <c r="F20" s="10" t="inlineStr">
-        <is>
           <t>Không giữ song song hai bản để quay lui</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F20"/>
+  <autoFilter ref="A1:F16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6695,7 +6543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6738,17 +6586,17 @@
           <t>budget propose</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C2" s="14" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="D2" s="14" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C2" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t>có</t>
         </is>
@@ -6761,17 +6609,17 @@
           <t>budget show</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C3" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>có</t>
         </is>
@@ -6784,17 +6632,17 @@
           <t>budget tokens</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C4" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>có</t>
         </is>
@@ -6807,17 +6655,17 @@
           <t>capabilities</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>có</t>
         </is>
@@ -6830,17 +6678,17 @@
           <t>datasheet list</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C6" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>có</t>
         </is>
@@ -6853,17 +6701,17 @@
           <t>deviations</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>không</t>
         </is>
@@ -6876,17 +6724,17 @@
           <t>diagnose list</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>có</t>
         </is>
@@ -6899,17 +6747,17 @@
           <t>diagnose measure</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>có</t>
         </is>
@@ -6922,17 +6770,17 @@
           <t>diagnose select</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>có</t>
         </is>
@@ -6945,17 +6793,17 @@
           <t>docs list</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>có</t>
         </is>
@@ -6968,17 +6816,17 @@
           <t>environ</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>không</t>
         </is>
@@ -6991,17 +6839,17 @@
           <t>errata lookup</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>có</t>
         </is>
@@ -7014,17 +6862,17 @@
           <t>errata show</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>có</t>
         </is>
@@ -7037,17 +6885,17 @@
           <t>field</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>có</t>
         </is>
@@ -7057,20 +6905,20 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>gate show</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D16" s="14" t="inlineStr">
+          <t>focus</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>có</t>
         </is>
@@ -7080,20 +6928,20 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>handover doc</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D17" s="14" t="inlineStr">
+          <t>gate show</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>có</t>
         </is>
@@ -7103,20 +6951,20 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>handover rollout</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C18" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D18" s="14" t="inlineStr">
+          <t>handover doc</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>có</t>
         </is>
@@ -7126,20 +6974,20 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>handover swap</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C19" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D19" s="14" t="inlineStr">
+          <t>handover rollout</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>có</t>
         </is>
@@ -7149,20 +6997,20 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>interface</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C20" s="14" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="D20" s="14" t="inlineStr">
+          <t>handover swap</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>có</t>
         </is>
@@ -7172,20 +7020,20 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>ledger list</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C21" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D21" s="14" t="inlineStr">
+          <t>interface</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t>có</t>
         </is>
@@ -7195,22 +7043,22 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>memory add</t>
-        </is>
-      </c>
-      <c r="B22" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C22" s="14" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="D22" s="14" t="inlineStr">
-        <is>
-          <t>không</t>
+          <t>ledger list</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr"/>
@@ -7218,20 +7066,20 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>memory list</t>
-        </is>
-      </c>
-      <c r="B23" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C23" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D23" s="14" t="inlineStr">
+          <t>memory add</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
         <is>
           <t>không</t>
         </is>
@@ -7241,20 +7089,20 @@
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>packs</t>
-        </is>
-      </c>
-      <c r="B24" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C24" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D24" s="14" t="inlineStr">
+          <t>memory list</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
         <is>
           <t>không</t>
         </is>
@@ -7264,22 +7112,22 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>plan add</t>
-        </is>
-      </c>
-      <c r="B25" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C25" s="14" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="D25" s="14" t="inlineStr">
-        <is>
-          <t>có</t>
+          <t>packs</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>không</t>
         </is>
       </c>
       <c r="E25" s="10" t="inlineStr"/>
@@ -7287,20 +7135,20 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>plan list</t>
-        </is>
-      </c>
-      <c r="B26" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C26" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D26" s="14" t="inlineStr">
+          <t>plan add</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
         <is>
           <t>có</t>
         </is>
@@ -7310,22 +7158,22 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>playbook list</t>
-        </is>
-      </c>
-      <c r="B27" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>không</t>
+          <t>plan list</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr"/>
@@ -7333,20 +7181,20 @@
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>playbook lookup</t>
-        </is>
-      </c>
-      <c r="B28" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C28" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D28" s="14" t="inlineStr">
+          <t>playbook list</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
         <is>
           <t>không</t>
         </is>
@@ -7356,20 +7204,20 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>playbook record</t>
-        </is>
-      </c>
-      <c r="B29" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C29" s="14" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="D29" s="14" t="inlineStr">
+          <t>playbook lookup</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
         <is>
           <t>không</t>
         </is>
@@ -7379,20 +7227,20 @@
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>policy</t>
-        </is>
-      </c>
-      <c r="B30" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C30" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D30" s="14" t="inlineStr">
+          <t>playbook record</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
         <is>
           <t>không</t>
         </is>
@@ -7402,22 +7250,22 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>propose acceptance</t>
-        </is>
-      </c>
-      <c r="B31" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C31" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D31" s="14" t="inlineStr">
-        <is>
-          <t>có</t>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>không</t>
         </is>
       </c>
       <c r="E31" s="10" t="inlineStr"/>
@@ -7425,20 +7273,20 @@
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>propose constraints</t>
-        </is>
-      </c>
-      <c r="B32" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C32" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D32" s="14" t="inlineStr">
+          <t>propose acceptance</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
         <is>
           <t>có</t>
         </is>
@@ -7448,20 +7296,20 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>propose pinmap</t>
-        </is>
-      </c>
-      <c r="B33" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C33" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D33" s="14" t="inlineStr">
+          <t>propose constraints</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
         <is>
           <t>có</t>
         </is>
@@ -7471,20 +7319,20 @@
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>propose plant</t>
-        </is>
-      </c>
-      <c r="B34" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C34" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D34" s="14" t="inlineStr">
+          <t>propose pinmap</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
         <is>
           <t>có</t>
         </is>
@@ -7494,20 +7342,20 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>propose scope</t>
-        </is>
-      </c>
-      <c r="B35" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C35" s="14" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="D35" s="14" t="inlineStr">
+          <t>propose plant</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
         <is>
           <t>có</t>
         </is>
@@ -7517,22 +7365,22 @@
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="B36" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C36" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D36" s="14" t="inlineStr">
-        <is>
-          <t>không</t>
+          <t>propose scope</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
         </is>
       </c>
       <c r="E36" s="10" t="inlineStr"/>
@@ -7540,22 +7388,22 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>report kpi</t>
-        </is>
-      </c>
-      <c r="B37" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C37" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D37" s="14" t="inlineStr">
-        <is>
-          <t>có</t>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>không</t>
         </is>
       </c>
       <c r="E37" s="10" t="inlineStr"/>
@@ -7563,20 +7411,20 @@
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>report retrieval</t>
-        </is>
-      </c>
-      <c r="B38" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C38" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D38" s="14" t="inlineStr">
+          <t>report kpi</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
         <is>
           <t>có</t>
         </is>
@@ -7586,20 +7434,20 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>report review</t>
-        </is>
-      </c>
-      <c r="B39" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C39" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D39" s="14" t="inlineStr">
+          <t>report retrieval</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
         <is>
           <t>có</t>
         </is>
@@ -7609,20 +7457,20 @@
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>report versions</t>
-        </is>
-      </c>
-      <c r="B40" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C40" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D40" s="14" t="inlineStr">
+          <t>report review</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
         <is>
           <t>có</t>
         </is>
@@ -7632,22 +7480,22 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="B41" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C41" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D41" s="14" t="inlineStr">
-        <is>
-          <t>không</t>
+          <t>report versions</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
         </is>
       </c>
       <c r="E41" s="10" t="inlineStr"/>
@@ -7655,22 +7503,22 @@
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>resolve</t>
-        </is>
-      </c>
-      <c r="B42" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C42" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D42" s="14" t="inlineStr">
-        <is>
-          <t>có</t>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>không</t>
         </is>
       </c>
       <c r="E42" s="10" t="inlineStr"/>
@@ -7678,20 +7526,20 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>safety propose</t>
-        </is>
-      </c>
-      <c r="B43" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C43" s="14" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="D43" s="14" t="inlineStr">
+          <t>resolve</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
         <is>
           <t>có</t>
         </is>
@@ -7701,20 +7549,20 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>safety show</t>
-        </is>
-      </c>
-      <c r="B44" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C44" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D44" s="14" t="inlineStr">
+          <t>safety propose</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
         <is>
           <t>có</t>
         </is>
@@ -7724,22 +7572,22 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>scratch</t>
-        </is>
-      </c>
-      <c r="B45" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C45" s="14" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="D45" s="14" t="inlineStr">
-        <is>
-          <t>không</t>
+          <t>safety show</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
         </is>
       </c>
       <c r="E45" s="10" t="inlineStr"/>
@@ -7747,22 +7595,22 @@
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>sim run</t>
-        </is>
-      </c>
-      <c r="B46" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C46" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D46" s="14" t="inlineStr">
-        <is>
-          <t>có</t>
+          <t>scratch</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C46" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>không</t>
         </is>
       </c>
       <c r="E46" s="10" t="inlineStr"/>
@@ -7770,20 +7618,20 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>sources need</t>
-        </is>
-      </c>
-      <c r="B47" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C47" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D47" s="14" t="inlineStr">
+          <t>sim run</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C47" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
         <is>
           <t>có</t>
         </is>
@@ -7793,22 +7641,22 @@
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>sources pages</t>
-        </is>
-      </c>
-      <c r="B48" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C48" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D48" s="14" t="inlineStr">
-        <is>
-          <t>có</t>
+          <t>skill list</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>không</t>
         </is>
       </c>
       <c r="E48" s="10" t="inlineStr"/>
@@ -7816,20 +7664,20 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B49" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C49" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D49" s="14" t="inlineStr">
+          <t>skill mine</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
         <is>
           <t>không</t>
         </is>
@@ -7839,22 +7687,22 @@
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>survey</t>
-        </is>
-      </c>
-      <c r="B50" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C50" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D50" s="14" t="inlineStr">
-        <is>
-          <t>có</t>
+          <t>skill run</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>không</t>
         </is>
       </c>
       <c r="E50" s="10" t="inlineStr"/>
@@ -7862,20 +7710,20 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>tool list</t>
-        </is>
-      </c>
-      <c r="B51" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C51" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D51" s="14" t="inlineStr">
+          <t>skill verify</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
         <is>
           <t>không</t>
         </is>
@@ -7885,22 +7733,22 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>tool propose</t>
-        </is>
-      </c>
-      <c r="B52" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C52" s="14" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="D52" s="14" t="inlineStr">
-        <is>
-          <t>không</t>
+          <t>sources need</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
         </is>
       </c>
       <c r="E52" s="10" t="inlineStr"/>
@@ -7908,22 +7756,22 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>tool run</t>
-        </is>
-      </c>
-      <c r="B53" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C53" s="14" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="D53" s="14" t="inlineStr">
-        <is>
-          <t>không</t>
+          <t>sources pages</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
         </is>
       </c>
       <c r="E53" s="10" t="inlineStr"/>
@@ -7931,20 +7779,20 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>tool verify</t>
-        </is>
-      </c>
-      <c r="B54" s="13" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="C54" s="14" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="D54" s="14" t="inlineStr">
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C54" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
         <is>
           <t>không</t>
         </is>
@@ -7954,64 +7802,68 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>brief</t>
-        </is>
-      </c>
-      <c r="B55" s="16" t="inlineStr">
-        <is>
-          <t>KHÔNG</t>
-        </is>
-      </c>
-      <c r="C55" s="14" t="inlineStr"/>
-      <c r="D55" s="14" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E55" s="10" t="inlineStr">
-        <is>
-          <t>Lệnh này hỏi bạn trực tiếp — tôi gọi hộ thì mất đúng phần hỏi.</t>
-        </is>
-      </c>
+          <t>survey</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>build</t>
-        </is>
-      </c>
-      <c r="B56" s="16" t="inlineStr">
-        <is>
-          <t>KHÔNG</t>
-        </is>
-      </c>
-      <c r="C56" s="14" t="inlineStr"/>
-      <c r="D56" s="14" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E56" s="10" t="inlineStr">
-        <is>
-          <t>Ráp firmware là bước trước khi nạp; bạn chạy để còn kiểm ảnh sinh ra.</t>
-        </is>
-      </c>
+          <t>tool list</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C56" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D56" s="12" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E56" s="10" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>chat</t>
-        </is>
-      </c>
-      <c r="B57" s="16" t="inlineStr">
-        <is>
-          <t>KHÔNG</t>
-        </is>
-      </c>
-      <c r="C57" s="14" t="inlineStr"/>
-      <c r="D57" s="14" t="inlineStr">
-        <is>
-          <t>có</t>
+          <t>tool propose</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C57" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>không</t>
         </is>
       </c>
       <c r="E57" s="10" t="inlineStr"/>
@@ -8019,53 +7871,53 @@
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>decide</t>
-        </is>
-      </c>
-      <c r="B58" s="16" t="inlineStr">
-        <is>
-          <t>KHÔNG</t>
-        </is>
-      </c>
-      <c r="C58" s="14" t="inlineStr"/>
-      <c r="D58" s="14" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E58" s="10" t="inlineStr">
-        <is>
-          <t>Trình phương án để BẠN chọn; tôi gọi hộ thì mất đúng chỗ bạn chọn.</t>
-        </is>
-      </c>
+          <t>tool run</t>
+        </is>
+      </c>
+      <c r="B58" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C58" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="D58" s="12" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E58" s="10" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>doctor</t>
-        </is>
-      </c>
-      <c r="B59" s="16" t="inlineStr">
-        <is>
-          <t>KHÔNG</t>
-        </is>
-      </c>
-      <c r="C59" s="14" t="inlineStr"/>
-      <c r="D59" s="14" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E59" s="10" t="inlineStr">
-        <is>
-          <t>Cài đặt công cụ đổi máy của bạn. Tôi quét và báo được ('doctor' không cờ là chỉ đọc), nhưng '--fix' phải do bạn chạy và xác nhận từng lệnh.</t>
-        </is>
-      </c>
+          <t>tool verify</t>
+        </is>
+      </c>
+      <c r="B59" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C59" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="D59" s="12" t="inlineStr">
+        <is>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>endurance</t>
+          <t>brief</t>
         </is>
       </c>
       <c r="B60" s="16" t="inlineStr">
@@ -8073,22 +7925,22 @@
           <t>KHÔNG</t>
         </is>
       </c>
-      <c r="C60" s="14" t="inlineStr"/>
-      <c r="D60" s="14" t="inlineStr">
+      <c r="C60" s="12" t="inlineStr"/>
+      <c r="D60" s="12" t="inlineStr">
         <is>
           <t>có</t>
         </is>
       </c>
       <c r="E60" s="10" t="inlineStr">
         <is>
-          <t>Lệnh này chiếm cổng nối tiếp và chạy hàng giờ; bạn nên tự bố trí.</t>
+          <t>Lệnh này hỏi bạn trực tiếp — tôi gọi hộ thì mất đúng phần hỏi.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>flash</t>
+          <t>build</t>
         </is>
       </c>
       <c r="B61" s="16" t="inlineStr">
@@ -8096,22 +7948,22 @@
           <t>KHÔNG</t>
         </is>
       </c>
-      <c r="C61" s="14" t="inlineStr"/>
-      <c r="D61" s="14" t="inlineStr">
+      <c r="C61" s="12" t="inlineStr"/>
+      <c r="D61" s="12" t="inlineStr">
         <is>
           <t>có</t>
         </is>
       </c>
       <c r="E61" s="10" t="inlineStr">
         <is>
-          <t>Nạp firmware chạm vào thiết bị thật. Luôn cần chính bạn xác nhận — một phiên không có người không được diễn giải thành một người đã đồng ý.</t>
+          <t>Ráp firmware là bước trước khi nạp; bạn chạy để còn kiểm ảnh sinh ra.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>gen</t>
+          <t>chat</t>
         </is>
       </c>
       <c r="B62" s="16" t="inlineStr">
@@ -8119,22 +7971,18 @@
           <t>KHÔNG</t>
         </is>
       </c>
-      <c r="C62" s="14" t="inlineStr"/>
-      <c r="D62" s="14" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E62" s="10" t="inlineStr">
-        <is>
-          <t>Vòng sinh mã ghi số liệu vào kpi_log.csv, và những dòng ấy là DỮ LIỆU THÍ NGHIỆM của Chương 3. Tôi tự khởi động nó sẽ chèn vào bảng số liệu những lượt chạy mà người làm thí nghiệm không định chạy — nên bạn là người bấm nút.</t>
-        </is>
-      </c>
+      <c r="C62" s="12" t="inlineStr"/>
+      <c r="D62" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E62" s="10" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>init</t>
+          <t>decide</t>
         </is>
       </c>
       <c r="B63" s="16" t="inlineStr">
@@ -8142,22 +7990,22 @@
           <t>KHÔNG</t>
         </is>
       </c>
-      <c r="C63" s="14" t="inlineStr"/>
-      <c r="D63" s="14" t="inlineStr">
+      <c r="C63" s="12" t="inlineStr"/>
+      <c r="D63" s="12" t="inlineStr">
         <is>
           <t>có</t>
         </is>
       </c>
       <c r="E63" s="10" t="inlineStr">
         <is>
-          <t>Khởi tạo dự án là quyết định mở đầu, không nên nằm giữa một câu hỏi.</t>
+          <t>Trình phương án để BẠN chọn; tôi gọi hộ thì mất đúng chỗ bạn chọn.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>ports</t>
+          <t>doctor</t>
         </is>
       </c>
       <c r="B64" s="16" t="inlineStr">
@@ -8165,22 +8013,22 @@
           <t>KHÔNG</t>
         </is>
       </c>
-      <c r="C64" s="14" t="inlineStr"/>
-      <c r="D64" s="14" t="inlineStr">
+      <c r="C64" s="12" t="inlineStr"/>
+      <c r="D64" s="12" t="inlineStr">
         <is>
           <t>có</t>
         </is>
       </c>
       <c r="E64" s="10" t="inlineStr">
         <is>
-          <t>Đọc cổng nối tiếp là việc chạm tới máy của bạn.</t>
+          <t>Cài đặt công cụ đổi máy của bạn. Tôi quét và báo được ('doctor' không cờ là chỉ đọc), nhưng '--fix' phải do bạn chạy và xác nhận từng lệnh.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>resume</t>
+          <t>endurance</t>
         </is>
       </c>
       <c r="B65" s="16" t="inlineStr">
@@ -8188,18 +8036,22 @@
           <t>KHÔNG</t>
         </is>
       </c>
-      <c r="C65" s="14" t="inlineStr"/>
-      <c r="D65" s="14" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E65" s="10" t="inlineStr"/>
+      <c r="C65" s="12" t="inlineStr"/>
+      <c r="D65" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E65" s="10" t="inlineStr">
+        <is>
+          <t>Lệnh này chiếm cổng nối tiếp và chạy hàng giờ; bạn nên tự bố trí.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>rollback</t>
+          <t>flash</t>
         </is>
       </c>
       <c r="B66" s="16" t="inlineStr">
@@ -8207,22 +8059,22 @@
           <t>KHÔNG</t>
         </is>
       </c>
-      <c r="C66" s="14" t="inlineStr"/>
-      <c r="D66" s="14" t="inlineStr">
+      <c r="C66" s="12" t="inlineStr"/>
+      <c r="D66" s="12" t="inlineStr">
         <is>
           <t>có</t>
         </is>
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>Quay lui đổi mã đang chạy trên thiết bị — quyết định của bạn.</t>
+          <t>Nạp firmware chạm vào thiết bị thật. Luôn cần chính bạn xác nhận — một phiên không có người không được diễn giải thành một người đã đồng ý.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>scope-image</t>
+          <t>gen</t>
         </is>
       </c>
       <c r="B67" s="16" t="inlineStr">
@@ -8230,22 +8082,22 @@
           <t>KHÔNG</t>
         </is>
       </c>
-      <c r="C67" s="14" t="inlineStr"/>
-      <c r="D67" s="14" t="inlineStr">
+      <c r="C67" s="12" t="inlineStr"/>
+      <c r="D67" s="12" t="inlineStr">
         <is>
           <t>có</t>
         </is>
       </c>
       <c r="E67" s="10" t="inlineStr">
         <is>
-          <t>Cần bạn đối chiếu ảnh gốc rồi chốt số đo.</t>
+          <t>Vòng sinh mã ghi số liệu vào kpi_log.csv, và những dòng ấy là DỮ LIỆU THÍ NGHIỆM của Chương 3. Tôi tự khởi động nó sẽ chèn vào bảng số liệu những lượt chạy mà người làm thí nghiệm không định chạy — nên bạn là người bấm nút.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>telemetry</t>
+          <t>init</t>
         </is>
       </c>
       <c r="B68" s="16" t="inlineStr">
@@ -8253,43 +8105,154 @@
           <t>KHÔNG</t>
         </is>
       </c>
-      <c r="C68" s="14" t="inlineStr"/>
-      <c r="D68" s="14" t="inlineStr">
+      <c r="C68" s="12" t="inlineStr"/>
+      <c r="D68" s="12" t="inlineStr">
         <is>
           <t>có</t>
         </is>
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>Lệnh này chiếm cổng nối tiếp của thiết bị; bạn nên tự cắm và chạy.</t>
+          <t>Khởi tạo dự án là quyết định mở đầu, không nên nằm giữa một câu hỏi.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
+          <t>ports</t>
+        </is>
+      </c>
+      <c r="B69" s="16" t="inlineStr">
+        <is>
+          <t>KHÔNG</t>
+        </is>
+      </c>
+      <c r="C69" s="12" t="inlineStr"/>
+      <c r="D69" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E69" s="10" t="inlineStr">
+        <is>
+          <t>Đọc cổng nối tiếp là việc chạm tới máy của bạn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t>resume</t>
+        </is>
+      </c>
+      <c r="B70" s="16" t="inlineStr">
+        <is>
+          <t>KHÔNG</t>
+        </is>
+      </c>
+      <c r="C70" s="12" t="inlineStr"/>
+      <c r="D70" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E70" s="10" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>rollback</t>
+        </is>
+      </c>
+      <c r="B71" s="16" t="inlineStr">
+        <is>
+          <t>KHÔNG</t>
+        </is>
+      </c>
+      <c r="C71" s="12" t="inlineStr"/>
+      <c r="D71" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E71" s="10" t="inlineStr">
+        <is>
+          <t>Quay lui đổi mã đang chạy trên thiết bị — quyết định của bạn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>scope-image</t>
+        </is>
+      </c>
+      <c r="B72" s="16" t="inlineStr">
+        <is>
+          <t>KHÔNG</t>
+        </is>
+      </c>
+      <c r="C72" s="12" t="inlineStr"/>
+      <c r="D72" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E72" s="10" t="inlineStr">
+        <is>
+          <t>Cần bạn đối chiếu ảnh gốc rồi chốt số đo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="inlineStr">
+        <is>
+          <t>telemetry</t>
+        </is>
+      </c>
+      <c r="B73" s="16" t="inlineStr">
+        <is>
+          <t>KHÔNG</t>
+        </is>
+      </c>
+      <c r="C73" s="12" t="inlineStr"/>
+      <c r="D73" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E73" s="10" t="inlineStr">
+        <is>
+          <t>Lệnh này chiếm cổng nối tiếp của thiết bị; bạn nên tự cắm và chạy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="inlineStr">
+        <is>
           <t>tune</t>
         </is>
       </c>
-      <c r="B69" s="16" t="inlineStr">
+      <c r="B74" s="16" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
       </c>
-      <c r="C69" s="14" t="inlineStr"/>
-      <c r="D69" s="14" t="inlineStr">
-        <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E69" s="10" t="inlineStr">
+      <c r="C74" s="12" t="inlineStr"/>
+      <c r="D74" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E74" s="10" t="inlineStr">
         <is>
           <t>Phong hạng hw-verified là một khẳng định về phần cứng. Nó chỉ được đặt bởi người vừa cầm thiết bị và đọc số đo.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E69"/>
+  <autoFilter ref="A1:E74"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/EAA_Bang_nang_luc.xlsx
+++ b/docs/EAA_Bang_nang_luc.xlsx
@@ -16,8 +16,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Năng lực nền'!$A$1:$G$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Năng lực nhúng'!$A$1:$G$87</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Khoảng trống'!$A$1:$F$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Bản đồ lệnh'!$A$1:$E$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Khoảng trống'!$A$1:$F$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Bản đồ lệnh'!$A$1:$E$78</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1472,24 +1472,20 @@
           <t>Đánh giá &amp; chọn công cụ: còn bảo trì, license, độ phổ biến, phụ thuộc hệ thống</t>
         </is>
       </c>
-      <c r="D21" s="13" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
         </is>
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>toolsearch đọc TRANG CÀI ĐẶT THẬT rồi mới đề xuất; ToolProposal.evidence ghi URL đã tải, và bản in nói rõ khi đề xuất chỉ dựa vào trí nhớ mô hình (SL-80)</t>
-        </is>
-      </c>
-      <c r="F21" s="10" t="inlineStr">
-        <is>
-          <t>Chưa tự đọc chỉ số bảo trì / license / độ phổ biến từ kho gói</t>
-        </is>
-      </c>
-      <c r="G21" s="15" t="inlineStr">
-        <is>
-          <t>Vừa</t>
+          <t>eaa/toolassess.py: đọc PyPI/npm/GitHub qua eaa/web.py — lần phát hành cuối, license, độ phổ biến, và TÊN CÓ THẬT KHÔNG (chống gõ nhầm một ký tự) · lệnh eaa assess · TC-75</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="inlineStr"/>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2189,24 +2185,20 @@
           <t>Nhận diện khi nào nên tự viết thay vì đi tìm</t>
         </is>
       </c>
-      <c r="D44" s="13" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
         </is>
       </c>
       <c r="E44" s="10" t="inlineStr">
         <is>
-          <t>`eaa tool propose` có sẵn và nằm trong danh mục Agent tự gọi</t>
-        </is>
-      </c>
-      <c r="F44" s="10" t="inlineStr">
-        <is>
-          <t>Agent chưa tự NHẬN RA lúc nào nên viết — vẫn cần người gợi ý</t>
-        </is>
-      </c>
-      <c r="G44" s="15" t="inlineStr">
-        <is>
-          <t>Vừa</t>
+          <t>eaa/suggest.py đọc nhật ký thật: lệnh Agent đòi mà không có, chuỗi đã lặp, công cụ hay hỏng → đề nghị viết công cụ hoặc rút kỹ năng, MỖI đề nghị kèm số · lệnh eaa suggest · TC-74</t>
+        </is>
+      </c>
+      <c r="F44" s="10" t="inlineStr"/>
+      <c r="G44" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2571,24 +2563,20 @@
           <t>Đánh giá chất lượng sau khi dùng thật (hay hỏng? chậm?)</t>
         </is>
       </c>
-      <c r="D56" s="13" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
+      <c r="D56" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
         </is>
       </c>
       <c r="E56" s="10" t="inlineStr">
         <is>
-          <t>kpi_log.csv đo vòng sinh mã; sổ tay lỗi đo tỉ lệ trúng từng CÁCH SỬA</t>
-        </is>
-      </c>
-      <c r="F56" s="10" t="inlineStr">
-        <is>
-          <t>Chưa đo độ tin cậy từng công cụ tự sinh sau khi dùng thật</t>
-        </is>
-      </c>
-      <c r="G56" s="15" t="inlineStr">
-        <is>
-          <t>Vừa</t>
+          <t>eaa/toolusage.py ghi mọi lần gọi công cụ tự sinh (đạt/hỏng/thời gian); eaa tool list hiện tỉ lệ và cảnh báo — nhưng KHÔNG tự gỡ cái nào · TC-74</t>
+        </is>
+      </c>
+      <c r="F56" s="10" t="inlineStr"/>
+      <c r="G56" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2775,7 @@
       </c>
       <c r="E63" s="10" t="inlineStr">
         <is>
-          <t>`eaa report kpi` + sổ tay lỗi + `eaa skill mine` đọc nhật ký thật và đề xuất rút chuỗi hay lặp thành kỹ năng</t>
+          <t>eaa suggest tự đề xuất 'nên viết công cụ mới cho việc này' từ nhật ký, không chờ người gợi ý · TC-74</t>
         </is>
       </c>
       <c r="F63" s="10" t="inlineStr"/>
@@ -2959,24 +2947,20 @@
           <t>Dùng được cho việc NHỎ mà không bắt đi hết vòng đời</t>
         </is>
       </c>
-      <c r="D70" s="13" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
+      <c r="D70" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
         </is>
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>`eaa scratch` sinh sẵn hồ sơ; 7 lệnh mới chạy không cần dự án; `eaa focus` nói rõ còn chặng nào</t>
-        </is>
-      </c>
-      <c r="F70" s="10" t="inlineStr">
-        <is>
-          <t>Vẫn phải `eaa init` trước khi vào `eaa chat`</t>
-        </is>
-      </c>
-      <c r="G70" s="15" t="inlineStr">
-        <is>
-          <t>Vừa</t>
+          <t>eaa scratch sinh sẵn hồ sơ VÀ khởi tạo luôn; eaa chat tự khởi tạo khi đang ở chỗ nháp; 10 lệnh chạy không cần dự án nào · TC-73</t>
+        </is>
+      </c>
+      <c r="F70" s="10" t="inlineStr"/>
+      <c r="G70" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3066,24 +3050,20 @@
           <t>Người dùng tự chọn cổng nào bật, cổng nào tắt</t>
         </is>
       </c>
-      <c r="D73" s="14" t="inlineStr">
-        <is>
-          <t>CHƯA</t>
+      <c r="D73" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
         </is>
       </c>
       <c r="E73" s="10" t="inlineStr">
         <is>
-          <t>Bộ cổng do pack.yaml khai, cố định cho cả pack</t>
-        </is>
-      </c>
-      <c r="F73" s="10" t="inlineStr">
-        <is>
-          <t>Cẩn trọng: cổng tắt được thì bất biến 'merge chỉ khi TOÀN BỘ passed' mất nghĩa. Nếu làm thì phải là 'chế độ nháp, không bao giờ merge được'</t>
-        </is>
-      </c>
-      <c r="G73" s="15" t="inlineStr">
-        <is>
-          <t>Vừa</t>
+          <t>eaa gen --draft chạy tập cổng nhẹ hơn. Bản nháp KHÔNG merge được DO CẤU TẠO: nó không ghi bằng chứng vào tệp đường merge đọc. Kèm bịt lỗ hổng phủ cổng của giấy phép merge (SL-87) · TC-73</t>
+        </is>
+      </c>
+      <c r="F73" s="10" t="inlineStr"/>
+      <c r="G73" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5274,9 +5254,9 @@
           <t>Chẩn đoán sâu bằng công cụ gỡ lỗi</t>
         </is>
       </c>
-      <c r="D66" s="14" t="inlineStr">
-        <is>
-          <t>CHƯA</t>
+      <c r="D66" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
         </is>
       </c>
       <c r="E66" s="12" t="inlineStr">
@@ -5286,7 +5266,8 @@
       </c>
       <c r="F66" s="10" t="inlineStr">
         <is>
-          <t>Ngoài phạm vi đề án (đã ghi từ trước).</t>
+          <t>eaa/debugsession.py + eaa debug plan/log/record · TC-75
+⚠ Đủ Ở ĐÚNG MỨC T0 — 'người làm, Agent ghi vết'. Agent dò mạch gỡ lỗi, dựng kế hoạch phiên từ tiêu chí kịch bản đã duyệt (mỗi bước khai trước hai nhánh kết luận), và ghi lại ai làm gì. Nó KHÔNG chạy phiên gỡ lỗi — việc ấy đòi mạch cắm vào bo thật và vẫn ngoài phạm vi đề án. Tên trình gỡ lỗi nằm ở packs/*/pack.yaml, không ở engine.</t>
         </is>
       </c>
       <c r="G66" s="10" t="inlineStr">
@@ -6008,7 +5989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -6052,14 +6033,14 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
-        <is>
-          <t>Vừa</t>
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Thấp</t>
         </is>
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>C10.1</t>
+          <t>C10.3</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
@@ -6069,7 +6050,7 @@
       </c>
       <c r="D2" s="10" t="inlineStr">
         <is>
-          <t>Dùng được cho việc NHỎ mà không bắt đi hết vòng đời</t>
+          <t>Chế độ không cần toolchain / không cần phần cứng</t>
         </is>
       </c>
       <c r="E2" s="13" t="inlineStr">
@@ -6079,19 +6060,19 @@
       </c>
       <c r="F2" s="10" t="inlineStr">
         <is>
-          <t>Vẫn phải `eaa init` trước khi vào `eaa chat`</t>
+          <t>Cổng compile/static vẫn đòi toolchain — đúng thiết kế cho bản bàn giao</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
-        <is>
-          <t>Vừa</t>
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Thấp</t>
         </is>
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>C10.4</t>
+          <t>C2.4</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
@@ -6101,135 +6082,135 @@
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>Người dùng tự chọn cổng nào bật, cổng nào tắt</t>
-        </is>
-      </c>
-      <c r="E3" s="14" t="inlineStr">
+          <t>Dò runtime: python --version, pip list, npm ls, which, docker ps</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>MỘT PHẦN</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>Vẫn chưa liệt kê được gói đã cài (pip list / npm ls)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Thấp</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>C2.9</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>nền</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Phát hiện xung đột phụ thuộc</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>CHƯA</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t>Cẩn trọng: cổng tắt được thì bất biến 'merge chỉ khi TOÀN BỘ passed' mất nghĩa. Nếu làm thì phải là 'chế độ nháp, không bao giờ merge được'</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="15" t="inlineStr">
-        <is>
-          <t>Vừa</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>C3.3</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>Chưa gặp vấn đề thật vì công cụ nhúng là binary độc lập, ít phụ thuộc chéo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Thấp</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>C4.1</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>nền</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>Đánh giá &amp; chọn công cụ: còn bảo trì, license, độ phổ biến, phụ thuộc hệ thống</t>
-        </is>
-      </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>Chọn cơ chế cài phù hợp</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>MỘT PHẦN</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t>Chưa tự đọc chỉ số bảo trì / license / độ phổ biến từ kho gói</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="15" t="inlineStr">
-        <is>
-          <t>Vừa</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>C6.1</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>Không build từ nguồn, không chạy container. Đủ cho toolchain nhúng phổ biến, thiếu cho công cụ lạ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Thấp</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>C4.2</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>nền</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
-        <is>
-          <t>Nhận diện khi nào nên tự viết thay vì đi tìm</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>Cô lập môi trường (venv riêng cho tool mới)</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>MỘT PHẦN</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
-        <is>
-          <t>Agent chưa tự NHẬN RA lúc nào nên viết — vẫn cần người gợi ý</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>Vừa</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>C7.4</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có venv riêng cho công cụ NGOÀI (avr-gcc, cppcheck…)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Thấp</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>C4.3</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>nền</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>Đánh giá chất lượng sau khi dùng thật (hay hỏng? chậm?)</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
-        </is>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>Chưa đo độ tin cậy từng công cụ tự sinh sau khi dùng thật</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>Vừa</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>N-085</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>nhúng</t>
-        </is>
-      </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Chẩn đoán sâu bằng công cụ gỡ lỗi</t>
+          <t>Cài theo thứ tự phụ thuộc (system lib trước, runtime package sau)</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -6239,7 +6220,7 @@
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
-          <t>Ngoài phạm vi đề án (đã ghi từ trước).</t>
+          <t>Hiện mỗi Tool Card độc lập, không khai phụ thuộc lẫn nhau</t>
         </is>
       </c>
     </row>
@@ -6251,7 +6232,7 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>C10.3</t>
+          <t>C5.6</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -6261,7 +6242,7 @@
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>Chế độ không cần toolchain / không cần phần cứng</t>
+          <t>Tự viết giải pháp tối thiểu thay thế</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
@@ -6271,7 +6252,7 @@
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>Cổng compile/static vẫn đòi toolchain — đúng thiết kế cho bản bàn giao</t>
+          <t>Chưa nối tự động vào thang gỡ lỗi cài đặt</t>
         </is>
       </c>
     </row>
@@ -6283,7 +6264,7 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>C2.4</t>
+          <t>C6.8</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
@@ -6293,7 +6274,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>Dò runtime: python --version, pip list, npm ls, which, docker ps</t>
+          <t>Tài liệu hoá tool mới: README ngắn, ví dụ, giới hạn đã biết</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
@@ -6303,7 +6284,7 @@
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
-          <t>Vẫn chưa liệt kê được gói đã cài (pip list / npm ls)</t>
+          <t>Chưa sinh README riêng cho từng công cụ</t>
         </is>
       </c>
     </row>
@@ -6315,7 +6296,7 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>C2.9</t>
+          <t>C7.3</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -6325,214 +6306,22 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>Phát hiện xung đột phụ thuộc</t>
-        </is>
-      </c>
-      <c r="E10" s="14" t="inlineStr">
-        <is>
-          <t>CHƯA</t>
+          <t>Versioning tool, giữ bản cũ nếu bản mới hỏng</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>MỘT PHẦN</t>
         </is>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
-          <t>Chưa gặp vấn đề thật vì công cụ nhúng là binary độc lập, ít phụ thuộc chéo</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>Thấp</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>C4.1</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>nền</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>Chọn cơ chế cài phù hợp</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
-        </is>
-      </c>
-      <c r="F11" s="10" t="inlineStr">
-        <is>
-          <t>Không build từ nguồn, không chạy container. Đủ cho toolchain nhúng phổ biến, thiếu cho công cụ lạ</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>Thấp</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>C4.2</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>nền</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>Cô lập môi trường (venv riêng cho tool mới)</t>
-        </is>
-      </c>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
-        </is>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>Chưa có venv riêng cho công cụ NGOÀI (avr-gcc, cppcheck…)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>Thấp</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>C4.3</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>nền</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>Cài theo thứ tự phụ thuộc (system lib trước, runtime package sau)</t>
-        </is>
-      </c>
-      <c r="E13" s="14" t="inlineStr">
-        <is>
-          <t>CHƯA</t>
-        </is>
-      </c>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t>Hiện mỗi Tool Card độc lập, không khai phụ thuộc lẫn nhau</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>Thấp</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>C5.6</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>nền</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>Tự viết giải pháp tối thiểu thay thế</t>
-        </is>
-      </c>
-      <c r="E14" s="13" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>Chưa nối tự động vào thang gỡ lỗi cài đặt</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>Thấp</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>C6.8</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>nền</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>Tài liệu hoá tool mới: README ngắn, ví dụ, giới hạn đã biết</t>
-        </is>
-      </c>
-      <c r="E15" s="13" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
-        </is>
-      </c>
-      <c r="F15" s="10" t="inlineStr">
-        <is>
-          <t>Chưa sinh README riêng cho từng công cụ</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>Thấp</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>C7.3</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>nền</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>Versioning tool, giữ bản cũ nếu bản mới hỏng</t>
-        </is>
-      </c>
-      <c r="E16" s="13" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
-        <is>
           <t>Không giữ song song hai bản để quay lui</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F16"/>
+  <autoFilter ref="A1:F10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6543,7 +6332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E74"/>
+  <dimension ref="A1:E78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6583,7 +6372,7 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>budget propose</t>
+          <t>assess</t>
         </is>
       </c>
       <c r="B2" s="11" t="inlineStr">
@@ -6593,12 +6382,12 @@
       </c>
       <c r="C2" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D2" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E2" s="10" t="inlineStr"/>
@@ -6606,7 +6395,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>budget show</t>
+          <t>budget propose</t>
         </is>
       </c>
       <c r="B3" s="11" t="inlineStr">
@@ -6616,7 +6405,7 @@
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>có</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
@@ -6629,7 +6418,7 @@
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>budget tokens</t>
+          <t>budget show</t>
         </is>
       </c>
       <c r="B4" s="11" t="inlineStr">
@@ -6652,7 +6441,7 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>capabilities</t>
+          <t>budget tokens</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
@@ -6675,7 +6464,7 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>datasheet list</t>
+          <t>capabilities</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
@@ -6698,7 +6487,7 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>deviations</t>
+          <t>datasheet list</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
@@ -6713,7 +6502,7 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E7" s="10" t="inlineStr"/>
@@ -6721,7 +6510,7 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>diagnose list</t>
+          <t>debug log</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
@@ -6736,7 +6525,7 @@
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr"/>
@@ -6744,7 +6533,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>diagnose measure</t>
+          <t>debug plan</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
@@ -6759,7 +6548,7 @@
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E9" s="10" t="inlineStr"/>
@@ -6767,7 +6556,7 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>diagnose select</t>
+          <t>deviations</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
@@ -6782,7 +6571,7 @@
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr"/>
@@ -6790,7 +6579,7 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>docs list</t>
+          <t>diagnose list</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
@@ -6813,7 +6602,7 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>environ</t>
+          <t>diagnose measure</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
@@ -6828,7 +6617,7 @@
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr"/>
@@ -6836,7 +6625,7 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>errata lookup</t>
+          <t>diagnose select</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
@@ -6846,7 +6635,7 @@
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -6859,7 +6648,7 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>errata show</t>
+          <t>docs list</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
@@ -6882,7 +6671,7 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>field</t>
+          <t>environ</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
@@ -6897,7 +6686,7 @@
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr"/>
@@ -6905,7 +6694,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>focus</t>
+          <t>errata lookup</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
@@ -6915,7 +6704,7 @@
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>có</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
@@ -6928,7 +6717,7 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>gate show</t>
+          <t>errata show</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
@@ -6951,7 +6740,7 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>handover doc</t>
+          <t>field</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
@@ -6974,7 +6763,7 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>handover rollout</t>
+          <t>focus</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
@@ -6997,7 +6786,7 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>handover swap</t>
+          <t>gate show</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
@@ -7020,7 +6809,7 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>interface</t>
+          <t>handover doc</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
@@ -7030,7 +6819,7 @@
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -7043,7 +6832,7 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>ledger list</t>
+          <t>handover rollout</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
@@ -7066,7 +6855,7 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>memory add</t>
+          <t>handover swap</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
@@ -7076,12 +6865,12 @@
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr"/>
@@ -7089,7 +6878,7 @@
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>memory list</t>
+          <t>interface</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
@@ -7099,12 +6888,12 @@
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>có</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr"/>
@@ -7112,7 +6901,7 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>ledger list</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
@@ -7127,7 +6916,7 @@
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E25" s="10" t="inlineStr"/>
@@ -7135,7 +6924,7 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>plan add</t>
+          <t>memory add</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
@@ -7150,7 +6939,7 @@
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr"/>
@@ -7158,7 +6947,7 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>plan list</t>
+          <t>memory list</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
@@ -7173,7 +6962,7 @@
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr"/>
@@ -7181,7 +6970,7 @@
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>playbook list</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
@@ -7204,7 +6993,7 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>playbook lookup</t>
+          <t>plan add</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
@@ -7214,12 +7003,12 @@
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>có</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E29" s="10" t="inlineStr"/>
@@ -7227,7 +7016,7 @@
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>playbook record</t>
+          <t>plan list</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
@@ -7237,12 +7026,12 @@
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr"/>
@@ -7250,7 +7039,7 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>policy</t>
+          <t>playbook list</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
@@ -7273,7 +7062,7 @@
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>propose acceptance</t>
+          <t>playbook lookup</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
@@ -7288,7 +7077,7 @@
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr"/>
@@ -7296,7 +7085,7 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>propose constraints</t>
+          <t>playbook record</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
@@ -7306,12 +7095,12 @@
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>có</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr"/>
@@ -7319,7 +7108,7 @@
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>propose pinmap</t>
+          <t>policy</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
@@ -7334,7 +7123,7 @@
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr"/>
@@ -7342,7 +7131,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>propose plant</t>
+          <t>propose acceptance</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
@@ -7365,7 +7154,7 @@
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>propose scope</t>
+          <t>propose constraints</t>
         </is>
       </c>
       <c r="B36" s="11" t="inlineStr">
@@ -7375,7 +7164,7 @@
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
@@ -7388,7 +7177,7 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>propose pinmap</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
@@ -7403,7 +7192,7 @@
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E37" s="10" t="inlineStr"/>
@@ -7411,7 +7200,7 @@
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>report kpi</t>
+          <t>propose plant</t>
         </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
@@ -7434,7 +7223,7 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>report retrieval</t>
+          <t>propose scope</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
@@ -7444,7 +7233,7 @@
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>có</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
@@ -7457,7 +7246,7 @@
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>report review</t>
+          <t>read</t>
         </is>
       </c>
       <c r="B40" s="11" t="inlineStr">
@@ -7472,7 +7261,7 @@
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr"/>
@@ -7480,7 +7269,7 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>report versions</t>
+          <t>report kpi</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
@@ -7503,7 +7292,7 @@
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>report retrieval</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
@@ -7518,7 +7307,7 @@
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E42" s="10" t="inlineStr"/>
@@ -7526,7 +7315,7 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>resolve</t>
+          <t>report review</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
@@ -7549,7 +7338,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>safety propose</t>
+          <t>report versions</t>
         </is>
       </c>
       <c r="B44" s="11" t="inlineStr">
@@ -7559,7 +7348,7 @@
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
@@ -7572,7 +7361,7 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>safety show</t>
+          <t>research</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
@@ -7587,7 +7376,7 @@
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E45" s="10" t="inlineStr"/>
@@ -7595,7 +7384,7 @@
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>scratch</t>
+          <t>resolve</t>
         </is>
       </c>
       <c r="B46" s="11" t="inlineStr">
@@ -7605,12 +7394,12 @@
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E46" s="10" t="inlineStr"/>
@@ -7618,7 +7407,7 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>sim run</t>
+          <t>safety propose</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
@@ -7628,7 +7417,7 @@
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>có</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
@@ -7641,7 +7430,7 @@
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>skill list</t>
+          <t>safety show</t>
         </is>
       </c>
       <c r="B48" s="11" t="inlineStr">
@@ -7656,7 +7445,7 @@
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E48" s="10" t="inlineStr"/>
@@ -7664,7 +7453,7 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>skill mine</t>
+          <t>scratch</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
@@ -7674,7 +7463,7 @@
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>có</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
@@ -7687,7 +7476,7 @@
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>skill run</t>
+          <t>sim run</t>
         </is>
       </c>
       <c r="B50" s="11" t="inlineStr">
@@ -7697,12 +7486,12 @@
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E50" s="10" t="inlineStr"/>
@@ -7710,7 +7499,7 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>skill verify</t>
+          <t>skill list</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
@@ -7720,7 +7509,7 @@
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
@@ -7733,7 +7522,7 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>sources need</t>
+          <t>skill mine</t>
         </is>
       </c>
       <c r="B52" s="11" t="inlineStr">
@@ -7748,7 +7537,7 @@
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E52" s="10" t="inlineStr"/>
@@ -7756,7 +7545,7 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>sources pages</t>
+          <t>skill run</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
@@ -7766,12 +7555,12 @@
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>có</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E53" s="10" t="inlineStr"/>
@@ -7779,7 +7568,7 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>skill verify</t>
         </is>
       </c>
       <c r="B54" s="11" t="inlineStr">
@@ -7789,7 +7578,7 @@
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>có</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
@@ -7802,7 +7591,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>survey</t>
+          <t>sources need</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
@@ -7825,7 +7614,7 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>tool list</t>
+          <t>sources pages</t>
         </is>
       </c>
       <c r="B56" s="11" t="inlineStr">
@@ -7840,7 +7629,7 @@
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E56" s="10" t="inlineStr"/>
@@ -7848,7 +7637,7 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>tool propose</t>
+          <t>status</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
@@ -7858,7 +7647,7 @@
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
@@ -7871,7 +7660,7 @@
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>tool run</t>
+          <t>suggest</t>
         </is>
       </c>
       <c r="B58" s="11" t="inlineStr">
@@ -7881,12 +7670,12 @@
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E58" s="10" t="inlineStr"/>
@@ -7894,7 +7683,7 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>tool verify</t>
+          <t>survey</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
@@ -7904,12 +7693,12 @@
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E59" s="10" t="inlineStr"/>
@@ -7917,64 +7706,68 @@
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>brief</t>
-        </is>
-      </c>
-      <c r="B60" s="16" t="inlineStr">
-        <is>
-          <t>KHÔNG</t>
-        </is>
-      </c>
-      <c r="C60" s="12" t="inlineStr"/>
+          <t>tool list</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C60" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E60" s="10" t="inlineStr">
-        <is>
-          <t>Lệnh này hỏi bạn trực tiếp — tôi gọi hộ thì mất đúng phần hỏi.</t>
-        </is>
-      </c>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E60" s="10" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>build</t>
-        </is>
-      </c>
-      <c r="B61" s="16" t="inlineStr">
-        <is>
-          <t>KHÔNG</t>
-        </is>
-      </c>
-      <c r="C61" s="12" t="inlineStr"/>
+          <t>tool propose</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C61" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E61" s="10" t="inlineStr">
-        <is>
-          <t>Ráp firmware là bước trước khi nạp; bạn chạy để còn kiểm ảnh sinh ra.</t>
-        </is>
-      </c>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E61" s="10" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>chat</t>
-        </is>
-      </c>
-      <c r="B62" s="16" t="inlineStr">
-        <is>
-          <t>KHÔNG</t>
-        </is>
-      </c>
-      <c r="C62" s="12" t="inlineStr"/>
+          <t>tool run</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C62" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E62" s="10" t="inlineStr"/>
@@ -7982,30 +7775,30 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>decide</t>
-        </is>
-      </c>
-      <c r="B63" s="16" t="inlineStr">
-        <is>
-          <t>KHÔNG</t>
-        </is>
-      </c>
-      <c r="C63" s="12" t="inlineStr"/>
+          <t>tool verify</t>
+        </is>
+      </c>
+      <c r="B63" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C63" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E63" s="10" t="inlineStr">
-        <is>
-          <t>Trình phương án để BẠN chọn; tôi gọi hộ thì mất đúng chỗ bạn chọn.</t>
-        </is>
-      </c>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E63" s="10" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>doctor</t>
+          <t>brief</t>
         </is>
       </c>
       <c r="B64" s="16" t="inlineStr">
@@ -8021,14 +7814,14 @@
       </c>
       <c r="E64" s="10" t="inlineStr">
         <is>
-          <t>Cài đặt công cụ đổi máy của bạn. Tôi quét và báo được ('doctor' không cờ là chỉ đọc), nhưng '--fix' phải do bạn chạy và xác nhận từng lệnh.</t>
+          <t>Lệnh này hỏi bạn trực tiếp — tôi gọi hộ thì mất đúng phần hỏi.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>endurance</t>
+          <t>build</t>
         </is>
       </c>
       <c r="B65" s="16" t="inlineStr">
@@ -8044,14 +7837,14 @@
       </c>
       <c r="E65" s="10" t="inlineStr">
         <is>
-          <t>Lệnh này chiếm cổng nối tiếp và chạy hàng giờ; bạn nên tự bố trí.</t>
+          <t>Ráp firmware là bước trước khi nạp; bạn chạy để còn kiểm ảnh sinh ra.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>flash</t>
+          <t>chat</t>
         </is>
       </c>
       <c r="B66" s="16" t="inlineStr">
@@ -8065,16 +7858,12 @@
           <t>có</t>
         </is>
       </c>
-      <c r="E66" s="10" t="inlineStr">
-        <is>
-          <t>Nạp firmware chạm vào thiết bị thật. Luôn cần chính bạn xác nhận — một phiên không có người không được diễn giải thành một người đã đồng ý.</t>
-        </is>
-      </c>
+      <c r="E66" s="10" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>gen</t>
+          <t>decide</t>
         </is>
       </c>
       <c r="B67" s="16" t="inlineStr">
@@ -8090,14 +7879,14 @@
       </c>
       <c r="E67" s="10" t="inlineStr">
         <is>
-          <t>Vòng sinh mã ghi số liệu vào kpi_log.csv, và những dòng ấy là DỮ LIỆU THÍ NGHIỆM của Chương 3. Tôi tự khởi động nó sẽ chèn vào bảng số liệu những lượt chạy mà người làm thí nghiệm không định chạy — nên bạn là người bấm nút.</t>
+          <t>Trình phương án để BẠN chọn; tôi gọi hộ thì mất đúng chỗ bạn chọn.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>init</t>
+          <t>doctor</t>
         </is>
       </c>
       <c r="B68" s="16" t="inlineStr">
@@ -8113,14 +7902,14 @@
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>Khởi tạo dự án là quyết định mở đầu, không nên nằm giữa một câu hỏi.</t>
+          <t>Cài đặt công cụ đổi máy của bạn. Tôi quét và báo được ('doctor' không cờ là chỉ đọc), nhưng '--fix' phải do bạn chạy và xác nhận từng lệnh.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>ports</t>
+          <t>endurance</t>
         </is>
       </c>
       <c r="B69" s="16" t="inlineStr">
@@ -8136,14 +7925,14 @@
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
-          <t>Đọc cổng nối tiếp là việc chạm tới máy của bạn.</t>
+          <t>Lệnh này chiếm cổng nối tiếp và chạy hàng giờ; bạn nên tự bố trí.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>resume</t>
+          <t>flash</t>
         </is>
       </c>
       <c r="B70" s="16" t="inlineStr">
@@ -8157,12 +7946,16 @@
           <t>có</t>
         </is>
       </c>
-      <c r="E70" s="10" t="inlineStr"/>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>Nạp firmware chạm vào thiết bị thật. Luôn cần chính bạn xác nhận — một phiên không có người không được diễn giải thành một người đã đồng ý.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>rollback</t>
+          <t>gen</t>
         </is>
       </c>
       <c r="B71" s="16" t="inlineStr">
@@ -8178,14 +7971,14 @@
       </c>
       <c r="E71" s="10" t="inlineStr">
         <is>
-          <t>Quay lui đổi mã đang chạy trên thiết bị — quyết định của bạn.</t>
+          <t>Vòng sinh mã ghi số liệu vào kpi_log.csv, và những dòng ấy là DỮ LIỆU THÍ NGHIỆM của Chương 3. Tôi tự khởi động nó sẽ chèn vào bảng số liệu những lượt chạy mà người làm thí nghiệm không định chạy — nên bạn là người bấm nút.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>scope-image</t>
+          <t>init</t>
         </is>
       </c>
       <c r="B72" s="16" t="inlineStr">
@@ -8201,14 +7994,14 @@
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>Cần bạn đối chiếu ảnh gốc rồi chốt số đo.</t>
+          <t>Khởi tạo dự án là quyết định mở đầu, không nên nằm giữa một câu hỏi.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>telemetry</t>
+          <t>ports</t>
         </is>
       </c>
       <c r="B73" s="16" t="inlineStr">
@@ -8224,14 +8017,14 @@
       </c>
       <c r="E73" s="10" t="inlineStr">
         <is>
-          <t>Lệnh này chiếm cổng nối tiếp của thiết bị; bạn nên tự cắm và chạy.</t>
+          <t>Đọc cổng nối tiếp là việc chạm tới máy của bạn.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>tune</t>
+          <t>resume</t>
         </is>
       </c>
       <c r="B74" s="16" t="inlineStr">
@@ -8245,14 +8038,102 @@
           <t>có</t>
         </is>
       </c>
-      <c r="E74" s="10" t="inlineStr">
+      <c r="E74" s="10" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>rollback</t>
+        </is>
+      </c>
+      <c r="B75" s="16" t="inlineStr">
+        <is>
+          <t>KHÔNG</t>
+        </is>
+      </c>
+      <c r="C75" s="12" t="inlineStr"/>
+      <c r="D75" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E75" s="10" t="inlineStr">
+        <is>
+          <t>Quay lui đổi mã đang chạy trên thiết bị — quyết định của bạn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="inlineStr">
+        <is>
+          <t>scope-image</t>
+        </is>
+      </c>
+      <c r="B76" s="16" t="inlineStr">
+        <is>
+          <t>KHÔNG</t>
+        </is>
+      </c>
+      <c r="C76" s="12" t="inlineStr"/>
+      <c r="D76" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E76" s="10" t="inlineStr">
+        <is>
+          <t>Cần bạn đối chiếu ảnh gốc rồi chốt số đo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>telemetry</t>
+        </is>
+      </c>
+      <c r="B77" s="16" t="inlineStr">
+        <is>
+          <t>KHÔNG</t>
+        </is>
+      </c>
+      <c r="C77" s="12" t="inlineStr"/>
+      <c r="D77" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E77" s="10" t="inlineStr">
+        <is>
+          <t>Lệnh này chiếm cổng nối tiếp của thiết bị; bạn nên tự cắm và chạy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="10" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="B78" s="16" t="inlineStr">
+        <is>
+          <t>KHÔNG</t>
+        </is>
+      </c>
+      <c r="C78" s="12" t="inlineStr"/>
+      <c r="D78" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E78" s="10" t="inlineStr">
         <is>
           <t>Phong hạng hw-verified là một khẳng định về phần cứng. Nó chỉ được đặt bởi người vừa cầm thiết bị và đọc số đo.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E74"/>
+  <autoFilter ref="A1:E78"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/EAA_Bang_nang_luc.xlsx
+++ b/docs/EAA_Bang_nang_luc.xlsx
@@ -16,8 +16,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Năng lực nền'!$A$1:$G$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Năng lực nhúng'!$A$1:$G$87</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Khoảng trống'!$A$1:$F$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Bản đồ lệnh'!$A$1:$E$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Khoảng trống'!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Bản đồ lệnh'!$A$1:$E$80</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -119,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -153,12 +153,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1181,24 +1175,20 @@
           <t>Dò runtime: python --version, pip list, npm ls, which, docker ps</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>doctor chạy argv `check` từng công cụ; `eaa environ` liệt kê trình quản lý gói có mặt</t>
-        </is>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>Vẫn chưa liệt kê được gói đã cài (pip list / npm ls)</t>
-        </is>
-      </c>
+          <t>eaa environ --packages liệt kê gói Python/npm đã cài — 'máy này sẵn có gì', khác với 'công cụ trong Tool Card đã cài chưa' của doctor · TC-77</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr"/>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>Thấp</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1358,24 +1348,20 @@
           <t>Phát hiện xung đột phụ thuộc</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
-        <is>
-          <t>CHƯA</t>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
         </is>
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="10" t="inlineStr">
-        <is>
-          <t>Chưa gặp vấn đề thật vì công cụ nhúng là binary độc lập, ít phụ thuộc chéo</t>
-        </is>
-      </c>
+          <t>eaa/installplan.py find_conflicts(): hai thẻ cùng đòi một thứ ở hai ràng buộc loại trừ nhau thì CHẶN cả kế hoạch cài. Chỉ báo khi CHẮC CHẮN đá nhau · eaa doctor --plan · TC-76</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr"/>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>Thấp</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1506,7 @@
           <t>Chưa chống typosquatting theo TÊN GÓI (avr-gcc vs avrgcc). Bù lại: mọi đề xuất đều phải qua người duyệt tại gate</t>
         </is>
       </c>
-      <c r="G22" s="15" t="inlineStr">
+      <c r="G22" s="13" t="inlineStr">
         <is>
           <t>Vừa</t>
         </is>
@@ -1615,24 +1601,20 @@
           <t>Chọn cơ chế cài phù hợp</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>Trình quản lý gói (apt / brew / choco / winget) và tải trực tiếp kèm checksum</t>
-        </is>
-      </c>
-      <c r="F26" s="10" t="inlineStr">
-        <is>
-          <t>Không build từ nguồn, không chạy container. Đủ cho toolchain nhúng phổ biến, thiếu cho công cụ lạ</t>
-        </is>
-      </c>
+          <t>Tool Card khai method: gói / nhị phân / nguồn / container / môi trường riêng; mỗi cách kèm lời giải thích nó hỏng kiểu gì. Nhị phân thiếu checksum thì cảnh báo · TC-76</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr"/>
       <c r="G26" s="12" t="inlineStr">
         <is>
-          <t>Thấp</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1652,24 +1634,20 @@
           <t>Cô lập môi trường (venv riêng cho tool mới)</t>
         </is>
       </c>
-      <c r="D27" s="13" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>Cổng chạy thử của xưởng công cụ chạy trong thư mục tạm riêng, tiến trình riêng, không mạng, không khóa API</t>
-        </is>
-      </c>
-      <c r="F27" s="10" t="inlineStr">
-        <is>
-          <t>Chưa có venv riêng cho công cụ NGOÀI (avr-gcc, cppcheck…)</t>
-        </is>
-      </c>
+          <t>method 'môi trường riêng' cho công cụ ngoài; cổng chạy thử của xưởng công cụ vốn đã chạy trong thư mục tạm riêng, không mạng, không khoá API</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="inlineStr"/>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>Thấp</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1689,24 +1667,20 @@
           <t>Cài theo thứ tự phụ thuộc (system lib trước, runtime package sau)</t>
         </is>
       </c>
-      <c r="D28" s="14" t="inlineStr">
-        <is>
-          <t>CHƯA</t>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F28" s="10" t="inlineStr">
-        <is>
-          <t>Hiện mỗi Tool Card độc lập, không khai phụ thuộc lẫn nhau</t>
-        </is>
-      </c>
+          <t>Tool Card khai requires; plan_installs() sắp xếp tô-pô ỔN ĐỊNH, bắt phụ thuộc vòng, và NÊU RA phụ thuộc trỏ ngoài manifest thay vì nuốt · TC-76</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr"/>
       <c r="G28" s="12" t="inlineStr">
         <is>
-          <t>Thấp</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1792,7 +1766,7 @@
           <t>Agent TỰ chạy lệnh cài</t>
         </is>
       </c>
-      <c r="D31" s="16" t="inlineStr">
+      <c r="D31" s="14" t="inlineStr">
         <is>
           <t>CỐ Ý KHÔNG</t>
         </is>
@@ -2001,24 +1975,20 @@
           <t>Tự viết giải pháp tối thiểu thay thế</t>
         </is>
       </c>
-      <c r="D38" s="13" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
         </is>
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
-          <t>eaa/toolforge.py viết được một công cụ thay thế tối thiểu</t>
-        </is>
-      </c>
-      <c r="F38" s="10" t="inlineStr">
-        <is>
-          <t>Chưa nối tự động vào thang gỡ lỗi cài đặt</t>
-        </is>
-      </c>
+          <t>Thang gỡ lỗi cài đặt có bậc áp chót 'tự viết một thứ tối thiểu thay thế', đặt SAU mọi bậc cài thật · TC-77</t>
+        </is>
+      </c>
+      <c r="F38" s="10" t="inlineStr"/>
       <c r="G38" s="12" t="inlineStr">
         <is>
-          <t>Thấp</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2416,24 +2386,20 @@
           <t>Tài liệu hoá tool mới: README ngắn, ví dụ, giới hạn đã biết</t>
         </is>
       </c>
-      <c r="D51" s="13" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
         </is>
       </c>
       <c r="E51" s="10" t="inlineStr">
         <is>
-          <t>MO_TA + SCHEMA + purpose hiện trong `eaa tool list` và trong prompt của Agent</t>
-        </is>
-      </c>
-      <c r="F51" s="10" t="inlineStr">
-        <is>
-          <t>Chưa sinh README riêng cho từng công cụ</t>
-        </is>
-      </c>
+          <t>eaa tool doc sinh tài liệu TỪ MÃ (MO_TA, SCHEMA, hàm test_) cộng số đo dùng thật — không hỏi mô hình, vì tài liệu lệch khỏi mã tệ hơn không có tài liệu · TC-77</t>
+        </is>
+      </c>
+      <c r="F51" s="10" t="inlineStr"/>
       <c r="G51" s="12" t="inlineStr">
         <is>
-          <t>Thấp</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2526,24 +2492,20 @@
           <t>Versioning tool, giữ bản cũ nếu bản mới hỏng</t>
         </is>
       </c>
-      <c r="D55" s="13" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
         </is>
       </c>
       <c r="E55" s="10" t="inlineStr">
         <is>
-          <t>env.lock ghim phiên bản; `eaa report versions` đối chiếu</t>
-        </is>
-      </c>
-      <c r="F55" s="10" t="inlineStr">
-        <is>
-          <t>Không giữ song song hai bản để quay lui</t>
-        </is>
-      </c>
+          <t>Mỗi lần ghi đè một bản ĐÃ DUYỆT thì cất bản cũ; eaa tool rollback quay về, và bản quay về phải đi lại ba cổng · TC-77</t>
+        </is>
+      </c>
+      <c r="F55" s="10" t="inlineStr"/>
       <c r="G55" s="12" t="inlineStr">
         <is>
-          <t>Thấp</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3013,24 +2975,20 @@
           <t>Chế độ không cần toolchain / không cần phần cứng</t>
         </is>
       </c>
-      <c r="D72" s="13" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
+      <c r="D72" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
         </is>
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>Mô phỏng + MockLLM chạy không cần bo; `eaa scratch` nói rõ ràng buộc là GIẢ ĐỊNH</t>
-        </is>
-      </c>
-      <c r="F72" s="10" t="inlineStr">
-        <is>
-          <t>Cổng compile/static vẫn đòi toolchain — đúng thiết kế cho bản bàn giao</t>
-        </is>
-      </c>
+          <t>eaa gen --preview sinh mã rồi DỪNG: không cổng, không nhánh, không commit. An toàn hơn cả chế độ nháp, và nới đúng một tiền điều kiện (pha) · TC-77</t>
+        </is>
+      </c>
+      <c r="F72" s="10" t="inlineStr"/>
       <c r="G72" s="12" t="inlineStr">
         <is>
-          <t>Thấp</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -4796,7 +4754,7 @@
           <t>Chạy chính mã C sinh ra trong mô phỏng</t>
         </is>
       </c>
-      <c r="D52" s="16" t="inlineStr">
+      <c r="D52" s="14" t="inlineStr">
         <is>
           <t>CỐ Ý KHÔNG</t>
         </is>
@@ -5989,7 +5947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -6032,296 +5990,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="12" t="inlineStr">
-        <is>
-          <t>Thấp</t>
-        </is>
-      </c>
-      <c r="B2" s="10" t="inlineStr">
-        <is>
-          <t>C10.3</t>
-        </is>
-      </c>
-      <c r="C2" s="10" t="inlineStr">
-        <is>
-          <t>nền</t>
-        </is>
-      </c>
-      <c r="D2" s="10" t="inlineStr">
-        <is>
-          <t>Chế độ không cần toolchain / không cần phần cứng</t>
-        </is>
-      </c>
-      <c r="E2" s="13" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
-        </is>
-      </c>
-      <c r="F2" s="10" t="inlineStr">
-        <is>
-          <t>Cổng compile/static vẫn đòi toolchain — đúng thiết kế cho bản bàn giao</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>Thấp</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>C2.4</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
-        <is>
-          <t>nền</t>
-        </is>
-      </c>
-      <c r="D3" s="10" t="inlineStr">
-        <is>
-          <t>Dò runtime: python --version, pip list, npm ls, which, docker ps</t>
-        </is>
-      </c>
-      <c r="E3" s="13" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
-        </is>
-      </c>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t>Vẫn chưa liệt kê được gói đã cài (pip list / npm ls)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>Thấp</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>C2.9</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>nền</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>Phát hiện xung đột phụ thuộc</t>
-        </is>
-      </c>
-      <c r="E4" s="14" t="inlineStr">
-        <is>
-          <t>CHƯA</t>
-        </is>
-      </c>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t>Chưa gặp vấn đề thật vì công cụ nhúng là binary độc lập, ít phụ thuộc chéo</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>Thấp</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>C4.1</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>nền</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="inlineStr">
-        <is>
-          <t>Chọn cơ chế cài phù hợp</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
-        </is>
-      </c>
-      <c r="F5" s="10" t="inlineStr">
-        <is>
-          <t>Không build từ nguồn, không chạy container. Đủ cho toolchain nhúng phổ biến, thiếu cho công cụ lạ</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Thấp</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>C4.2</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>nền</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>Cô lập môi trường (venv riêng cho tool mới)</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
-        </is>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>Chưa có venv riêng cho công cụ NGOÀI (avr-gcc, cppcheck…)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>Thấp</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>C4.3</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>nền</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>Cài theo thứ tự phụ thuộc (system lib trước, runtime package sau)</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>CHƯA</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>Hiện mỗi Tool Card độc lập, không khai phụ thuộc lẫn nhau</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Thấp</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>C5.6</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>nền</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>Tự viết giải pháp tối thiểu thay thế</t>
-        </is>
-      </c>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>Chưa nối tự động vào thang gỡ lỗi cài đặt</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>Thấp</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>C6.8</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>nền</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>Tài liệu hoá tool mới: README ngắn, ví dụ, giới hạn đã biết</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
-        </is>
-      </c>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t>Chưa sinh README riêng cho từng công cụ</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>Thấp</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>C7.3</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>nền</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>Versioning tool, giữ bản cũ nếu bản mới hỏng</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
-        </is>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t>Không giữ song song hai bản để quay lui</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F10"/>
+  <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6332,7 +6002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E78"/>
+  <dimension ref="A1:E80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7706,7 +7376,7 @@
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>tool list</t>
+          <t>tool doc</t>
         </is>
       </c>
       <c r="B60" s="11" t="inlineStr">
@@ -7729,7 +7399,7 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>tool propose</t>
+          <t>tool list</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
@@ -7739,7 +7409,7 @@
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
@@ -7752,7 +7422,7 @@
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>tool run</t>
+          <t>tool propose</t>
         </is>
       </c>
       <c r="B62" s="11" t="inlineStr">
@@ -7775,7 +7445,7 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>tool verify</t>
+          <t>tool rollback</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
@@ -7798,56 +7468,56 @@
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>brief</t>
-        </is>
-      </c>
-      <c r="B64" s="16" t="inlineStr">
-        <is>
-          <t>KHÔNG</t>
-        </is>
-      </c>
-      <c r="C64" s="12" t="inlineStr"/>
+          <t>tool run</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C64" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E64" s="10" t="inlineStr">
-        <is>
-          <t>Lệnh này hỏi bạn trực tiếp — tôi gọi hộ thì mất đúng phần hỏi.</t>
-        </is>
-      </c>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E64" s="10" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>build</t>
-        </is>
-      </c>
-      <c r="B65" s="16" t="inlineStr">
-        <is>
-          <t>KHÔNG</t>
-        </is>
-      </c>
-      <c r="C65" s="12" t="inlineStr"/>
+          <t>tool verify</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C65" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E65" s="10" t="inlineStr">
-        <is>
-          <t>Ráp firmware là bước trước khi nạp; bạn chạy để còn kiểm ảnh sinh ra.</t>
-        </is>
-      </c>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E65" s="10" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>chat</t>
-        </is>
-      </c>
-      <c r="B66" s="16" t="inlineStr">
+          <t>brief</t>
+        </is>
+      </c>
+      <c r="B66" s="14" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -7858,15 +7528,19 @@
           <t>có</t>
         </is>
       </c>
-      <c r="E66" s="10" t="inlineStr"/>
+      <c r="E66" s="10" t="inlineStr">
+        <is>
+          <t>Lệnh này hỏi bạn trực tiếp — tôi gọi hộ thì mất đúng phần hỏi.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>decide</t>
-        </is>
-      </c>
-      <c r="B67" s="16" t="inlineStr">
+          <t>build</t>
+        </is>
+      </c>
+      <c r="B67" s="14" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -7879,17 +7553,17 @@
       </c>
       <c r="E67" s="10" t="inlineStr">
         <is>
-          <t>Trình phương án để BẠN chọn; tôi gọi hộ thì mất đúng chỗ bạn chọn.</t>
+          <t>Ráp firmware là bước trước khi nạp; bạn chạy để còn kiểm ảnh sinh ra.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>doctor</t>
-        </is>
-      </c>
-      <c r="B68" s="16" t="inlineStr">
+          <t>chat</t>
+        </is>
+      </c>
+      <c r="B68" s="14" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -7900,19 +7574,15 @@
           <t>có</t>
         </is>
       </c>
-      <c r="E68" s="10" t="inlineStr">
-        <is>
-          <t>Cài đặt công cụ đổi máy của bạn. Tôi quét và báo được ('doctor' không cờ là chỉ đọc), nhưng '--fix' phải do bạn chạy và xác nhận từng lệnh.</t>
-        </is>
-      </c>
+      <c r="E68" s="10" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>endurance</t>
-        </is>
-      </c>
-      <c r="B69" s="16" t="inlineStr">
+          <t>decide</t>
+        </is>
+      </c>
+      <c r="B69" s="14" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -7925,17 +7595,17 @@
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
-          <t>Lệnh này chiếm cổng nối tiếp và chạy hàng giờ; bạn nên tự bố trí.</t>
+          <t>Trình phương án để BẠN chọn; tôi gọi hộ thì mất đúng chỗ bạn chọn.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>flash</t>
-        </is>
-      </c>
-      <c r="B70" s="16" t="inlineStr">
+          <t>doctor</t>
+        </is>
+      </c>
+      <c r="B70" s="14" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -7948,17 +7618,17 @@
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>Nạp firmware chạm vào thiết bị thật. Luôn cần chính bạn xác nhận — một phiên không có người không được diễn giải thành một người đã đồng ý.</t>
+          <t>Cài đặt công cụ đổi máy của bạn. Tôi quét và báo được ('doctor' không cờ là chỉ đọc), nhưng '--fix' phải do bạn chạy và xác nhận từng lệnh.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>gen</t>
-        </is>
-      </c>
-      <c r="B71" s="16" t="inlineStr">
+          <t>endurance</t>
+        </is>
+      </c>
+      <c r="B71" s="14" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -7971,17 +7641,17 @@
       </c>
       <c r="E71" s="10" t="inlineStr">
         <is>
-          <t>Vòng sinh mã ghi số liệu vào kpi_log.csv, và những dòng ấy là DỮ LIỆU THÍ NGHIỆM của Chương 3. Tôi tự khởi động nó sẽ chèn vào bảng số liệu những lượt chạy mà người làm thí nghiệm không định chạy — nên bạn là người bấm nút.</t>
+          <t>Lệnh này chiếm cổng nối tiếp và chạy hàng giờ; bạn nên tự bố trí.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>init</t>
-        </is>
-      </c>
-      <c r="B72" s="16" t="inlineStr">
+          <t>flash</t>
+        </is>
+      </c>
+      <c r="B72" s="14" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -7994,17 +7664,17 @@
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>Khởi tạo dự án là quyết định mở đầu, không nên nằm giữa một câu hỏi.</t>
+          <t>Nạp firmware chạm vào thiết bị thật. Luôn cần chính bạn xác nhận — một phiên không có người không được diễn giải thành một người đã đồng ý.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>ports</t>
-        </is>
-      </c>
-      <c r="B73" s="16" t="inlineStr">
+          <t>gen</t>
+        </is>
+      </c>
+      <c r="B73" s="14" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -8017,17 +7687,17 @@
       </c>
       <c r="E73" s="10" t="inlineStr">
         <is>
-          <t>Đọc cổng nối tiếp là việc chạm tới máy của bạn.</t>
+          <t>Vòng sinh mã ghi số liệu vào kpi_log.csv, và những dòng ấy là DỮ LIỆU THÍ NGHIỆM của Chương 3. Tôi tự khởi động nó sẽ chèn vào bảng số liệu những lượt chạy mà người làm thí nghiệm không định chạy — nên bạn là người bấm nút.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>resume</t>
-        </is>
-      </c>
-      <c r="B74" s="16" t="inlineStr">
+          <t>init</t>
+        </is>
+      </c>
+      <c r="B74" s="14" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -8038,15 +7708,19 @@
           <t>có</t>
         </is>
       </c>
-      <c r="E74" s="10" t="inlineStr"/>
+      <c r="E74" s="10" t="inlineStr">
+        <is>
+          <t>Khởi tạo dự án là quyết định mở đầu, không nên nằm giữa một câu hỏi.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>rollback</t>
-        </is>
-      </c>
-      <c r="B75" s="16" t="inlineStr">
+          <t>ports</t>
+        </is>
+      </c>
+      <c r="B75" s="14" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -8059,17 +7733,17 @@
       </c>
       <c r="E75" s="10" t="inlineStr">
         <is>
-          <t>Quay lui đổi mã đang chạy trên thiết bị — quyết định của bạn.</t>
+          <t>Đọc cổng nối tiếp là việc chạm tới máy của bạn.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>scope-image</t>
-        </is>
-      </c>
-      <c r="B76" s="16" t="inlineStr">
+          <t>resume</t>
+        </is>
+      </c>
+      <c r="B76" s="14" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -8080,19 +7754,15 @@
           <t>có</t>
         </is>
       </c>
-      <c r="E76" s="10" t="inlineStr">
-        <is>
-          <t>Cần bạn đối chiếu ảnh gốc rồi chốt số đo.</t>
-        </is>
-      </c>
+      <c r="E76" s="10" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>telemetry</t>
-        </is>
-      </c>
-      <c r="B77" s="16" t="inlineStr">
+          <t>rollback</t>
+        </is>
+      </c>
+      <c r="B77" s="14" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -8105,17 +7775,17 @@
       </c>
       <c r="E77" s="10" t="inlineStr">
         <is>
-          <t>Lệnh này chiếm cổng nối tiếp của thiết bị; bạn nên tự cắm và chạy.</t>
+          <t>Quay lui đổi mã đang chạy trên thiết bị — quyết định của bạn.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>tune</t>
-        </is>
-      </c>
-      <c r="B78" s="16" t="inlineStr">
+          <t>scope-image</t>
+        </is>
+      </c>
+      <c r="B78" s="14" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
@@ -8128,12 +7798,58 @@
       </c>
       <c r="E78" s="10" t="inlineStr">
         <is>
+          <t>Cần bạn đối chiếu ảnh gốc rồi chốt số đo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="inlineStr">
+        <is>
+          <t>telemetry</t>
+        </is>
+      </c>
+      <c r="B79" s="14" t="inlineStr">
+        <is>
+          <t>KHÔNG</t>
+        </is>
+      </c>
+      <c r="C79" s="12" t="inlineStr"/>
+      <c r="D79" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E79" s="10" t="inlineStr">
+        <is>
+          <t>Lệnh này chiếm cổng nối tiếp của thiết bị; bạn nên tự cắm và chạy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="B80" s="14" t="inlineStr">
+        <is>
+          <t>KHÔNG</t>
+        </is>
+      </c>
+      <c r="C80" s="12" t="inlineStr"/>
+      <c r="D80" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E80" s="10" t="inlineStr">
+        <is>
           <t>Phong hạng hw-verified là một khẳng định về phần cứng. Nó chỉ được đặt bởi người vừa cầm thiết bị và đọc số đo.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E78"/>
+  <autoFilter ref="A1:E80"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/EAA_Bang_nang_luc.xlsx
+++ b/docs/EAA_Bang_nang_luc.xlsx
@@ -15,9 +15,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Năng lực nền'!$A$1:$G$73</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Năng lực nhúng'!$A$1:$G$87</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Khoảng trống'!$A$1:$F$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Bản đồ lệnh'!$A$1:$E$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Năng lực nhúng'!$A$1:$G$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Khoảng trống'!$A$1:$F$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Bản đồ lệnh'!$A$1:$E$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -50,7 +50,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -92,6 +92,11 @@
         <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF9999"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -119,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -159,6 +164,15 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -526,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -594,220 +608,240 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
-      <c r="B7" s="2" t="inlineStr"/>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Rà soát gần nhất</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>04/09/2026 — kiểm bằng máy: python scripts/kiem_bang_nang_luc.py. Bộ kiểm ấy đối chiếu từng dòng với mã và báo bốn kiểu lệch: tệp khai không có thật, ký hiệu khai không có thật, mã TC khai không tệp test nào nhắc, và — đáng giá nhất — MÃ CÓ MÀ KHÔNG AI GỌI.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>BẢNG NÀY SO CÁI GÌ</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Sheet 'Năng lực nền'</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Khung năng lực agent tổng quát do người dùng cung cấp (9 nhóm), đối chiếu với mã hiện có. Nhóm C10 là phần thêm, dựng từ ghi chú cuối của bản ấy: quy trình không nên đóng cứng.</t>
-        </is>
-      </c>
+      <c r="B9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Sheet 'Năng lực nhúng'</t>
+          <t>Sheet 'Năng lực nền'</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>74 nghiệp vụ riêng của lập trình nhúng, xếp theo 11 giai đoạn vòng đời + nhóm xuyên suốt. Đây là phần KHÔNG có trong khung chung — giá trị riêng của đề án nằm ở đây.</t>
+          <t>Khung năng lực agent tổng quát do người dùng cung cấp (9 nhóm), đối chiếu với mã hiện có. Nhóm C10 là phần thêm, dựng từ ghi chú cuối của bản ấy: quy trình không nên đóng cứng.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Sheet 'Khoảng trống'</t>
+          <t>Sheet 'Năng lực nhúng'</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Lọc mọi dòng CHƯA / MỘT PHẦN của cả hai sheet, xếp theo mức ưu tiên đề xuất.</t>
+          <t>74 nghiệp vụ riêng của lập trình nhúng, xếp theo 11 giai đoạn vòng đời + nhóm xuyên suốt. Đây là phần KHÔNG có trong khung chung — giá trị riêng của đề án nằm ở đây.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>Sheet 'Khoảng trống'</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Lọc mọi dòng CHƯA / MỘT PHẦN của cả hai sheet, xếp theo mức ưu tiên đề xuất. ĐÂY LÀ SHEET ĐỂ LÀM VIỆC — hai sheet trước chỉ để tra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
           <t>Sheet 'Bản đồ lệnh'</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>38 lệnh CLI: lệnh nào Agent tự gọi được, lệnh nào đòi hồ sơ dự án.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr"/>
-      <c r="B13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Lệnh nào Agent tự gọi được, lệnh nào đòi hồ sơ dự án. Số lệnh đọc thẳng từ eaa/cli.py.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>CÁCH ĐỌC CỘT TRẠNG THÁI</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Có mã chạy được VÀ chỉ ra được module/lệnh cụ thể ở cột Bằng chứng. Dòng không chỉ được thì không phải ĐỦ.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>MỘT PHẦN</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Có phần lõi, thiếu một nhánh. Cột Khoảng trống nói rõ thiếu gì.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>CHƯA</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Không có mã nào làm việc này.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>CỐ Ý KHÔNG</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Quyết định thiết kế, không phải thiếu sót. Không nên lấp.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr"/>
-      <c r="B19" s="2" t="inlineStr"/>
-    </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>THANG MỨC TỰ CHỦ (sheet Năng lực nhúng)</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>T0</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Người làm, Agent ghi vết</t>
-        </is>
-      </c>
+      <c r="B21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T0</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Agent đề xuất, người quyết</t>
+          <t>Người làm, Agent ghi vết</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Agent làm, người duyệt trước khi có hiệu lực</t>
+          <t>Agent đề xuất, người quyết</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Agent tự làm, báo lại</t>
+          <t>Agent làm, người duyệt trước khi có hiệu lực</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Agent tự làm, báo lại</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Agent tự làm, không cần báo</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr"/>
-      <c r="B26" s="2" t="inlineStr"/>
-    </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>ĐIỀU BẢNG NÀY KHÔNG LÀM</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr"/>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Nó không chạy thử năng lực nào — nó đối chiếu khung với mã. Câu 'nó chạy đúng không' thuộc về bộ test (pytest -q, 1428 test) và scripts/kiem_on_dinh.py.</t>
-        </is>
-      </c>
+      <c r="B28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Nó không chạy thử năng lực nào — nó đối chiếu khung với mã. Câu 'nó chạy đúng không' thuộc về bộ test (2157 hàm test trong 116 tệp) và scripts/kiem_on_dinh.py.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Nó cũng không kiểm được một dòng ĐỦ có ĐƯỜNG GỌI hay không — việc ấy thuộc về scripts/kiem_bang_nang_luc.py, và chính nó tìm ra bảy dòng khai ĐỦ ngày 04/09.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Nó cũng không nói năng lực nào ĐÁNG có. Cột 'Ưu tiên' chỉ là đề xuất để rà soát, người chốt lại là người đọc.</t>
         </is>
@@ -1810,9 +1844,9 @@
           <t>Đọc và phân loại lỗi (mạng / quyền / phụ thuộc / build / runtime)</t>
         </is>
       </c>
-      <c r="D33" s="11" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
+      <c r="D33" s="15" t="inlineStr">
+        <is>
+          <t>MỘT PHẦN</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr">
@@ -1820,10 +1854,14 @@
           <t>eaa/installerr.py classify(): 6 loại (mạng/quyền/phụ thuộc/build/không tìm thấy/khác), thứ tự mẫu có chủ ý · TC-69</t>
         </is>
       </c>
-      <c r="F33" s="10" t="inlineStr"/>
-      <c r="G33" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>Không có người gọi: `eaa/doctor.py _run_install` bắt ngoại lệ rồi ghi 'KHÔNG tải được — {exc}' và trả về, không đưa đầu ra qua classify(). Cần nối vào doctor để một lần cài trượt sinh ra CHẨN ĐOÁN chứ không sinh ra một dòng log</t>
+        </is>
+      </c>
+      <c r="G33" s="16" t="inlineStr">
+        <is>
+          <t>Cao</t>
         </is>
       </c>
     </row>
@@ -1843,9 +1881,9 @@
           <t>Thử lại có kiểm soát (retry + backoff) cho lỗi mạng</t>
         </is>
       </c>
-      <c r="D34" s="11" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
+      <c r="D34" s="15" t="inlineStr">
+        <is>
+          <t>MỘT PHẦN</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
@@ -1853,10 +1891,14 @@
           <t>installerr.retry_delays() 2s/4s/8s + WebFetcher.max_retries — và CHỈ lỗi mạng mới retryable, có test canh điều đó</t>
         </is>
       </c>
-      <c r="F34" s="10" t="inlineStr"/>
-      <c r="G34" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>Nửa có thật là nhánh WEB: WebFetcher.max_retries nằm trên đường `eaa read`/`eaa research` và có người gọi. Nhánh CÀI ĐẶT thì không: retry_delays() không ai gọi, nên một lần cài đứt mạng là trượt hẳn</t>
+        </is>
+      </c>
+      <c r="G34" s="16" t="inlineStr">
+        <is>
+          <t>Cao</t>
         </is>
       </c>
     </row>
@@ -1876,9 +1918,9 @@
           <t>Đổi tham số: ghim phiên bản cũ hơn, cờ khác, mirror khác</t>
         </is>
       </c>
-      <c r="D35" s="11" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
+      <c r="D35" s="15" t="inlineStr">
+        <is>
+          <t>MỘT PHẦN</t>
         </is>
       </c>
       <c r="E35" s="10" t="inlineStr">
@@ -1886,10 +1928,14 @@
           <t>installerr.remedies(): bậc đổi kho/mirror, bậc ghim phiên bản cũ hơn, bậc cài ngoại tuyến</t>
         </is>
       </c>
-      <c r="F35" s="10" t="inlineStr"/>
-      <c r="G35" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F35" s="10" t="inlineStr">
+        <is>
+          <t>Thang gỡ dựng đủ bậc và có TC-69 canh thứ tự, nhưng không lệnh nào in nó ra cho người đọc</t>
+        </is>
+      </c>
+      <c r="G35" s="16" t="inlineStr">
+        <is>
+          <t>Cao</t>
         </is>
       </c>
     </row>
@@ -1916,13 +1962,17 @@
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
-          <t>`eaa research` tra nguyên văn dòng lỗi; thang gỡ của loại KHÁC gọi thẳng lệnh ấy kèm dòng lỗi</t>
-        </is>
-      </c>
-      <c r="F36" s="10" t="inlineStr"/>
+          <t>`eaa research` tra nguyên văn dòng lỗi — lệnh có thật, Agent tự gọi được</t>
+        </is>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>Đủ ở mức người gõ lệnh. Chưa tự động: thang gỡ của loại KHÁC nêu lệnh ấy trong văn bản, không tự chạy nó</t>
+        </is>
+      </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Thấp</t>
         </is>
       </c>
     </row>
@@ -1942,9 +1992,9 @@
           <t>Đổi sang công cụ thay thế tương đương</t>
         </is>
       </c>
-      <c r="D37" s="11" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
+      <c r="D37" s="15" t="inlineStr">
+        <is>
+          <t>MỘT PHẦN</t>
         </is>
       </c>
       <c r="E37" s="10" t="inlineStr">
@@ -1952,10 +2002,14 @@
           <t>installerr.remedies(alternatives=…) — bậc ấy KHÔNG cho Agent tự làm: đổi công cụ là đổi cả cổng kiểm chứng</t>
         </is>
       </c>
-      <c r="F37" s="10" t="inlineStr"/>
-      <c r="G37" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>Cùng gốc với C5.3: bậc có trong thư viện, không có đường nào chạy tới</t>
+        </is>
+      </c>
+      <c r="G37" s="13" t="inlineStr">
+        <is>
+          <t>Vừa</t>
         </is>
       </c>
     </row>
@@ -1975,20 +2029,24 @@
           <t>Tự viết giải pháp tối thiểu thay thế</t>
         </is>
       </c>
-      <c r="D38" s="11" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
+      <c r="D38" s="15" t="inlineStr">
+        <is>
+          <t>MỘT PHẦN</t>
         </is>
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
-          <t>Thang gỡ lỗi cài đặt có bậc áp chót 'tự viết một thứ tối thiểu thay thế', đặt SAU mọi bậc cài thật · TC-77</t>
-        </is>
-      </c>
-      <c r="F38" s="10" t="inlineStr"/>
-      <c r="G38" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Bậc áp chót của installerr.remedies(): 'tự viết một thứ tối thiểu thay thế', đặt SAU mọi bậc cài thật · TC-77</t>
+        </is>
+      </c>
+      <c r="F38" s="10" t="inlineStr">
+        <is>
+          <t>Xưởng công cụ (eaa/toolforge.py) thì có đường chạy thật; riêng bậc DẪN tới nó trong thang gỡ lỗi cài đặt thì không ai gọi, nên Agent không tự đi tới bậc ấy được</t>
+        </is>
+      </c>
+      <c r="G38" s="13" t="inlineStr">
+        <is>
+          <t>Vừa</t>
         </is>
       </c>
     </row>
@@ -2020,12 +2078,12 @@
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
-          <t>Đủ cho vòng sinh mã. Với lỗi cài đặt thì mỏng hơn vì C5.1–C5.5 còn trống</t>
-        </is>
-      </c>
-      <c r="G39" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Đủ cho vòng sinh mã, và mạnh thêm từ SL-162: cổng unittests quy lỗi về TỆP (metrics['failing_files']). Với lỗi cài đặt thì vẫn mỏng, vì C5.1–C5.3 chưa có đường gọi</t>
+        </is>
+      </c>
+      <c r="G39" s="13" t="inlineStr">
+        <is>
+          <t>Vừa</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2115,7 @@
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>Mạnh hơn khung: giới hạn là bất biến có test chặn, không phải một hằng số ai cũng sửa được</t>
+          <t>Mạnh hơn khung: giới hạn là bất biến có test chặn, không phải một hằng số ai cũng sửa được. Từ SL-162/TC-123 thêm hạng dừng thứ ba: lỗi ngoài phạm vi module thì KHÔNG mở vòng vá</t>
         </is>
       </c>
       <c r="G40" s="12" t="inlineStr">
@@ -2082,9 +2140,9 @@
           <t>Rollback về trạng thái trước</t>
         </is>
       </c>
-      <c r="D41" s="11" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
+      <c r="D41" s="15" t="inlineStr">
+        <is>
+          <t>MỘT PHẦN</t>
         </is>
       </c>
       <c r="E41" s="10" t="inlineStr">
@@ -2092,10 +2150,14 @@
           <t>installerr.rollback_command() suy lệnh gỡ từ chính lệnh cài; không suy được thì trả RỖNG chứ không đoán</t>
         </is>
       </c>
-      <c r="F41" s="10" t="inlineStr"/>
-      <c r="G41" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>Không ai gọi. Một lần `eaa doctor --fix` cài dở dang hiện KHÔNG có đường lui nào ngoài tay người</t>
+        </is>
+      </c>
+      <c r="G41" s="16" t="inlineStr">
+        <is>
+          <t>Cao</t>
         </is>
       </c>
     </row>
@@ -2115,20 +2177,24 @@
           <t>Phân biệt lỗi của tool với lỗi do input</t>
         </is>
       </c>
-      <c r="D42" s="11" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
+      <c r="D42" s="15" t="inlineStr">
+        <is>
+          <t>MỘT PHẦN</t>
         </is>
       </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
-          <t>Tầng cổng: env error vs code error. Tầng cài đặt: 6 loại của installerr</t>
-        </is>
-      </c>
-      <c r="F42" s="10" t="inlineStr"/>
-      <c r="G42" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Tầng cổng có thật và đang chạy: env_error / config_error / blocked trong eaa/orchestrator.py (SL-162, TC-123). Tầng cài đặt là 6 loại của installerr.classify()</t>
+        </is>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>Chỉ tầng cổng đang chạy. Tầng cài đặt chưa nối, nên câu 'công cụ hỏng hay tôi gõ sai' vẫn phải người trả lời</t>
+        </is>
+      </c>
+      <c r="G42" s="13" t="inlineStr">
+        <is>
+          <t>Vừa</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4067,9 +4133,9 @@
           <t>Quản lý vòng đời tri thức</t>
         </is>
       </c>
-      <c r="D31" s="11" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>MỘT PHẦN</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
@@ -4079,7 +4145,8 @@
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
-          <t>eaa/lifecycle.py (3 đường truy ngược) · TC-29</t>
+          <t>eaa/lifecycle.py KnowledgeLifecycle (3 đường truy ngược) · TC-29
+⚠ Rà soát 04/09: KHÔNG module nào trong eaa/ import lifecycle, và không lệnh CLI nào gọi tới. `eaa docs regen` đi qua registry, không qua vòng đời tri thức. Cơ chế đúng, đường chạy chưa có</t>
         </is>
       </c>
       <c r="G31" s="10" t="inlineStr">
@@ -5486,9 +5553,9 @@
           <t>Đánh giá ảnh hưởng khi tài liệu đổi</t>
         </is>
       </c>
-      <c r="D75" s="11" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
+      <c r="D75" s="15" t="inlineStr">
+        <is>
+          <t>MỘT PHẦN</t>
         </is>
       </c>
       <c r="E75" s="12" t="inlineStr">
@@ -5498,7 +5565,8 @@
       </c>
       <c r="F75" s="10" t="inlineStr">
         <is>
-          <t>eaa/lifecycle.py · TC-29</t>
+          <t>eaa/lifecycle.py StaleSet · TC-29
+⚠ Cùng gốc với N-036: sửa một datasheet hiện KHÔNG có lệnh nào trả lời 'mã nào bị ảnh hưởng'. Cần một lệnh (vd `eaa knowledge stale`) nối StaleSet vào đường người dùng</t>
         </is>
       </c>
       <c r="G75" s="10" t="inlineStr">
@@ -5921,8 +5989,231 @@
         </is>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" s="10" t="inlineStr">
+        <is>
+          <t>N-908</t>
+        </is>
+      </c>
+      <c r="B88" s="10" t="inlineStr">
+        <is>
+          <t>XS · Xuyên suốt</t>
+        </is>
+      </c>
+      <c r="C88" s="10" t="inlineStr">
+        <is>
+          <t>Phân biệt 'mã tôi sai' với 'bài kiểm tôi sai'</t>
+        </is>
+      </c>
+      <c r="D88" s="17" t="inlineStr">
+        <is>
+          <t>CHƯA</t>
+        </is>
+      </c>
+      <c r="E88" s="12" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F88" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có gì. Bốn cổng đo mã CÓ CHẠY KHÔNG, không đo mã có ĐANG ĐO ĐÚNG THỨ nó nhận không. Bằng chứng: 3/12 lần từ chối G3 (drv_imu, logic_pid, app_balance) · §3.1</t>
+        </is>
+      </c>
+      <c r="G88" s="10" t="inlineStr">
+        <is>
+          <t>Ba trong 12 lần từ chối G3 là mã tự chỉnh cho vừa đồ đo của chính nó, và cả ba qua sạch bốn cổng</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="10" t="inlineStr">
+        <is>
+          <t>N-909</t>
+        </is>
+      </c>
+      <c r="B89" s="10" t="inlineStr">
+        <is>
+          <t>XS · Xuyên suốt</t>
+        </is>
+      </c>
+      <c r="C89" s="10" t="inlineStr">
+        <is>
+          <t>Phát hiện bài kiểm KHÔNG chứng minh điều nó nhận là mình chứng minh</t>
+        </is>
+      </c>
+      <c r="D89" s="17" t="inlineStr">
+        <is>
+          <t>CHƯA</t>
+        </is>
+      </c>
+      <c r="E89" s="12" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F89" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có gì. Cần một phép kiểm ĐỘ NHẠY: chạy lại bài kiểm mới trên bản mã SAI đã biết, xanh thì bài kiểm ấy rỗng. Bằng chứng: test_deadband_keeps_setpoint_steady · §3.3, §3.8</t>
+        </is>
+      </c>
+      <c r="G89" s="10" t="inlineStr">
+        <is>
+          <t>Bài kiểm đỏ đúng lúc rồi xanh đúng lúc — vì một lý do khác — nguy hiểm hơn bài kiểm đỏ, vì lần sau không ai đọc lại nó nữa (§3.8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="10" t="inlineStr">
+        <is>
+          <t>N-910</t>
+        </is>
+      </c>
+      <c r="B90" s="10" t="inlineStr">
+        <is>
+          <t>XS · Xuyên suốt</t>
+        </is>
+      </c>
+      <c r="C90" s="10" t="inlineStr">
+        <is>
+          <t>Canh thoái lui giữa các lượt sinh của cùng một module</t>
+        </is>
+      </c>
+      <c r="D90" s="15" t="inlineStr">
+        <is>
+          <t>MỘT PHẦN</t>
+        </is>
+      </c>
+      <c r="E90" s="12" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="F90" s="10" t="inlineStr">
+        <is>
+          <t>eaa/contract.py so khai báo header với bản trên main · TC-124 (16 bài)
+⚠ Nửa đã có là CHỮ KÝ HÀM (SL-163). Nửa còn thiếu là TẬP LỜI GỌI trong hàm vào — mất một lời gọi khởi tạo không cổng nào đỏ. Bằng chứng: app_init() · §3.2</t>
+        </is>
+      </c>
+      <c r="G90" s="10" t="inlineStr">
+        <is>
+          <t>app_init() mất bốn lời gọi khởi tạo driver sau một vòng vá → firmware câm, 33 bài kiểm vẫn xanh</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="10" t="inlineStr">
+        <is>
+          <t>N-911</t>
+        </is>
+      </c>
+      <c r="B91" s="10" t="inlineStr">
+        <is>
+          <t>XS · Xuyên suốt</t>
+        </is>
+      </c>
+      <c r="C91" s="10" t="inlineStr">
+        <is>
+          <t>Kiểm chú thích số học có đúng thứ nguyên không</t>
+        </is>
+      </c>
+      <c r="D91" s="17" t="inlineStr">
+        <is>
+          <t>CHƯA</t>
+        </is>
+      </c>
+      <c r="E91" s="12" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="F91" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có gì. Hồ sơ phần cứng đã khai đơn vị của từng đại lượng, nên dữ liệu để làm thì có sẵn. Bằng chứng: chú thích '4ms / 0.000031s = 129' · §3.4</t>
+        </is>
+      </c>
+      <c r="G91" s="10" t="inlineStr">
+        <is>
+          <t>'4ms per step / 0.000031s per sample = 129' chia chu kỳ cho một hệ số ĐỘ TRÊN LSB. Con số vô nghĩa, chú thích nghe hợp lý, và nó là nguyên nhân robot không lấy đủ mẫu</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="10" t="inlineStr">
+        <is>
+          <t>N-912</t>
+        </is>
+      </c>
+      <c r="B92" s="10" t="inlineStr">
+        <is>
+          <t>XS · Xuyên suốt</t>
+        </is>
+      </c>
+      <c r="C92" s="10" t="inlineStr">
+        <is>
+          <t>Thiết kế khả quan sát — làm cho lỗi kêu lên được</t>
+        </is>
+      </c>
+      <c r="D92" s="17" t="inlineStr">
+        <is>
+          <t>CHƯA</t>
+        </is>
+      </c>
+      <c r="E92" s="12" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F92" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có gì. eaa/decompose.py chưa đòi module khai dấu hiệu sống/hỏng; eaa/propose.py AcceptanceProposal chưa sinh tiêu chí quan sát được bằng mắt/tai · §3.6</t>
+        </is>
+      </c>
+      <c r="G92" s="10" t="inlineStr">
+        <is>
+          <t>Ba lượt nạp đầu robot chỉ 'im' hoặc 'ngã', không phân biệt được với chip chết. Mọi cải tiến quan sát — nhịp bíp, nút thoát, watchdog mất mẫu — đều do người thêm</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="10" t="inlineStr">
+        <is>
+          <t>N-913</t>
+        </is>
+      </c>
+      <c r="B93" s="10" t="inlineStr">
+        <is>
+          <t>XS · Xuyên suốt</t>
+        </is>
+      </c>
+      <c r="C93" s="10" t="inlineStr">
+        <is>
+          <t>Đưa số đo từ phần cứng ngược vào prompt</t>
+        </is>
+      </c>
+      <c r="D93" s="17" t="inlineStr">
+        <is>
+          <t>CHƯA</t>
+        </is>
+      </c>
+      <c r="E93" s="12" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="F93" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có gì. measurements.jsonl và kết quả DS-xx nằm NGOÀI eaa/composer.py. Đây là mục đắt nhất trong sáu mục, vì nó đụng vào bộ ghép prompt và vào gate tri thức · §3.7</t>
+        </is>
+      </c>
+      <c r="G93" s="10" t="inlineStr">
+        <is>
+          <t>Bài học từ bo hiện chỉ tới mô hình qua LÝ DO TỪ CHỐI kỹ sư gõ tay — mất là mất hẳn</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G87"/>
+  <autoFilter ref="A1:G93"/>
   <mergeCells count="12">
     <mergeCell ref="A68:G68"/>
     <mergeCell ref="A74:G74"/>
@@ -5947,7 +6238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5990,8 +6281,488 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>C5.1</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>nền</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>Đọc và phân loại lỗi (mạng / quyền / phụ thuộc / build / runtime)</t>
+        </is>
+      </c>
+      <c r="E2" s="15" t="inlineStr">
+        <is>
+          <t>MỘT PHẦN</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>Không có người gọi: `eaa/doctor.py _run_install` bắt ngoại lệ rồi ghi 'KHÔNG tải được — {exc}' và trả về, không đưa đầu ra qua classify(). Cần nối vào doctor để một lần cài trượt sinh ra CHẨN ĐOÁN chứ không sinh ra một dòng log</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>C5.2</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>nền</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Thử lại có kiểm soát (retry + backoff) cho lỗi mạng</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>MỘT PHẦN</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>Nửa có thật là nhánh WEB: WebFetcher.max_retries nằm trên đường `eaa read`/`eaa research` và có người gọi. Nhánh CÀI ĐẶT thì không: retry_delays() không ai gọi, nên một lần cài đứt mạng là trượt hẳn</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>C5.3</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>nền</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Đổi tham số: ghim phiên bản cũ hơn, cờ khác, mirror khác</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>MỘT PHẦN</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>Thang gỡ dựng đủ bậc và có TC-69 canh thứ tự, nhưng không lệnh nào in nó ra cho người đọc</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>C5.9</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>nền</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>Rollback về trạng thái trước</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>MỘT PHẦN</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>Không ai gọi. Một lần `eaa doctor --fix` cài dở dang hiện KHÔNG có đường lui nào ngoài tay người</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>N-908</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>nhúng</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>Phân biệt 'mã tôi sai' với 'bài kiểm tôi sai'</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>CHƯA</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có gì. Bốn cổng đo mã CÓ CHẠY KHÔNG, không đo mã có ĐANG ĐO ĐÚNG THỨ nó nhận không. Bằng chứng: 3/12 lần từ chối G3 (drv_imu, logic_pid, app_balance) · §3.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>N-909</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>nhúng</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Phát hiện bài kiểm KHÔNG chứng minh điều nó nhận là mình chứng minh</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>CHƯA</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có gì. Cần một phép kiểm ĐỘ NHẠY: chạy lại bài kiểm mới trên bản mã SAI đã biết, xanh thì bài kiểm ấy rỗng. Bằng chứng: test_deadband_keeps_setpoint_steady · §3.3, §3.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>N-910</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>nhúng</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Canh thoái lui giữa các lượt sinh của cùng một module</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>MỘT PHẦN</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>Nửa đã có là CHỮ KÝ HÀM (SL-163). Nửa còn thiếu là TẬP LỜI GỌI trong hàm vào — mất một lời gọi khởi tạo không cổng nào đỏ. Bằng chứng: app_init() · §3.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Vừa</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>C5.10</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>nền</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Phân biệt lỗi của tool với lỗi do input</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>MỘT PHẦN</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>Chỉ tầng cổng đang chạy. Tầng cài đặt chưa nối, nên câu 'công cụ hỏng hay tôi gõ sai' vẫn phải người trả lời</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Vừa</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>C5.5</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>nền</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>Đổi sang công cụ thay thế tương đương</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>MỘT PHẦN</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>Cùng gốc với C5.3: bậc có trong thư viện, không có đường nào chạy tới</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Vừa</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>C5.6</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>nền</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Tự viết giải pháp tối thiểu thay thế</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>MỘT PHẦN</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>Xưởng công cụ (eaa/toolforge.py) thì có đường chạy thật; riêng bậc DẪN tới nó trong thang gỡ lỗi cài đặt thì không ai gọi, nên Agent không tự đi tới bậc ấy được</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>Vừa</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>N-036</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>nhúng</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Quản lý vòng đời tri thức</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>MỘT PHẦN</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>Rà soát 04/09: KHÔNG module nào trong eaa/ import lifecycle, và không lệnh CLI nào gọi tới. `eaa docs regen` đi qua registry, không qua vòng đời tri thức. Cơ chế đúng, đường chạy chưa có</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>Vừa</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>N-100</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>nhúng</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>Đánh giá ảnh hưởng khi tài liệu đổi</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>MỘT PHẦN</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>Cùng gốc với N-036: sửa một datasheet hiện KHÔNG có lệnh nào trả lời 'mã nào bị ảnh hưởng'. Cần một lệnh (vd `eaa knowledge stale`) nối StaleSet vào đường người dùng</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>Vừa</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>N-911</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>nhúng</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>Kiểm chú thích số học có đúng thứ nguyên không</t>
+        </is>
+      </c>
+      <c r="E14" s="17" t="inlineStr">
+        <is>
+          <t>CHƯA</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có gì. Hồ sơ phần cứng đã khai đơn vị của từng đại lượng, nên dữ liệu để làm thì có sẵn. Bằng chứng: chú thích '4ms / 0.000031s = 129' · §3.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>Vừa</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>N-912</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>nhúng</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>Thiết kế khả quan sát — làm cho lỗi kêu lên được</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="inlineStr">
+        <is>
+          <t>CHƯA</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có gì. eaa/decompose.py chưa đòi module khai dấu hiệu sống/hỏng; eaa/propose.py AcceptanceProposal chưa sinh tiêu chí quan sát được bằng mắt/tai · §3.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Vừa</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>N-913</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>nhúng</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>Đưa số đo từ phần cứng ngược vào prompt</t>
+        </is>
+      </c>
+      <c r="E16" s="17" t="inlineStr">
+        <is>
+          <t>CHƯA</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có gì. measurements.jsonl và kết quả DS-xx nằm NGOÀI eaa/composer.py. Đây là mục đắt nhất trong sáu mục, vì nó đụng vào bộ ghép prompt và vào gate tri thức · §3.7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:F16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6002,7 +6773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E80"/>
+  <dimension ref="A1:E85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6226,7 +6997,7 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>deviations</t>
+          <t>design gen</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
@@ -6249,7 +7020,7 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>diagnose list</t>
+          <t>design list</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
@@ -6264,7 +7035,7 @@
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr"/>
@@ -6272,7 +7043,7 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>diagnose measure</t>
+          <t>deviations</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
@@ -6287,7 +7058,7 @@
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr"/>
@@ -6295,7 +7066,7 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>diagnose select</t>
+          <t>diagnose list</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
@@ -6318,7 +7089,7 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>docs list</t>
+          <t>diagnose measure</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
@@ -6341,7 +7112,7 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>environ</t>
+          <t>diagnose select</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
@@ -6356,7 +7127,7 @@
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr"/>
@@ -6364,7 +7135,7 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>errata lookup</t>
+          <t>docs list</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
@@ -6374,7 +7145,7 @@
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
@@ -6387,7 +7158,7 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>errata show</t>
+          <t>doctor</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
@@ -6410,7 +7181,7 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>field</t>
+          <t>doctor --fix</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
@@ -6420,7 +7191,7 @@
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>có</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
@@ -6433,7 +7204,7 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>focus</t>
+          <t>environ</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
@@ -6448,7 +7219,7 @@
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr"/>
@@ -6456,7 +7227,7 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>gate show</t>
+          <t>errata lookup</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
@@ -6466,7 +7237,7 @@
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>có</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
@@ -6479,7 +7250,7 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>handover doc</t>
+          <t>errata show</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
@@ -6502,7 +7273,7 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>handover rollout</t>
+          <t>field</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
@@ -6525,7 +7296,7 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>handover swap</t>
+          <t>flash</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
@@ -6535,7 +7306,7 @@
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>có</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -6548,7 +7319,7 @@
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>interface</t>
+          <t>focus</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
@@ -6558,7 +7329,7 @@
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
@@ -6571,7 +7342,7 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>ledger list</t>
+          <t>gate show</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
@@ -6594,7 +7365,7 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>memory add</t>
+          <t>handover doc</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
@@ -6604,12 +7375,12 @@
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr"/>
@@ -6617,7 +7388,7 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>memory list</t>
+          <t>handover rollout</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
@@ -6632,7 +7403,7 @@
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr"/>
@@ -6640,7 +7411,7 @@
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>handover swap</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
@@ -6655,7 +7426,7 @@
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr"/>
@@ -6663,7 +7434,7 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>plan add</t>
+          <t>interface</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
@@ -6686,7 +7457,7 @@
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>plan list</t>
+          <t>ledger list</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
@@ -6709,7 +7480,7 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>playbook list</t>
+          <t>memory add</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
@@ -6719,7 +7490,7 @@
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>có</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -6732,7 +7503,7 @@
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>playbook lookup</t>
+          <t>memory list</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
@@ -6755,7 +7526,7 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>playbook record</t>
+          <t>models</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
@@ -6765,12 +7536,12 @@
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr"/>
@@ -6778,7 +7549,7 @@
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>policy</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
@@ -6801,7 +7572,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>propose acceptance</t>
+          <t>plan add</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
@@ -6811,7 +7582,7 @@
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>có</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
@@ -6824,7 +7595,7 @@
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>propose constraints</t>
+          <t>plan list</t>
         </is>
       </c>
       <c r="B36" s="11" t="inlineStr">
@@ -6847,7 +7618,7 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>propose pinmap</t>
+          <t>playbook list</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
@@ -6862,7 +7633,7 @@
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E37" s="10" t="inlineStr"/>
@@ -6870,7 +7641,7 @@
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>propose plant</t>
+          <t>playbook lookup</t>
         </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
@@ -6885,7 +7656,7 @@
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E38" s="10" t="inlineStr"/>
@@ -6893,7 +7664,7 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>propose scope</t>
+          <t>playbook record</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
@@ -6908,7 +7679,7 @@
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E39" s="10" t="inlineStr"/>
@@ -6916,7 +7687,7 @@
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>policy</t>
         </is>
       </c>
       <c r="B40" s="11" t="inlineStr">
@@ -6939,7 +7710,7 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>report kpi</t>
+          <t>propose acceptance</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
@@ -6962,7 +7733,7 @@
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>report retrieval</t>
+          <t>propose constraints</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
@@ -6985,7 +7756,7 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>report review</t>
+          <t>propose pinmap</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
@@ -7008,7 +7779,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>report versions</t>
+          <t>propose plant</t>
         </is>
       </c>
       <c r="B44" s="11" t="inlineStr">
@@ -7031,7 +7802,7 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>propose scope</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
@@ -7041,12 +7812,12 @@
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>có</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E45" s="10" t="inlineStr"/>
@@ -7054,7 +7825,7 @@
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>resolve</t>
+          <t>read</t>
         </is>
       </c>
       <c r="B46" s="11" t="inlineStr">
@@ -7069,7 +7840,7 @@
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E46" s="10" t="inlineStr"/>
@@ -7077,7 +7848,7 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>safety propose</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
@@ -7087,7 +7858,7 @@
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
@@ -7100,7 +7871,7 @@
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>safety show</t>
+          <t>report kpi</t>
         </is>
       </c>
       <c r="B48" s="11" t="inlineStr">
@@ -7123,7 +7894,7 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>scratch</t>
+          <t>report retrieval</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
@@ -7133,12 +7904,12 @@
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E49" s="10" t="inlineStr"/>
@@ -7146,7 +7917,7 @@
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>sim run</t>
+          <t>report review</t>
         </is>
       </c>
       <c r="B50" s="11" t="inlineStr">
@@ -7169,7 +7940,7 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>skill list</t>
+          <t>report versions</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
@@ -7184,7 +7955,7 @@
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E51" s="10" t="inlineStr"/>
@@ -7192,7 +7963,7 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>skill mine</t>
+          <t>research</t>
         </is>
       </c>
       <c r="B52" s="11" t="inlineStr">
@@ -7215,7 +7986,7 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>skill run</t>
+          <t>resolve</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
@@ -7230,7 +8001,7 @@
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E53" s="10" t="inlineStr"/>
@@ -7238,7 +8009,7 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>skill verify</t>
+          <t>safety propose</t>
         </is>
       </c>
       <c r="B54" s="11" t="inlineStr">
@@ -7253,7 +8024,7 @@
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E54" s="10" t="inlineStr"/>
@@ -7261,7 +8032,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>sources need</t>
+          <t>safety show</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
@@ -7284,7 +8055,7 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>sources pages</t>
+          <t>scratch</t>
         </is>
       </c>
       <c r="B56" s="11" t="inlineStr">
@@ -7294,12 +8065,12 @@
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>có</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E56" s="10" t="inlineStr"/>
@@ -7307,7 +8078,7 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>sim run</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
@@ -7322,7 +8093,7 @@
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E57" s="10" t="inlineStr"/>
@@ -7330,7 +8101,7 @@
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>suggest</t>
+          <t>skill list</t>
         </is>
       </c>
       <c r="B58" s="11" t="inlineStr">
@@ -7345,7 +8116,7 @@
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E58" s="10" t="inlineStr"/>
@@ -7353,7 +8124,7 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>survey</t>
+          <t>skill mine</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
@@ -7368,7 +8139,7 @@
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E59" s="10" t="inlineStr"/>
@@ -7376,7 +8147,7 @@
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>tool doc</t>
+          <t>skill run</t>
         </is>
       </c>
       <c r="B60" s="11" t="inlineStr">
@@ -7386,7 +8157,7 @@
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>có</t>
         </is>
       </c>
       <c r="D60" s="12" t="inlineStr">
@@ -7399,7 +8170,7 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>tool list</t>
+          <t>skill verify</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
@@ -7409,7 +8180,7 @@
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>có</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
@@ -7422,7 +8193,7 @@
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>tool propose</t>
+          <t>sources need</t>
         </is>
       </c>
       <c r="B62" s="11" t="inlineStr">
@@ -7432,12 +8203,12 @@
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E62" s="10" t="inlineStr"/>
@@ -7445,7 +8216,7 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>tool rollback</t>
+          <t>sources pages</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
@@ -7455,12 +8226,12 @@
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E63" s="10" t="inlineStr"/>
@@ -7468,7 +8239,7 @@
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>tool run</t>
+          <t>status</t>
         </is>
       </c>
       <c r="B64" s="11" t="inlineStr">
@@ -7478,7 +8249,7 @@
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
@@ -7491,7 +8262,7 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>tool verify</t>
+          <t>suggest</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
@@ -7501,12 +8272,12 @@
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E65" s="10" t="inlineStr"/>
@@ -7514,64 +8285,68 @@
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>brief</t>
-        </is>
-      </c>
-      <c r="B66" s="14" t="inlineStr">
-        <is>
-          <t>KHÔNG</t>
-        </is>
-      </c>
-      <c r="C66" s="12" t="inlineStr"/>
+          <t>survey</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C66" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
           <t>có</t>
         </is>
       </c>
-      <c r="E66" s="10" t="inlineStr">
-        <is>
-          <t>Lệnh này hỏi bạn trực tiếp — tôi gọi hộ thì mất đúng phần hỏi.</t>
-        </is>
-      </c>
+      <c r="E66" s="10" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>build</t>
-        </is>
-      </c>
-      <c r="B67" s="14" t="inlineStr">
-        <is>
-          <t>KHÔNG</t>
-        </is>
-      </c>
-      <c r="C67" s="12" t="inlineStr"/>
+          <t>tool doc</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C67" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E67" s="10" t="inlineStr">
-        <is>
-          <t>Ráp firmware là bước trước khi nạp; bạn chạy để còn kiểm ảnh sinh ra.</t>
-        </is>
-      </c>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E67" s="10" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>chat</t>
-        </is>
-      </c>
-      <c r="B68" s="14" t="inlineStr">
-        <is>
-          <t>KHÔNG</t>
-        </is>
-      </c>
-      <c r="C68" s="12" t="inlineStr"/>
+          <t>tool list</t>
+        </is>
+      </c>
+      <c r="B68" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C68" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E68" s="10" t="inlineStr"/>
@@ -7579,99 +8354,99 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>decide</t>
-        </is>
-      </c>
-      <c r="B69" s="14" t="inlineStr">
-        <is>
-          <t>KHÔNG</t>
-        </is>
-      </c>
-      <c r="C69" s="12" t="inlineStr"/>
+          <t>tool propose</t>
+        </is>
+      </c>
+      <c r="B69" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C69" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E69" s="10" t="inlineStr">
-        <is>
-          <t>Trình phương án để BẠN chọn; tôi gọi hộ thì mất đúng chỗ bạn chọn.</t>
-        </is>
-      </c>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E69" s="10" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>doctor</t>
-        </is>
-      </c>
-      <c r="B70" s="14" t="inlineStr">
-        <is>
-          <t>KHÔNG</t>
-        </is>
-      </c>
-      <c r="C70" s="12" t="inlineStr"/>
+          <t>tool rollback</t>
+        </is>
+      </c>
+      <c r="B70" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C70" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E70" s="10" t="inlineStr">
-        <is>
-          <t>Cài đặt công cụ đổi máy của bạn. Tôi quét và báo được ('doctor' không cờ là chỉ đọc), nhưng '--fix' phải do bạn chạy và xác nhận từng lệnh.</t>
-        </is>
-      </c>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E70" s="10" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>endurance</t>
-        </is>
-      </c>
-      <c r="B71" s="14" t="inlineStr">
-        <is>
-          <t>KHÔNG</t>
-        </is>
-      </c>
-      <c r="C71" s="12" t="inlineStr"/>
+          <t>tool run</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C71" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E71" s="10" t="inlineStr">
-        <is>
-          <t>Lệnh này chiếm cổng nối tiếp và chạy hàng giờ; bạn nên tự bố trí.</t>
-        </is>
-      </c>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E71" s="10" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>flash</t>
-        </is>
-      </c>
-      <c r="B72" s="14" t="inlineStr">
-        <is>
-          <t>KHÔNG</t>
-        </is>
-      </c>
-      <c r="C72" s="12" t="inlineStr"/>
+          <t>tool verify</t>
+        </is>
+      </c>
+      <c r="B72" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C72" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E72" s="10" t="inlineStr">
-        <is>
-          <t>Nạp firmware chạm vào thiết bị thật. Luôn cần chính bạn xác nhận — một phiên không có người không được diễn giải thành một người đã đồng ý.</t>
-        </is>
-      </c>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E72" s="10" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>gen</t>
+          <t>brief</t>
         </is>
       </c>
       <c r="B73" s="14" t="inlineStr">
@@ -7687,14 +8462,14 @@
       </c>
       <c r="E73" s="10" t="inlineStr">
         <is>
-          <t>Vòng sinh mã ghi số liệu vào kpi_log.csv, và những dòng ấy là DỮ LIỆU THÍ NGHIỆM của Chương 3. Tôi tự khởi động nó sẽ chèn vào bảng số liệu những lượt chạy mà người làm thí nghiệm không định chạy — nên bạn là người bấm nút.</t>
+          <t>Lệnh này hỏi bạn trực tiếp — tôi gọi hộ thì mất đúng phần hỏi.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>init</t>
+          <t>build</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
@@ -7710,14 +8485,14 @@
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>Khởi tạo dự án là quyết định mở đầu, không nên nằm giữa một câu hỏi.</t>
+          <t>Ráp firmware là bước trước khi nạp; bạn chạy để còn kiểm ảnh sinh ra.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>ports</t>
+          <t>chat</t>
         </is>
       </c>
       <c r="B75" s="14" t="inlineStr">
@@ -7731,16 +8506,12 @@
           <t>có</t>
         </is>
       </c>
-      <c r="E75" s="10" t="inlineStr">
-        <is>
-          <t>Đọc cổng nối tiếp là việc chạm tới máy của bạn.</t>
-        </is>
-      </c>
+      <c r="E75" s="10" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>resume</t>
+          <t>decide</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
@@ -7754,12 +8525,16 @@
           <t>có</t>
         </is>
       </c>
-      <c r="E76" s="10" t="inlineStr"/>
+      <c r="E76" s="10" t="inlineStr">
+        <is>
+          <t>Trình phương án để BẠN chọn; tôi gọi hộ thì mất đúng chỗ bạn chọn.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>rollback</t>
+          <t>endurance</t>
         </is>
       </c>
       <c r="B77" s="14" t="inlineStr">
@@ -7775,14 +8550,14 @@
       </c>
       <c r="E77" s="10" t="inlineStr">
         <is>
-          <t>Quay lui đổi mã đang chạy trên thiết bị — quyết định của bạn.</t>
+          <t>Lệnh này chiếm cổng nối tiếp và chạy hàng giờ; bạn nên tự bố trí.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>scope-image</t>
+          <t>gen</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
@@ -7798,14 +8573,14 @@
       </c>
       <c r="E78" s="10" t="inlineStr">
         <is>
-          <t>Cần bạn đối chiếu ảnh gốc rồi chốt số đo.</t>
+          <t>Vòng sinh mã ghi số liệu vào kpi_log.csv, và những dòng ấy là DỮ LIỆU THÍ NGHIỆM của Chương 3. Tôi tự khởi động nó sẽ chèn vào bảng số liệu những lượt chạy mà người làm thí nghiệm không định chạy — nên bạn là người bấm nút.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>telemetry</t>
+          <t>init</t>
         </is>
       </c>
       <c r="B79" s="14" t="inlineStr">
@@ -7821,14 +8596,14 @@
       </c>
       <c r="E79" s="10" t="inlineStr">
         <is>
-          <t>Lệnh này chiếm cổng nối tiếp của thiết bị; bạn nên tự cắm và chạy.</t>
+          <t>Khởi tạo dự án là quyết định mở đầu, không nên nằm giữa một câu hỏi.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>tune</t>
+          <t>ports</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
@@ -7844,12 +8619,123 @@
       </c>
       <c r="E80" s="10" t="inlineStr">
         <is>
+          <t>Đọc cổng nối tiếp là việc chạm tới máy của bạn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>resume</t>
+        </is>
+      </c>
+      <c r="B81" s="14" t="inlineStr">
+        <is>
+          <t>KHÔNG</t>
+        </is>
+      </c>
+      <c r="C81" s="12" t="inlineStr"/>
+      <c r="D81" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E81" s="10" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="10" t="inlineStr">
+        <is>
+          <t>rollback</t>
+        </is>
+      </c>
+      <c r="B82" s="14" t="inlineStr">
+        <is>
+          <t>KHÔNG</t>
+        </is>
+      </c>
+      <c r="C82" s="12" t="inlineStr"/>
+      <c r="D82" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E82" s="10" t="inlineStr">
+        <is>
+          <t>Quay lui đổi mã đang chạy trên thiết bị — quyết định của bạn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="inlineStr">
+        <is>
+          <t>scope-image</t>
+        </is>
+      </c>
+      <c r="B83" s="14" t="inlineStr">
+        <is>
+          <t>KHÔNG</t>
+        </is>
+      </c>
+      <c r="C83" s="12" t="inlineStr"/>
+      <c r="D83" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E83" s="10" t="inlineStr">
+        <is>
+          <t>Cần bạn đối chiếu ảnh gốc rồi chốt số đo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="10" t="inlineStr">
+        <is>
+          <t>telemetry</t>
+        </is>
+      </c>
+      <c r="B84" s="14" t="inlineStr">
+        <is>
+          <t>KHÔNG</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="inlineStr"/>
+      <c r="D84" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E84" s="10" t="inlineStr">
+        <is>
+          <t>Lệnh này chiếm cổng nối tiếp của thiết bị; bạn nên tự cắm và chạy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="10" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="B85" s="14" t="inlineStr">
+        <is>
+          <t>KHÔNG</t>
+        </is>
+      </c>
+      <c r="C85" s="12" t="inlineStr"/>
+      <c r="D85" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E85" s="10" t="inlineStr">
+        <is>
           <t>Phong hạng hw-verified là một khẳng định về phần cứng. Nó chỉ được đặt bởi người vừa cầm thiết bị và đọc số đo.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E80"/>
+  <autoFilter ref="A1:E85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/EAA_Bang_nang_luc.xlsx
+++ b/docs/EAA_Bang_nang_luc.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Năng lực nền'!$A$1:$G$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Năng lực nhúng'!$A$1:$G$93</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Khoảng trống'!$A$1:$F$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Khoảng trống'!$A$1:$F$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Bản đồ lệnh'!$A$1:$E$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -827,7 +827,7 @@
       <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Nó không chạy thử năng lực nào — nó đối chiếu khung với mã. Câu 'nó chạy đúng không' thuộc về bộ test (2157 hàm test trong 116 tệp) và scripts/kiem_on_dinh.py.</t>
+          <t>Nó không chạy thử năng lực nào — nó đối chiếu khung với mã. Câu 'nó chạy đúng không' thuộc về bộ test (2190 hàm test trong 117 tệp) và scripts/kiem_on_dinh.py.</t>
         </is>
       </c>
     </row>
@@ -6079,9 +6079,9 @@
           <t>Canh thoái lui giữa các lượt sinh của cùng một module</t>
         </is>
       </c>
-      <c r="D90" s="15" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
+      <c r="D90" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
         </is>
       </c>
       <c r="E90" s="12" t="inlineStr">
@@ -6091,8 +6091,7 @@
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t>eaa/contract.py so khai báo header với bản trên main · TC-124 (16 bài)
-⚠ Nửa đã có là CHỮ KÝ HÀM (SL-163). Nửa còn thiếu là TẬP LỜI GỌI trong hàm vào — mất một lời gọi khởi tạo không cổng nào đỏ. Bằng chứng: app_init() · §3.2</t>
+          <t>eaa/contract.py: pha_vo_hop_dong so chữ ký header (SL-163, TC-124) + mat_loi_goi so tập lời gọi LIÊN MODULE của tệp .c với bản đã merge (SL-167, TC-127, 33 bài)</t>
         </is>
       </c>
       <c r="G90" s="10" t="inlineStr">
@@ -6238,7 +6237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -6474,24 +6473,24 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t>Cao</t>
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Vừa</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>N-910</t>
+          <t>C5.10</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>nhúng</t>
+          <t>nền</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>Canh thoái lui giữa các lượt sinh của cùng một module</t>
+          <t>Phân biệt lỗi của tool với lỗi do input</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
@@ -6501,7 +6500,7 @@
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>Nửa đã có là CHỮ KÝ HÀM (SL-163). Nửa còn thiếu là TẬP LỜI GỌI trong hàm vào — mất một lời gọi khởi tạo không cổng nào đỏ. Bằng chứng: app_init() · §3.2</t>
+          <t>Chỉ tầng cổng đang chạy. Tầng cài đặt chưa nối, nên câu 'công cụ hỏng hay tôi gõ sai' vẫn phải người trả lời</t>
         </is>
       </c>
     </row>
@@ -6513,7 +6512,7 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>C5.10</t>
+          <t>C5.5</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
@@ -6523,7 +6522,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>Phân biệt lỗi của tool với lỗi do input</t>
+          <t>Đổi sang công cụ thay thế tương đương</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -6533,7 +6532,7 @@
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
-          <t>Chỉ tầng cổng đang chạy. Tầng cài đặt chưa nối, nên câu 'công cụ hỏng hay tôi gõ sai' vẫn phải người trả lời</t>
+          <t>Cùng gốc với C5.3: bậc có trong thư viện, không có đường nào chạy tới</t>
         </is>
       </c>
     </row>
@@ -6545,7 +6544,7 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>C5.5</t>
+          <t>C5.6</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -6555,7 +6554,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>Đổi sang công cụ thay thế tương đương</t>
+          <t>Tự viết giải pháp tối thiểu thay thế</t>
         </is>
       </c>
       <c r="E10" s="15" t="inlineStr">
@@ -6565,7 +6564,7 @@
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
-          <t>Cùng gốc với C5.3: bậc có trong thư viện, không có đường nào chạy tới</t>
+          <t>Xưởng công cụ (eaa/toolforge.py) thì có đường chạy thật; riêng bậc DẪN tới nó trong thang gỡ lỗi cài đặt thì không ai gọi, nên Agent không tự đi tới bậc ấy được</t>
         </is>
       </c>
     </row>
@@ -6577,17 +6576,17 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>C5.6</t>
+          <t>N-036</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>nền</t>
+          <t>nhúng</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>Tự viết giải pháp tối thiểu thay thế</t>
+          <t>Quản lý vòng đời tri thức</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -6597,7 +6596,7 @@
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
-          <t>Xưởng công cụ (eaa/toolforge.py) thì có đường chạy thật; riêng bậc DẪN tới nó trong thang gỡ lỗi cài đặt thì không ai gọi, nên Agent không tự đi tới bậc ấy được</t>
+          <t>Rà soát 04/09: KHÔNG module nào trong eaa/ import lifecycle, và không lệnh CLI nào gọi tới. `eaa docs regen` đi qua registry, không qua vòng đời tri thức. Cơ chế đúng, đường chạy chưa có</t>
         </is>
       </c>
     </row>
@@ -6609,7 +6608,7 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>N-036</t>
+          <t>N-100</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
@@ -6619,7 +6618,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>Quản lý vòng đời tri thức</t>
+          <t>Đánh giá ảnh hưởng khi tài liệu đổi</t>
         </is>
       </c>
       <c r="E12" s="15" t="inlineStr">
@@ -6629,7 +6628,7 @@
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>Rà soát 04/09: KHÔNG module nào trong eaa/ import lifecycle, và không lệnh CLI nào gọi tới. `eaa docs regen` đi qua registry, không qua vòng đời tri thức. Cơ chế đúng, đường chạy chưa có</t>
+          <t>Cùng gốc với N-036: sửa một datasheet hiện KHÔNG có lệnh nào trả lời 'mã nào bị ảnh hưởng'. Cần một lệnh (vd `eaa knowledge stale`) nối StaleSet vào đường người dùng</t>
         </is>
       </c>
     </row>
@@ -6641,7 +6640,7 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>N-100</t>
+          <t>N-911</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
@@ -6651,17 +6650,17 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>Đánh giá ảnh hưởng khi tài liệu đổi</t>
-        </is>
-      </c>
-      <c r="E13" s="15" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
+          <t>Kiểm chú thích số học có đúng thứ nguyên không</t>
+        </is>
+      </c>
+      <c r="E13" s="17" t="inlineStr">
+        <is>
+          <t>CHƯA</t>
         </is>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>Cùng gốc với N-036: sửa một datasheet hiện KHÔNG có lệnh nào trả lời 'mã nào bị ảnh hưởng'. Cần một lệnh (vd `eaa knowledge stale`) nối StaleSet vào đường người dùng</t>
+          <t>Chưa có gì. Hồ sơ phần cứng đã khai đơn vị của từng đại lượng, nên dữ liệu để làm thì có sẵn. Bằng chứng: chú thích '4ms / 0.000031s = 129' · §3.4</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6672,7 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>N-911</t>
+          <t>N-912</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
@@ -6683,7 +6682,7 @@
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>Kiểm chú thích số học có đúng thứ nguyên không</t>
+          <t>Thiết kế khả quan sát — làm cho lỗi kêu lên được</t>
         </is>
       </c>
       <c r="E14" s="17" t="inlineStr">
@@ -6693,7 +6692,7 @@
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>Chưa có gì. Hồ sơ phần cứng đã khai đơn vị của từng đại lượng, nên dữ liệu để làm thì có sẵn. Bằng chứng: chú thích '4ms / 0.000031s = 129' · §3.4</t>
+          <t>Chưa có gì. eaa/decompose.py chưa đòi module khai dấu hiệu sống/hỏng; eaa/propose.py AcceptanceProposal chưa sinh tiêu chí quan sát được bằng mắt/tai · §3.6</t>
         </is>
       </c>
     </row>
@@ -6705,7 +6704,7 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>N-912</t>
+          <t>N-913</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
@@ -6715,7 +6714,7 @@
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>Thiết kế khả quan sát — làm cho lỗi kêu lên được</t>
+          <t>Đưa số đo từ phần cứng ngược vào prompt</t>
         </is>
       </c>
       <c r="E15" s="17" t="inlineStr">
@@ -6725,44 +6724,12 @@
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>Chưa có gì. eaa/decompose.py chưa đòi module khai dấu hiệu sống/hỏng; eaa/propose.py AcceptanceProposal chưa sinh tiêu chí quan sát được bằng mắt/tai · §3.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>Vừa</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>N-913</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>nhúng</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>Đưa số đo từ phần cứng ngược vào prompt</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>CHƯA</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
-        <is>
           <t>Chưa có gì. measurements.jsonl và kết quả DS-xx nằm NGOÀI eaa/composer.py. Đây là mục đắt nhất trong sáu mục, vì nó đụng vào bộ ghép prompt và vào gate tri thức · §3.7</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F16"/>
+  <autoFilter ref="A1:F15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/EAA_Bang_nang_luc.xlsx
+++ b/docs/EAA_Bang_nang_luc.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Năng lực nền'!$A$1:$G$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Năng lực nhúng'!$A$1:$G$93</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Khoảng trống'!$A$1:$F$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Khoảng trống'!$A$1:$F$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Bản đồ lệnh'!$A$1:$E$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -169,10 +169,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -827,7 +827,7 @@
       <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Nó không chạy thử năng lực nào — nó đối chiếu khung với mã. Câu 'nó chạy đúng không' thuộc về bộ test (2190 hàm test trong 117 tệp) và scripts/kiem_on_dinh.py.</t>
+          <t>Nó không chạy thử năng lực nào — nó đối chiếu khung với mã. Câu 'nó chạy đúng không' thuộc về bộ test (2233 hàm test trong 119 tệp) và scripts/kiem_on_dinh.py.</t>
         </is>
       </c>
     </row>
@@ -1844,24 +1844,20 @@
           <t>Đọc và phân loại lỗi (mạng / quyền / phụ thuộc / build / runtime)</t>
         </is>
       </c>
-      <c r="D33" s="15" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>eaa/installerr.py classify(): 6 loại (mạng/quyền/phụ thuộc/build/không tìm thấy/khác), thứ tự mẫu có chủ ý · TC-69</t>
-        </is>
-      </c>
-      <c r="F33" s="10" t="inlineStr">
-        <is>
-          <t>Không có người gọi: `eaa/doctor.py _run_install` bắt ngoại lệ rồi ghi 'KHÔNG tải được — {exc}' và trả về, không đưa đầu ra qua classify(). Cần nối vào doctor để một lần cài trượt sinh ra CHẨN ĐOÁN chứ không sinh ra một dòng log</t>
-        </is>
-      </c>
-      <c r="G33" s="16" t="inlineStr">
-        <is>
-          <t>Cao</t>
+          <t>eaa/installerr.py classify(): 6 loại (mạng/quyền/phụ thuộc/build/không tìm thấy/khác), thứ tự mẫu có chủ ý · TC-69. Gọi từ eaa/doctor.py _run_install trên mọi lần cài trượt, kể cả timeout · SL-169, TC-129</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="inlineStr"/>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1881,24 +1877,20 @@
           <t>Thử lại có kiểm soát (retry + backoff) cho lỗi mạng</t>
         </is>
       </c>
-      <c r="D34" s="15" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>installerr.retry_delays() 2s/4s/8s + WebFetcher.max_retries — và CHỈ lỗi mạng mới retryable, có test canh điều đó</t>
-        </is>
-      </c>
-      <c r="F34" s="10" t="inlineStr">
-        <is>
-          <t>Nửa có thật là nhánh WEB: WebFetcher.max_retries nằm trên đường `eaa read`/`eaa research` và có người gọi. Nhánh CÀI ĐẶT thì không: retry_delays() không ai gọi, nên một lần cài đứt mạng là trượt hẳn</t>
-        </is>
-      </c>
-      <c r="G34" s="16" t="inlineStr">
-        <is>
-          <t>Cao</t>
+          <t>installerr.retry_delays() 2s/4s/8s + WebFetcher.max_retries. Doctor thử lại CHỈ khi diagnosis.retryable — bản trước thử mù 2 lần cho mọi loại, kể cả lỗi quyền · TC-129</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="inlineStr"/>
+      <c r="G34" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1918,24 +1910,20 @@
           <t>Đổi tham số: ghim phiên bản cũ hơn, cờ khác, mirror khác</t>
         </is>
       </c>
-      <c r="D35" s="15" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
         </is>
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>installerr.remedies(): bậc đổi kho/mirror, bậc ghim phiên bản cũ hơn, bậc cài ngoại tuyến</t>
-        </is>
-      </c>
-      <c r="F35" s="10" t="inlineStr">
-        <is>
-          <t>Thang gỡ dựng đủ bậc và có TC-69 canh thứ tự, nhưng không lệnh nào in nó ra cho người đọc</t>
-        </is>
-      </c>
-      <c r="G35" s="16" t="inlineStr">
-        <is>
-          <t>Cao</t>
+          <t>installerr.remedies(): bậc đổi kho/mirror, bậc ghim phiên bản cũ hơn, bậc cài ngoại tuyến. In ra trong nhật ký doctor khi cài trượt (InstallDiagnosis.render) · TC-129</t>
+        </is>
+      </c>
+      <c r="F35" s="10" t="inlineStr"/>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1992,24 +1980,20 @@
           <t>Đổi sang công cụ thay thế tương đương</t>
         </is>
       </c>
-      <c r="D37" s="15" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
         </is>
       </c>
       <c r="E37" s="10" t="inlineStr">
         <is>
-          <t>installerr.remedies(alternatives=…) — bậc ấy KHÔNG cho Agent tự làm: đổi công cụ là đổi cả cổng kiểm chứng</t>
-        </is>
-      </c>
-      <c r="F37" s="10" t="inlineStr">
-        <is>
-          <t>Cùng gốc với C5.3: bậc có trong thư viện, không có đường nào chạy tới</t>
-        </is>
-      </c>
-      <c r="G37" s="13" t="inlineStr">
-        <is>
-          <t>Vừa</t>
+          <t>installerr.remedies(alternatives=…) — bậc ấy KHÔNG cho Agent tự làm: đổi công cụ là đổi cả cổng kiểm chứng. Đi cùng thang gỡ vào nhật ký doctor · TC-129</t>
+        </is>
+      </c>
+      <c r="F37" s="10" t="inlineStr"/>
+      <c r="G37" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2029,24 +2013,20 @@
           <t>Tự viết giải pháp tối thiểu thay thế</t>
         </is>
       </c>
-      <c r="D38" s="15" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
         </is>
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
-          <t>Bậc áp chót của installerr.remedies(): 'tự viết một thứ tối thiểu thay thế', đặt SAU mọi bậc cài thật · TC-77</t>
-        </is>
-      </c>
-      <c r="F38" s="10" t="inlineStr">
-        <is>
-          <t>Xưởng công cụ (eaa/toolforge.py) thì có đường chạy thật; riêng bậc DẪN tới nó trong thang gỡ lỗi cài đặt thì không ai gọi, nên Agent không tự đi tới bậc ấy được</t>
-        </is>
-      </c>
-      <c r="G38" s="13" t="inlineStr">
-        <is>
-          <t>Vừa</t>
+          <t>Bậc áp chót của installerr.remedies(): 'tự viết một thứ tối thiểu thay thế', đặt SAU mọi bậc cài thật · TC-77. Xưởng công cụ eaa/toolforge.py là chỗ thực thi bậc ấy</t>
+        </is>
+      </c>
+      <c r="F38" s="10" t="inlineStr"/>
+      <c r="G38" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2073,17 +2053,17 @@
       </c>
       <c r="E39" s="10" t="inlineStr">
         <is>
-          <t>ToolReport ghi kết quả từng cổng kèm đầu ra thật; `eaa report review`; vòng tự sửa ghi lại từng lần thử</t>
+          <t>ToolReport ghi kết quả từng cổng kèm đầu ra thật; `eaa report review`; vòng tự sửa ghi lại từng lần thử. Với lỗi CÀI: InstallDiagnosis nêu loại, dấu hiệu nhận ra, mức tin cậy, thang gỡ và lệnh quay lui · TC-129</t>
         </is>
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
-          <t>Đủ cho vòng sinh mã, và mạnh thêm từ SL-162: cổng unittests quy lỗi về TỆP (metrics['failing_files']). Với lỗi cài đặt thì vẫn mỏng, vì C5.1–C5.3 chưa có đường gọi</t>
-        </is>
-      </c>
-      <c r="G39" s="13" t="inlineStr">
-        <is>
-          <t>Vừa</t>
+          <t>Mạnh thêm từ SL-162: cổng unittests quy lỗi về TỆP (metrics['failing_files'])</t>
+        </is>
+      </c>
+      <c r="G39" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2140,24 +2120,20 @@
           <t>Rollback về trạng thái trước</t>
         </is>
       </c>
-      <c r="D41" s="15" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
         </is>
       </c>
       <c r="E41" s="10" t="inlineStr">
         <is>
-          <t>installerr.rollback_command() suy lệnh gỡ từ chính lệnh cài; không suy được thì trả RỖNG chứ không đoán</t>
-        </is>
-      </c>
-      <c r="F41" s="10" t="inlineStr">
-        <is>
-          <t>Không ai gọi. Một lần `eaa doctor --fix` cài dở dang hiện KHÔNG có đường lui nào ngoài tay người</t>
-        </is>
-      </c>
-      <c r="G41" s="16" t="inlineStr">
-        <is>
-          <t>Cao</t>
+          <t>installerr.rollback_command() suy lệnh gỡ từ chính lệnh cài; không suy được thì trả RỖNG chứ không đoán. Doctor NÊU lệnh lui cho mọi bước đã chạy, và KHÔNG tự chạy — gỡ cũng là một lần đổi máy (N-022 mức T2) · TC-129</t>
+        </is>
+      </c>
+      <c r="F41" s="10" t="inlineStr"/>
+      <c r="G41" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2177,24 +2153,20 @@
           <t>Phân biệt lỗi của tool với lỗi do input</t>
         </is>
       </c>
-      <c r="D42" s="15" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
+      <c r="D42" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
         </is>
       </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
-          <t>Tầng cổng có thật và đang chạy: env_error / config_error / blocked trong eaa/orchestrator.py (SL-162, TC-123). Tầng cài đặt là 6 loại của installerr.classify()</t>
-        </is>
-      </c>
-      <c r="F42" s="10" t="inlineStr">
-        <is>
-          <t>Chỉ tầng cổng đang chạy. Tầng cài đặt chưa nối, nên câu 'công cụ hỏng hay tôi gõ sai' vẫn phải người trả lời</t>
-        </is>
-      </c>
-      <c r="G42" s="13" t="inlineStr">
-        <is>
-          <t>Vừa</t>
+          <t>Tầng cổng: env_error / config_error / blocked trong eaa/orchestrator.py (SL-162, TC-123). Tầng cài đặt: 6 loại của installerr.classify(), nay có đường gọi từ doctor · TC-129</t>
+        </is>
+      </c>
+      <c r="F42" s="10" t="inlineStr"/>
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6005,7 +5977,7 @@
           <t>Phân biệt 'mã tôi sai' với 'bài kiểm tôi sai'</t>
         </is>
       </c>
-      <c r="D88" s="17" t="inlineStr">
+      <c r="D88" s="16" t="inlineStr">
         <is>
           <t>CHƯA</t>
         </is>
@@ -6042,9 +6014,9 @@
           <t>Phát hiện bài kiểm KHÔNG chứng minh điều nó nhận là mình chứng minh</t>
         </is>
       </c>
-      <c r="D89" s="17" t="inlineStr">
-        <is>
-          <t>CHƯA</t>
+      <c r="D89" s="15" t="inlineStr">
+        <is>
+          <t>MỘT PHẦN</t>
         </is>
       </c>
       <c r="E89" s="12" t="inlineStr">
@@ -6054,7 +6026,8 @@
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
-          <t>Chưa có gì. Cần một phép kiểm ĐỘ NHẠY: chạy lại bài kiểm mới trên bản mã SAI đã biết, xanh thì bài kiểm ấy rỗng. Bằng chứng: test_deadband_keeps_setpoint_steady · §3.3, §3.8</t>
+          <t>eaa/sensitivity.py chạy bộ kiểm MỚI trên mã CŨ trong bản sao tạm; kết quả vào nhật ký, KPI test_sensitivity, và đầu checklist G3 (SL-168, TC-128, 28 bài)
+⚠ Bắt được hạng NHẸ HƠN hạng đã sinh ra nó: bài kiểm không phân biệt được gì. Ca deadband vẫn đỏ trên mã cũ vì lý do khác nên vẫn QUA được phép đo — phần ấy còn cần người đọc ở G3</t>
         </is>
       </c>
       <c r="G89" s="10" t="inlineStr">
@@ -6116,7 +6089,7 @@
           <t>Kiểm chú thích số học có đúng thứ nguyên không</t>
         </is>
       </c>
-      <c r="D91" s="17" t="inlineStr">
+      <c r="D91" s="16" t="inlineStr">
         <is>
           <t>CHƯA</t>
         </is>
@@ -6153,7 +6126,7 @@
           <t>Thiết kế khả quan sát — làm cho lỗi kêu lên được</t>
         </is>
       </c>
-      <c r="D92" s="17" t="inlineStr">
+      <c r="D92" s="16" t="inlineStr">
         <is>
           <t>CHƯA</t>
         </is>
@@ -6190,7 +6163,7 @@
           <t>Đưa số đo từ phần cứng ngược vào prompt</t>
         </is>
       </c>
-      <c r="D93" s="17" t="inlineStr">
+      <c r="D93" s="16" t="inlineStr">
         <is>
           <t>CHƯA</t>
         </is>
@@ -6237,7 +6210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -6281,142 +6254,142 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>Cao</t>
         </is>
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>C5.1</t>
+          <t>N-908</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>nền</t>
+          <t>nhúng</t>
         </is>
       </c>
       <c r="D2" s="10" t="inlineStr">
         <is>
-          <t>Đọc và phân loại lỗi (mạng / quyền / phụ thuộc / build / runtime)</t>
-        </is>
-      </c>
-      <c r="E2" s="15" t="inlineStr">
+          <t>Phân biệt 'mã tôi sai' với 'bài kiểm tôi sai'</t>
+        </is>
+      </c>
+      <c r="E2" s="16" t="inlineStr">
+        <is>
+          <t>CHƯA</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có gì. Bốn cổng đo mã CÓ CHẠY KHÔNG, không đo mã có ĐANG ĐO ĐÚNG THỨ nó nhận không. Bằng chứng: 3/12 lần từ chối G3 (drv_imu, logic_pid, app_balance) · §3.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>N-909</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>nhúng</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Phát hiện bài kiểm KHÔNG chứng minh điều nó nhận là mình chứng minh</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>MỘT PHẦN</t>
         </is>
       </c>
-      <c r="F2" s="10" t="inlineStr">
-        <is>
-          <t>Không có người gọi: `eaa/doctor.py _run_install` bắt ngoại lệ rồi ghi 'KHÔNG tải được — {exc}' và trả về, không đưa đầu ra qua classify(). Cần nối vào doctor để một lần cài trượt sinh ra CHẨN ĐOÁN chứ không sinh ra một dòng log</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="16" t="inlineStr">
-        <is>
-          <t>Cao</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>C5.2</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
-        <is>
-          <t>nền</t>
-        </is>
-      </c>
-      <c r="D3" s="10" t="inlineStr">
-        <is>
-          <t>Thử lại có kiểm soát (retry + backoff) cho lỗi mạng</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>Bắt được hạng NHẸ HƠN hạng đã sinh ra nó: bài kiểm không phân biệt được gì. Ca deadband vẫn đỏ trên mã cũ vì lý do khác nên vẫn QUA được phép đo — phần ấy còn cần người đọc ở G3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Vừa</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>N-036</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>nhúng</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Quản lý vòng đời tri thức</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>MỘT PHẦN</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t>Nửa có thật là nhánh WEB: WebFetcher.max_retries nằm trên đường `eaa read`/`eaa research` và có người gọi. Nhánh CÀI ĐẶT thì không: retry_delays() không ai gọi, nên một lần cài đứt mạng là trượt hẳn</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="16" t="inlineStr">
-        <is>
-          <t>Cao</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>C5.3</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>nền</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>Đổi tham số: ghim phiên bản cũ hơn, cờ khác, mirror khác</t>
-        </is>
-      </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>Rà soát 04/09: KHÔNG module nào trong eaa/ import lifecycle, và không lệnh CLI nào gọi tới. `eaa docs regen` đi qua registry, không qua vòng đời tri thức. Cơ chế đúng, đường chạy chưa có</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Vừa</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>N-100</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>nhúng</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>Đánh giá ảnh hưởng khi tài liệu đổi</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
         <is>
           <t>MỘT PHẦN</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t>Thang gỡ dựng đủ bậc và có TC-69 canh thứ tự, nhưng không lệnh nào in nó ra cho người đọc</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="16" t="inlineStr">
-        <is>
-          <t>Cao</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>C5.9</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>nền</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="inlineStr">
-        <is>
-          <t>Rollback về trạng thái trước</t>
-        </is>
-      </c>
-      <c r="E5" s="15" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
-        </is>
-      </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
-          <t>Không ai gọi. Một lần `eaa doctor --fix` cài dở dang hiện KHÔNG có đường lui nào ngoài tay người</t>
+          <t>Cùng gốc với N-036: sửa một datasheet hiện KHÔNG có lệnh nào trả lời 'mã nào bị ảnh hưởng'. Cần một lệnh (vd `eaa knowledge stale`) nối StaleSet vào đường người dùng</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>Cao</t>
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Vừa</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>N-908</t>
+          <t>N-911</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -6426,29 +6399,29 @@
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>Phân biệt 'mã tôi sai' với 'bài kiểm tôi sai'</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
+          <t>Kiểm chú thích số học có đúng thứ nguyên không</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>CHƯA</t>
         </is>
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
-          <t>Chưa có gì. Bốn cổng đo mã CÓ CHẠY KHÔNG, không đo mã có ĐANG ĐO ĐÚNG THỨ nó nhận không. Bằng chứng: 3/12 lần từ chối G3 (drv_imu, logic_pid, app_balance) · §3.1</t>
+          <t>Chưa có gì. Hồ sơ phần cứng đã khai đơn vị của từng đại lượng, nên dữ liệu để làm thì có sẵn. Bằng chứng: chú thích '4ms / 0.000031s = 129' · §3.4</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>Cao</t>
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Vừa</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>N-909</t>
+          <t>N-912</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -6458,17 +6431,17 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Phát hiện bài kiểm KHÔNG chứng minh điều nó nhận là mình chứng minh</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
+          <t>Thiết kế khả quan sát — làm cho lỗi kêu lên được</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>CHƯA</t>
         </is>
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
-          <t>Chưa có gì. Cần một phép kiểm ĐỘ NHẠY: chạy lại bài kiểm mới trên bản mã SAI đã biết, xanh thì bài kiểm ấy rỗng. Bằng chứng: test_deadband_keeps_setpoint_steady · §3.3, §3.8</t>
+          <t>Chưa có gì. eaa/decompose.py chưa đòi module khai dấu hiệu sống/hỏng; eaa/propose.py AcceptanceProposal chưa sinh tiêu chí quan sát được bằng mắt/tai · §3.6</t>
         </is>
       </c>
     </row>
@@ -6480,256 +6453,32 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>C5.10</t>
+          <t>N-913</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>nền</t>
+          <t>nhúng</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>Phân biệt lỗi của tool với lỗi do input</t>
-        </is>
-      </c>
-      <c r="E8" s="15" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
+          <t>Đưa số đo từ phần cứng ngược vào prompt</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>CHƯA</t>
         </is>
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>Chỉ tầng cổng đang chạy. Tầng cài đặt chưa nối, nên câu 'công cụ hỏng hay tôi gõ sai' vẫn phải người trả lời</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>Vừa</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>C5.5</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>nền</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>Đổi sang công cụ thay thế tương đương</t>
-        </is>
-      </c>
-      <c r="E9" s="15" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
-        </is>
-      </c>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t>Cùng gốc với C5.3: bậc có trong thư viện, không có đường nào chạy tới</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>Vừa</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>C5.6</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>nền</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>Tự viết giải pháp tối thiểu thay thế</t>
-        </is>
-      </c>
-      <c r="E10" s="15" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
-        </is>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t>Xưởng công cụ (eaa/toolforge.py) thì có đường chạy thật; riêng bậc DẪN tới nó trong thang gỡ lỗi cài đặt thì không ai gọi, nên Agent không tự đi tới bậc ấy được</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>Vừa</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>N-036</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>nhúng</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>Quản lý vòng đời tri thức</t>
-        </is>
-      </c>
-      <c r="E11" s="15" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
-        </is>
-      </c>
-      <c r="F11" s="10" t="inlineStr">
-        <is>
-          <t>Rà soát 04/09: KHÔNG module nào trong eaa/ import lifecycle, và không lệnh CLI nào gọi tới. `eaa docs regen` đi qua registry, không qua vòng đời tri thức. Cơ chế đúng, đường chạy chưa có</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>Vừa</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>N-100</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>nhúng</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>Đánh giá ảnh hưởng khi tài liệu đổi</t>
-        </is>
-      </c>
-      <c r="E12" s="15" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
-        </is>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>Cùng gốc với N-036: sửa một datasheet hiện KHÔNG có lệnh nào trả lời 'mã nào bị ảnh hưởng'. Cần một lệnh (vd `eaa knowledge stale`) nối StaleSet vào đường người dùng</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>Vừa</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>N-911</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>nhúng</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>Kiểm chú thích số học có đúng thứ nguyên không</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>CHƯA</t>
-        </is>
-      </c>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t>Chưa có gì. Hồ sơ phần cứng đã khai đơn vị của từng đại lượng, nên dữ liệu để làm thì có sẵn. Bằng chứng: chú thích '4ms / 0.000031s = 129' · §3.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>Vừa</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>N-912</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>nhúng</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>Thiết kế khả quan sát — làm cho lỗi kêu lên được</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>CHƯA</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>Chưa có gì. eaa/decompose.py chưa đòi module khai dấu hiệu sống/hỏng; eaa/propose.py AcceptanceProposal chưa sinh tiêu chí quan sát được bằng mắt/tai · §3.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>Vừa</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>N-913</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>nhúng</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>Đưa số đo từ phần cứng ngược vào prompt</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>CHƯA</t>
-        </is>
-      </c>
-      <c r="F15" s="10" t="inlineStr">
-        <is>
           <t>Chưa có gì. measurements.jsonl và kết quả DS-xx nằm NGOÀI eaa/composer.py. Đây là mục đắt nhất trong sáu mục, vì nó đụng vào bộ ghép prompt và vào gate tri thức · §3.7</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F15"/>
+  <autoFilter ref="A1:F8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/EAA_Bang_nang_luc.xlsx
+++ b/docs/EAA_Bang_nang_luc.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Năng lực nền'!$A$1:$G$73</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Năng lực nhúng'!$A$1:$G$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Năng lực nhúng'!$A$1:$G$97</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Khoảng trống'!$A$1:$F$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Bản đồ lệnh'!$A$1:$E$85</definedName>
   </definedNames>
@@ -651,7 +651,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>74 nghiệp vụ riêng của lập trình nhúng, xếp theo 11 giai đoạn vòng đời + nhóm xuyên suốt. Đây là phần KHÔNG có trong khung chung — giá trị riêng của đề án nằm ở đây.</t>
+          <t>84 nghiệp vụ riêng của lập trình nhúng, xếp theo 11 giai đoạn vòng đời + nhóm xuyên suốt. Đây là phần KHÔNG có trong khung chung — giá trị riêng của đề án nằm ở đây. Số đếm tại chỗ: bảng dài thêm mỗi lần rà soát tìm ra việc chưa ai đặt tên.</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Nó không chạy thử năng lực nào — nó đối chiếu khung với mã. Câu 'nó chạy đúng không' thuộc về bộ test (2233 hàm test trong 119 tệp) và scripts/kiem_on_dinh.py.</t>
+          <t>Nó không chạy thử năng lực nào — nó đối chiếu khung với mã. Câu 'nó chạy đúng không' thuộc về bộ test (2248 hàm test trong 120 tệp) và scripts/kiem_on_dinh.py.</t>
         </is>
       </c>
     </row>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="E59" s="10" t="inlineStr">
         <is>
-          <t>state.json ghi nguyên tử sống sót qua crash (TC-03, N-907); KB append-only + supersede không ghi đè vật lý; tools.yaml; env.lock</t>
+          <t>state.json ghi nguyên tử sống sót qua crash (TC-03, N-907); eaa/kb.py nạp 5 kho của dự án — append-only + supersede, không ghi đè vật lý; tools.yaml; env.lock</t>
         </is>
       </c>
       <c r="F59" s="10" t="inlineStr"/>
@@ -3087,7 +3087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
-          <t>eaa/brief.py probe_hardware · TC-49a</t>
+          <t>eaa/brief.py probe_hardware + eaa/usbdev.py (hỏi BO ĐÃ LÊN BUS CHƯA, khác hẳn câu có cổng nối tiếp không) + eaa/serialport.py · TC-49a, TC-85</t>
         </is>
       </c>
       <c r="G4" s="10" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
-          <t>eaa/docplan.py plan_documents · TC-55a,b</t>
+          <t>eaa/docplan.py plan_documents + eaa/archive.py (nhận cả một kho nén hồ sơ: giải nén, phân loại, giữ nguyên bản gốc) · TC-55a,b</t>
         </is>
       </c>
       <c r="G6" s="10" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>eaa/ingest.py → G2 · TC-22</t>
+          <t>eaa/ingest.py → G2, đọc PDF qua eaa/pdftext.py — bọc pypdf và NÓI RA chỗ nó đọc không được thay vì trả về chuỗi rỗng · TC-22</t>
         </is>
       </c>
       <c r="G26" s="10" t="inlineStr">
@@ -4165,53 +4165,53 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>N-038</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>GĐ3 · Tri thức phần cứng</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>Trả lời câu hỏi kỹ thuật từ kho tri thức ĐÃ DUYỆT</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>eaa/rag.py search_chunks (đồ thị trước, BM25 sau) + lệnh eaa recall + mục recall trong TOOLBOX; chất lượng truy xuất đo bằng eaa/goldenset.py — precision@k trên bộ chuẩn, eaa report retrieval · SL-166, TC-126, TC-20</t>
+        </is>
+      </c>
+      <c r="G33" s="10" t="inlineStr">
+        <is>
+          <t>Toàn bộ giá trị của G2 nằm ở chỗ một người đã đọc bản gốc. Đường hỏi-đáp không chạm được vào kết quả ấy thì câu trả lời tụt xuống hạng chưa kiểm mà không có gì nói ra điều đó</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>GĐ4 · Thiết kế &amp; phân rã</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t>N-040</t>
-        </is>
-      </c>
-      <c r="B34" s="10" t="inlineStr">
-        <is>
-          <t>GĐ4 · Thiết kế &amp; phân rã</t>
-        </is>
-      </c>
-      <c r="C34" s="10" t="inlineStr">
-        <is>
-          <t>Phân rã bài toán thành module</t>
-        </is>
-      </c>
-      <c r="D34" s="11" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E34" s="12" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="F34" s="10" t="inlineStr">
-        <is>
-          <t>eaa/decompose.py + eaa plan propose · TC-50 (32 test)</t>
-        </is>
-      </c>
-      <c r="G34" s="10" t="inlineStr">
-        <is>
-          <t>Phân rã sai làm module phụ thuộc chằng chịt, không kiểm chứng riêng được</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>N-041</t>
+          <t>N-040</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>Định nghĩa giao diện giữa module</t>
+          <t>Phân rã bài toán thành module</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
@@ -4231,24 +4231,24 @@
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
-          <t>eaa/interfaces.py + khuôn interfaces của pack · TC-56a..e</t>
+          <t>eaa/decompose.py + eaa plan propose · TC-50 (32 test)</t>
         </is>
       </c>
       <c r="G35" s="10" t="inlineStr">
         <is>
-          <t>Đổi giao diện sau khi đã viết thân là sửa lan ra mọi nơi gọi tới</t>
+          <t>Phân rã sai làm module phụ thuộc chằng chịt, không kiểm chứng riêng được</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>N-042</t>
+          <t>N-041</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>Xếp thứ tự làm theo phụ thuộc</t>
+          <t>Định nghĩa giao diện giữa module</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
@@ -4268,105 +4268,105 @@
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t>decompose.order()/parallel_groups() · TC-50b</t>
+          <t>eaa/interfaces.py + khuôn interfaces của pack · TC-56a..e</t>
         </is>
       </c>
       <c r="G36" s="10" t="inlineStr">
         <is>
-          <t>Làm sai thứ tự thì phải giả lập phụ thuộc, tốn công gấp đôi</t>
+          <t>Đổi giao diện sau khi đã viết thân là sửa lan ra mọi nơi gọi tới</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
+          <t>N-042</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>GĐ4 · Thiết kế &amp; phân rã</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>Xếp thứ tự làm theo phụ thuộc</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>decompose.order()/parallel_groups() · TC-50b</t>
+        </is>
+      </c>
+      <c r="G37" s="10" t="inlineStr">
+        <is>
+          <t>Làm sai thứ tự thì phải giả lập phụ thuộc, tốn công gấp đôi</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
           <t>N-043</t>
         </is>
       </c>
-      <c r="B37" s="10" t="inlineStr">
+      <c r="B38" s="10" t="inlineStr">
         <is>
           <t>GĐ4 · Thiết kế &amp; phân rã</t>
         </is>
       </c>
-      <c r="C37" s="10" t="inlineStr">
+      <c r="C38" s="10" t="inlineStr">
         <is>
           <t>Thiết kế lịch chạy</t>
         </is>
       </c>
-      <c r="D37" s="11" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E37" s="12" t="inlineStr">
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="F37" s="10" t="inlineStr">
+      <c r="F38" s="10" t="inlineStr">
         <is>
           <t>decompose: chu kỳ + tải CPU + 3 phép kiểm · TC-50c</t>
         </is>
       </c>
-      <c r="G37" s="10" t="inlineStr">
+      <c r="G38" s="10" t="inlineStr">
         <is>
           <t>Chu kỳ là quyết định vật lý — máy đọc được tên hàm, không đọc được rằng con lắc cần 10 ms</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="9" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>GĐ5 · Sinh mã &amp; kiểm chứng tĩnh</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="10" t="inlineStr">
-        <is>
-          <t>N-050</t>
-        </is>
-      </c>
-      <c r="B39" s="10" t="inlineStr">
-        <is>
-          <t>GĐ5 · Sinh mã &amp; kiểm chứng tĩnh</t>
-        </is>
-      </c>
-      <c r="C39" s="10" t="inlineStr">
-        <is>
-          <t>Sinh mã một module</t>
-        </is>
-      </c>
-      <c r="D39" s="11" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E39" s="12" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="F39" s="10" t="inlineStr">
-        <is>
-          <t>eaa/composer.py + orchestrator · TC-04, TC-17</t>
-        </is>
-      </c>
-      <c r="G39" s="10" t="inlineStr">
-        <is>
-          <t>Mã không trích dẫn nguồn thì không phân biệt được tra được với bịa ra</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>N-051</t>
+          <t>N-050</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>Biên dịch</t>
+          <t>Sinh mã một module</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
@@ -4386,24 +4386,24 @@
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>eaa/tools/compile.py CompileGate · TC-40</t>
+          <t>eaa/composer.py + orchestrator · TC-04, TC-17</t>
         </is>
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>Gộp dịch với liên kết làm mọi module trượt vì lý do chẳng liên quan tới chất lượng mã</t>
+          <t>Mã không trích dẫn nguồn thì không phân biệt được tra được với bịa ra</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>N-052</t>
+          <t>N-051</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>Phân tích tĩnh theo ràng buộc dự án</t>
+          <t>Biên dịch</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
@@ -4428,19 +4428,19 @@
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
-          <t>eaa/tools/static.py · TC-07</t>
+          <t>eaa/tools/compile.py CompileGate · TC-40</t>
         </is>
       </c>
       <c r="G41" s="10" t="inlineStr">
         <is>
-          <t>Cổng chỉ chặn được thứ nó ĐƯỢC BẢO là cấm; im lặng ở đây là cho qua</t>
+          <t>Gộp dịch với liên kết làm mọi module trượt vì lý do chẳng liên quan tới chất lượng mã</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>N-053</t>
+          <t>N-052</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>Kiểm thử đơn vị trên máy chủ</t>
+          <t>Phân tích tĩnh theo ràng buộc dự án</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
@@ -4465,19 +4465,19 @@
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>eaa/tools/unittests.py host_gaps · TC-56f,g</t>
+          <t>eaa/tools/static.py · TC-07</t>
         </is>
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>Nhầm 'qua test trên máy chủ' với 'chạy đúng trên chip' là ngộ nhận tốn kém nhất</t>
+          <t>Cổng chỉ chặn được thứ nó ĐƯỢC BẢO là cấm; im lặng ở đây là cho qua</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>N-054</t>
+          <t>N-053</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>Đo chiếm dụng bộ nhớ</t>
+          <t>Kiểm thử đơn vị trên máy chủ</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
@@ -4502,19 +4502,19 @@
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
-          <t>eaa/tools/compile.py SizeGate + size_scope · TC-40d</t>
+          <t>eaa/tools/unittests.py host_gaps · TC-56f,g</t>
         </is>
       </c>
       <c r="G43" s="10" t="inlineStr">
         <is>
-          <t>Đo nhầm tầm làm ngân sách mất tác dụng đúng lúc cần nhất</t>
+          <t>Nhầm 'qua test trên máy chủ' với 'chạy đúng trên chip' là ngộ nhận tốn kém nhất</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>N-055</t>
+          <t>N-054</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>Vòng tự sửa khi cổng không đạt</t>
+          <t>Đo chiếm dụng bộ nhớ</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
@@ -4534,24 +4534,24 @@
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t>eaa/orchestrator.py · TC-06, TC-19</t>
+          <t>eaa/tools/compile.py SizeGate + size_scope · TC-40d</t>
         </is>
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>Đốt lượt sửa vào lỗi môi trường làm mất luôn cơ hội sửa lỗi thật</t>
+          <t>Đo nhầm tầm làm ngân sách mất tác dụng đúng lúc cần nhất</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>N-056</t>
+          <t>N-055</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>Review và hợp nhất</t>
+          <t>Vòng tự sửa khi cổng không đạt</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
@@ -4571,105 +4571,105 @@
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>eaa/gates.py + vcs.py content_digest · TC-01</t>
+          <t>eaa/orchestrator.py · TC-06, TC-19</t>
         </is>
       </c>
       <c r="G45" s="10" t="inlineStr">
         <is>
-          <t>Một nhánh thứ hai dẫn tới hợp nhất là chỗ mọi bất biến bị vô hiệu</t>
+          <t>Đốt lượt sửa vào lỗi môi trường làm mất luôn cơ hội sửa lỗi thật</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
+          <t>N-056</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>GĐ5 · Sinh mã &amp; kiểm chứng tĩnh</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>Review và hợp nhất</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E46" s="12" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F46" s="10" t="inlineStr">
+        <is>
+          <t>eaa/gates.py + vcs.py content_digest · TC-01</t>
+        </is>
+      </c>
+      <c r="G46" s="10" t="inlineStr">
+        <is>
+          <t>Một nhánh thứ hai dẫn tới hợp nhất là chỗ mọi bất biến bị vô hiệu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
           <t>N-057</t>
         </is>
       </c>
-      <c r="B46" s="10" t="inlineStr">
+      <c r="B47" s="10" t="inlineStr">
         <is>
           <t>GĐ5 · Sinh mã &amp; kiểm chứng tĩnh</t>
         </is>
       </c>
-      <c r="C46" s="10" t="inlineStr">
+      <c r="C47" s="10" t="inlineStr">
         <is>
           <t>Ghi nhận lỗi mô hình bịa ra</t>
         </is>
       </c>
-      <c r="D46" s="11" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E46" s="12" t="inlineStr">
+      <c r="D47" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E47" s="12" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="F46" s="10" t="inlineStr">
+      <c r="F47" s="10" t="inlineStr">
         <is>
           <t>eaa/ledger.py · TC-10</t>
         </is>
       </c>
-      <c r="G46" s="10" t="inlineStr">
+      <c r="G47" s="10" t="inlineStr">
         <is>
           <t>Không đo được tỉ lệ bịa thì không chứng minh được quy trình có tác dụng</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="9" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
         <is>
           <t>GĐ6 · Mô phỏng</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="10" t="inlineStr">
-        <is>
-          <t>N-060</t>
-        </is>
-      </c>
-      <c r="B48" s="10" t="inlineStr">
-        <is>
-          <t>GĐ6 · Mô phỏng</t>
-        </is>
-      </c>
-      <c r="C48" s="10" t="inlineStr">
-        <is>
-          <t>Dựng mô hình đối tượng điều khiển</t>
-        </is>
-      </c>
-      <c r="D48" s="11" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E48" s="12" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="F48" s="10" t="inlineStr">
-        <is>
-          <t>eaa/propose.py PlantModelProposal · TC-57f,g</t>
-        </is>
-      </c>
-      <c r="G48" s="10" t="inlineStr">
-        <is>
-          <t>Mô hình sai làm mọi kết quả mô phỏng thành vô nghĩa mà vẫn trông thuyết phục</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>N-061</t>
+          <t>N-060</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>Chạy mô phỏng vòng kín</t>
+          <t>Dựng mô hình đối tượng điều khiển</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
@@ -4689,24 +4689,24 @@
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="F49" s="10" t="inlineStr">
         <is>
-          <t>eaa/tools/sim.py, sim_runner.py · TC-12</t>
+          <t>eaa/propose.py PlantModelProposal · TC-57f,g</t>
         </is>
       </c>
       <c r="G49" s="10" t="inlineStr">
         <is>
-          <t>Chỉ số định nghĩa mơ hồ thì hai lần đo không so được với nhau</t>
+          <t>Mô hình sai làm mọi kết quả mô phỏng thành vô nghĩa mà vẫn trông thuyết phục</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>N-062</t>
+          <t>N-061</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>Quét tham số và đề xuất bộ tham số</t>
+          <t>Chạy mô phỏng vòng kín</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
@@ -4726,24 +4726,24 @@
       </c>
       <c r="E50" s="12" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t>eaa sim --sweep · TC-12</t>
+          <t>eaa/tools/sim.py, sim_runner.py · TC-12</t>
         </is>
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
-          <t>Tự chốt tham số là quyết định thay người ở chỗ ảnh hưởng trực tiếp tới an toàn</t>
+          <t>Chỉ số định nghĩa mơ hồ thì hai lần đo không so được với nhau</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>N-063</t>
+          <t>N-062</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>Tiêm lỗi trong mô phỏng</t>
+          <t>Quét tham số và đề xuất bộ tham số</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
@@ -4763,105 +4763,105 @@
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="F51" s="10" t="inlineStr">
         <is>
-          <t>sim_runner FaultSpec + require_safe_state · TC-57a..e</t>
+          <t>eaa sim --sweep · TC-12</t>
         </is>
       </c>
       <c r="G51" s="10" t="inlineStr">
         <is>
-          <t>Chỉ thử đường đi thuận là chỉ chứng minh hệ chạy khi không có gì hỏng</t>
+          <t>Tự chốt tham số là quyết định thay người ở chỗ ảnh hưởng trực tiếp tới an toàn</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
+          <t>N-063</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>GĐ6 · Mô phỏng</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>Tiêm lỗi trong mô phỏng</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E52" s="12" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="F52" s="10" t="inlineStr">
+        <is>
+          <t>sim_runner FaultSpec + require_safe_state · TC-57a..e</t>
+        </is>
+      </c>
+      <c r="G52" s="10" t="inlineStr">
+        <is>
+          <t>Chỉ thử đường đi thuận là chỉ chứng minh hệ chạy khi không có gì hỏng</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
           <t>N-064</t>
         </is>
       </c>
-      <c r="B52" s="10" t="inlineStr">
+      <c r="B53" s="10" t="inlineStr">
         <is>
           <t>GĐ6 · Mô phỏng</t>
         </is>
       </c>
-      <c r="C52" s="10" t="inlineStr">
+      <c r="C53" s="10" t="inlineStr">
         <is>
           <t>Chạy chính mã C sinh ra trong mô phỏng</t>
         </is>
       </c>
-      <c r="D52" s="14" t="inlineStr">
+      <c r="D53" s="14" t="inlineStr">
         <is>
           <t>CỐ Ý KHÔNG</t>
         </is>
       </c>
-      <c r="E52" s="12" t="inlineStr">
+      <c r="E53" s="12" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="F52" s="10" t="inlineStr">
+      <c r="F53" s="10" t="inlineStr">
         <is>
           <t>Cố ý để ngoài chuỗi tự động: nối vào mà không thật sự chạy artifact thì cổng sẽ 'đạt' mà chẳng kiểm gì.</t>
         </is>
       </c>
-      <c r="G52" s="10" t="inlineStr">
+      <c r="G53" s="10" t="inlineStr">
         <is>
           <t>Mô phỏng một bản chép tay rồi kết luận cho bản sẽ nạp là ngộ nhận âm thầm</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="9" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
         <is>
           <t>GĐ7 · Ráp &amp; nạp</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="10" t="inlineStr">
-        <is>
-          <t>N-070</t>
-        </is>
-      </c>
-      <c r="B54" s="10" t="inlineStr">
-        <is>
-          <t>GĐ7 · Ráp &amp; nạp</t>
-        </is>
-      </c>
-      <c r="C54" s="10" t="inlineStr">
-        <is>
-          <t>Ráp firmware hoàn chỉnh</t>
-        </is>
-      </c>
-      <c r="D54" s="11" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E54" s="12" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="F54" s="10" t="inlineStr">
-        <is>
-          <t>eaa/firmware.py + eaa build · TC-41</t>
-        </is>
-      </c>
-      <c r="G54" s="10" t="inlineStr">
-        <is>
-          <t>Firmware thiếu một module đã qua kiểm chứng là thứ mà mọi bằng chứng đều nói là có</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>N-071</t>
+          <t>N-070</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>Kiểm bộ nhớ ở tầm firmware</t>
+          <t>Ráp firmware hoàn chỉnh</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
@@ -4881,24 +4881,24 @@
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="F55" s="10" t="inlineStr">
         <is>
-          <t>budget.derived + stack_headroom_bytes_min · TC-53d</t>
+          <t>eaa/firmware.py + eaa build · TC-41</t>
         </is>
       </c>
       <c r="G55" s="10" t="inlineStr">
         <is>
-          <t>Tràn ngăn xếp là lỗi hiện ra ngẫu nhiên, rất khó lần ra nguyên nhân</t>
+          <t>Firmware thiếu một module đã qua kiểm chứng là thứ mà mọi bằng chứng đều nói là có</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>N-072</t>
+          <t>N-071</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>Kiểm trước khi nạp</t>
+          <t>Kiểm bộ nhớ ở tầm firmware</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
@@ -4918,24 +4918,24 @@
       </c>
       <c r="E56" s="12" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t>eaa/flash.py preflight · TC-42b</t>
+          <t>budget.derived + stack_headroom_bytes_min · TC-53d</t>
         </is>
       </c>
       <c r="G56" s="10" t="inlineStr">
         <is>
-          <t>Nạp ảnh cũ là cách hỏng âm thầm nhất: mạch chạy mã cũ, người đọc mã mới</t>
+          <t>Tràn ngăn xếp là lỗi hiện ra ngẫu nhiên, rất khó lần ra nguyên nhân</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>N-073</t>
+          <t>N-072</t>
         </is>
       </c>
       <c r="B57" s="10" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>Chọn đúng thiết bị để nạp</t>
+          <t>Kiểm trước khi nạp</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
@@ -4955,24 +4955,24 @@
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="F57" s="10" t="inlineStr">
         <is>
-          <t>eaa/serialport.py match_confirmed · TC-47d</t>
+          <t>eaa/flash.py preflight · TC-42b</t>
         </is>
       </c>
       <c r="G57" s="10" t="inlineStr">
         <is>
-          <t>Nạp nhầm thiết bị là hỏng thật, không phải một lượt chạy lại</t>
+          <t>Nạp ảnh cũ là cách hỏng âm thầm nhất: mạch chạy mã cũ, người đọc mã mới</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>N-074</t>
+          <t>N-073</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>Nạp và ghi nhật ký</t>
+          <t>Chọn đúng thiết bị để nạp</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
@@ -4992,105 +4992,105 @@
       </c>
       <c r="E58" s="12" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="F58" s="10" t="inlineStr">
         <is>
-          <t>eaa/flash.py + FlashLog · TC-42d</t>
+          <t>eaa/serialport.py match_confirmed · TC-47d</t>
         </is>
       </c>
       <c r="G58" s="10" t="inlineStr">
         <is>
-          <t>Không biết bản nào đang trên chip thì mọi số đo về sau đều mất neo</t>
+          <t>Nạp nhầm thiết bị là hỏng thật, không phải một lượt chạy lại</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
+          <t>N-074</t>
+        </is>
+      </c>
+      <c r="B59" s="10" t="inlineStr">
+        <is>
+          <t>GĐ7 · Ráp &amp; nạp</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t>Nạp và ghi nhật ký</t>
+        </is>
+      </c>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E59" s="12" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F59" s="10" t="inlineStr">
+        <is>
+          <t>eaa/flash.py + FlashLog · TC-42d</t>
+        </is>
+      </c>
+      <c r="G59" s="10" t="inlineStr">
+        <is>
+          <t>Không biết bản nào đang trên chip thì mọi số đo về sau đều mất neo</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
           <t>N-075</t>
         </is>
       </c>
-      <c r="B59" s="10" t="inlineStr">
+      <c r="B60" s="10" t="inlineStr">
         <is>
           <t>GĐ7 · Ráp &amp; nạp</t>
         </is>
       </c>
-      <c r="C59" s="10" t="inlineStr">
+      <c r="C60" s="10" t="inlineStr">
         <is>
           <t>Kiểm sau khi nạp</t>
         </is>
       </c>
-      <c r="D59" s="11" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E59" s="12" t="inlineStr">
+      <c r="D60" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E60" s="12" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="F59" s="10" t="inlineStr">
+      <c r="F60" s="10" t="inlineStr">
         <is>
           <t>eaa/flash.py VerifyResult + năng lực flash_verify · TC-52</t>
         </is>
       </c>
-      <c r="G59" s="10" t="inlineStr">
+      <c r="G60" s="10" t="inlineStr">
         <is>
           <t>Nạp lỗi một phần tạo ra hành vi kỳ quái không thể lần theo mã nguồn</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="9" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="9" t="inlineStr">
         <is>
           <t>GĐ8 · Đưa lên mạch &amp; đo</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="10" t="inlineStr">
-        <is>
-          <t>N-080</t>
-        </is>
-      </c>
-      <c r="B61" s="10" t="inlineStr">
-        <is>
-          <t>GĐ8 · Đưa lên mạch &amp; đo</t>
-        </is>
-      </c>
-      <c r="C61" s="10" t="inlineStr">
-        <is>
-          <t>Thiết lập kênh đo</t>
-        </is>
-      </c>
-      <c r="D61" s="11" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E61" s="12" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="F61" s="10" t="inlineStr">
-        <is>
-          <t>eaa/telemetry.py + eaa telemetry · TC-43</t>
-        </is>
-      </c>
-      <c r="G61" s="10" t="inlineStr">
-        <is>
-          <t>Phiên đo nhiều khung hỏng vẫn cho ra vài con số trông hợp lý</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>N-081</t>
+          <t>N-080</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>Sinh firmware đo cho từng kịch bản chẩn đoán</t>
+          <t>Thiết lập kênh đo</t>
         </is>
       </c>
       <c r="D62" s="11" t="inlineStr">
@@ -5110,24 +5110,24 @@
       </c>
       <c r="E62" s="12" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="F62" s="10" t="inlineStr">
         <is>
-          <t>đủ 6 kịch bản khai firmware_template · TC-58a</t>
+          <t>eaa/telemetry.py + eaa telemetry · TC-43</t>
         </is>
       </c>
       <c r="G62" s="10" t="inlineStr">
         <is>
-          <t>Firmware đo im lặng không phân biệt được với mạch hỏng</t>
+          <t>Phiên đo nhiều khung hỏng vẫn cho ra vài con số trông hợp lý</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>N-082</t>
+          <t>N-081</t>
         </is>
       </c>
       <c r="B63" s="10" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>Chẩn đoán hai kênh</t>
+          <t>Sinh firmware đo cho từng kịch bản chẩn đoán</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
@@ -5147,24 +5147,24 @@
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="F63" s="10" t="inlineStr">
         <is>
-          <t>eaa/diagnostics.py · TC-27</t>
+          <t>đủ 6 kịch bản khai firmware_template · TC-58a</t>
         </is>
       </c>
       <c r="G63" s="10" t="inlineStr">
         <is>
-          <t>Kết luận chỉ từ một kênh là đoán mò có vẻ khoa học</t>
+          <t>Firmware đo im lặng không phân biệt được với mạch hỏng</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>N-083</t>
+          <t>N-082</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>Đo đặc tính thời gian thực</t>
+          <t>Chẩn đoán hai kênh</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr">
@@ -5184,24 +5184,24 @@
       </c>
       <c r="E64" s="12" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="F64" s="10" t="inlineStr">
         <is>
-          <t>DS-06 đo cả trường hợp xấu nhất và tải CPU · TC-58b</t>
+          <t>eaa/diagnostics.py · TC-27</t>
         </is>
       </c>
       <c r="G64" s="10" t="inlineStr">
         <is>
-          <t>Trung bình đạt mà đỉnh trượt là lỗi chỉ xuất hiện lúc tải nặng</t>
+          <t>Kết luận chỉ từ một kênh là đoán mò có vẻ khoa học</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>N-084</t>
+          <t>N-083</t>
         </is>
       </c>
       <c r="B65" s="10" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>Đo điện và nhiệt</t>
+          <t>Đo đặc tính thời gian thực</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
@@ -5221,143 +5221,143 @@
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>T0</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="F65" s="10" t="inlineStr">
         <is>
-          <t>ManualMeasurement + eaa diagnose measure · TC-58c,d</t>
+          <t>DS-06 đo cả trường hợp xấu nhất và tải CPU · TC-58b</t>
         </is>
       </c>
       <c r="G65" s="10" t="inlineStr">
         <is>
-          <t>Sụt áp khi động cơ tăng tốc là nguyên nhân reset ngẫu nhiên rất hay bị bỏ sót</t>
+          <t>Trung bình đạt mà đỉnh trượt là lỗi chỉ xuất hiện lúc tải nặng</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
+          <t>N-084</t>
+        </is>
+      </c>
+      <c r="B66" s="10" t="inlineStr">
+        <is>
+          <t>GĐ8 · Đưa lên mạch &amp; đo</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>Đo điện và nhiệt</t>
+        </is>
+      </c>
+      <c r="D66" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E66" s="12" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="F66" s="10" t="inlineStr">
+        <is>
+          <t>ManualMeasurement + eaa diagnose measure · TC-58c,d</t>
+        </is>
+      </c>
+      <c r="G66" s="10" t="inlineStr">
+        <is>
+          <t>Sụt áp khi động cơ tăng tốc là nguyên nhân reset ngẫu nhiên rất hay bị bỏ sót</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
           <t>N-085</t>
         </is>
       </c>
-      <c r="B66" s="10" t="inlineStr">
+      <c r="B67" s="10" t="inlineStr">
         <is>
           <t>GĐ8 · Đưa lên mạch &amp; đo</t>
         </is>
       </c>
-      <c r="C66" s="10" t="inlineStr">
+      <c r="C67" s="10" t="inlineStr">
         <is>
           <t>Chẩn đoán sâu bằng công cụ gỡ lỗi</t>
         </is>
       </c>
-      <c r="D66" s="11" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E66" s="12" t="inlineStr">
+      <c r="D67" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E67" s="12" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="F66" s="10" t="inlineStr">
+      <c r="F67" s="10" t="inlineStr">
         <is>
           <t>eaa/debugsession.py + eaa debug plan/log/record · TC-75
 ⚠ Đủ Ở ĐÚNG MỨC T0 — 'người làm, Agent ghi vết'. Agent dò mạch gỡ lỗi, dựng kế hoạch phiên từ tiêu chí kịch bản đã duyệt (mỗi bước khai trước hai nhánh kết luận), và ghi lại ai làm gì. Nó KHÔNG chạy phiên gỡ lỗi — việc ấy đòi mạch cắm vào bo thật và vẫn ngoài phạm vi đề án. Tên trình gỡ lỗi nằm ở packs/*/pack.yaml, không ở engine.</t>
         </is>
       </c>
-      <c r="G66" s="10" t="inlineStr">
+      <c r="G67" s="10" t="inlineStr">
         <is>
           <t>Nhảy vào gỡ lỗi quá sớm tốn thời gian hơn đọc kỹ telemetry</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="10" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="10" t="inlineStr">
         <is>
           <t>N-086</t>
         </is>
       </c>
-      <c r="B67" s="10" t="inlineStr">
+      <c r="B68" s="10" t="inlineStr">
         <is>
           <t>GĐ8 · Đưa lên mạch &amp; đo</t>
         </is>
       </c>
-      <c r="C67" s="10" t="inlineStr">
+      <c r="C68" s="10" t="inlineStr">
         <is>
           <t>Kiểm độ bền dài hạn</t>
         </is>
       </c>
-      <c r="D67" s="11" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E67" s="12" t="inlineStr">
+      <c r="D68" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E68" s="12" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="F67" s="10" t="inlineStr">
+      <c r="F68" s="10" t="inlineStr">
         <is>
           <t>eaa/endurance.py + eaa endurance · TC-58e,f,g</t>
         </is>
       </c>
-      <c r="G67" s="10" t="inlineStr">
+      <c r="G68" s="10" t="inlineStr">
         <is>
           <t>Lỗi tích lũy (trôi, tràn bộ đếm) chỉ lộ ra sau thời gian dài</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="9" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="9" t="inlineStr">
         <is>
           <t>GĐ9 · Nghiệm thu &amp; phát hành</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="10" t="inlineStr">
-        <is>
-          <t>N-090</t>
-        </is>
-      </c>
-      <c r="B69" s="10" t="inlineStr">
-        <is>
-          <t>GĐ9 · Nghiệm thu &amp; phát hành</t>
-        </is>
-      </c>
-      <c r="C69" s="10" t="inlineStr">
-        <is>
-          <t>Đối chiếu tiêu chí nghiệm thu</t>
-        </is>
-      </c>
-      <c r="D69" s="11" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E69" s="12" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="F69" s="10" t="inlineStr">
-        <is>
-          <t>eaa/acceptance.py · TC-45</t>
-        </is>
-      </c>
-      <c r="G69" s="10" t="inlineStr">
-        <is>
-          <t>Tiêu chí viết sau khi nhìn số thì phép đối chiếu không còn nghĩa gì</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>N-091</t>
+          <t>N-090</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>Phong hạng chất lượng bản mã</t>
+          <t>Đối chiếu tiêu chí nghiệm thu</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr">
@@ -5382,19 +5382,19 @@
       </c>
       <c r="F70" s="10" t="inlineStr">
         <is>
-          <t>eaa/versions.py + check_device_commit · TC-30, TC-45a</t>
+          <t>eaa/acceptance.py · TC-45</t>
         </is>
       </c>
       <c r="G70" s="10" t="inlineStr">
         <is>
-          <t>Phong hạng cho bản chưa từng chạy trên chip làm hỏng mọi lần quay lui về sau</t>
+          <t>Tiêu chí viết sau khi nhìn số thì phép đối chiếu không còn nghĩa gì</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>N-092</t>
+          <t>N-091</t>
         </is>
       </c>
       <c r="B71" s="10" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>Giữ bản chạy tốt và quay lui</t>
+          <t>Phong hạng chất lượng bản mã</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
@@ -5414,24 +5414,24 @@
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="F71" s="10" t="inlineStr">
         <is>
-          <t>eaa/versions.py + eaa rollback · TC-30</t>
+          <t>eaa/versions.py + check_device_commit · TC-30, TC-45a</t>
         </is>
       </c>
       <c r="G71" s="10" t="inlineStr">
         <is>
-          <t>Không có đường lui thì một bản hỏng làm dừng cả kỳ thực nghiệm</t>
+          <t>Phong hạng cho bản chưa từng chạy trên chip làm hỏng mọi lần quay lui về sau</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>N-093</t>
+          <t>N-092</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>Xuất báo cáo và dấu vết</t>
+          <t>Giữ bản chạy tốt và quay lui</t>
         </is>
       </c>
       <c r="D72" s="11" t="inlineStr">
@@ -5456,175 +5456,175 @@
       </c>
       <c r="F72" s="10" t="inlineStr">
         <is>
-          <t>eaa/kpi.py + llm/calllog.py + registry.py · TC-09, TC-15</t>
+          <t>eaa/versions.py + eaa rollback · TC-30</t>
         </is>
       </c>
       <c r="G72" s="10" t="inlineStr">
         <is>
-          <t>Kết quả không truy vết được thì không bảo vệ được</t>
+          <t>Không có đường lui thì một bản hỏng làm dừng cả kỳ thực nghiệm</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
+          <t>N-093</t>
+        </is>
+      </c>
+      <c r="B73" s="10" t="inlineStr">
+        <is>
+          <t>GĐ9 · Nghiệm thu &amp; phát hành</t>
+        </is>
+      </c>
+      <c r="C73" s="10" t="inlineStr">
+        <is>
+          <t>Xuất báo cáo và dấu vết</t>
+        </is>
+      </c>
+      <c r="D73" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E73" s="12" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="F73" s="10" t="inlineStr">
+        <is>
+          <t>eaa/kpi.py + llm/calllog.py + registry.py · TC-09, TC-15</t>
+        </is>
+      </c>
+      <c r="G73" s="10" t="inlineStr">
+        <is>
+          <t>Kết quả không truy vết được thì không bảo vệ được</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="inlineStr">
+        <is>
           <t>N-094</t>
         </is>
       </c>
-      <c r="B73" s="10" t="inlineStr">
+      <c r="B74" s="10" t="inlineStr">
         <is>
           <t>GĐ9 · Nghiệm thu &amp; phát hành</t>
         </is>
       </c>
-      <c r="C73" s="10" t="inlineStr">
+      <c r="C74" s="10" t="inlineStr">
         <is>
           <t>Bàn giao tài liệu vận hành</t>
         </is>
       </c>
-      <c r="D73" s="11" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E73" s="12" t="inlineStr">
+      <c r="D74" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E74" s="12" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="F73" s="10" t="inlineStr">
+      <c r="F74" s="10" t="inlineStr">
         <is>
           <t>eaa/handover.py OperationsHandbook · TC-59a,b</t>
         </is>
       </c>
-      <c r="G73" s="10" t="inlineStr">
+      <c r="G74" s="10" t="inlineStr">
         <is>
           <t>Bàn giao thiếu giới hạn đã biết là đẩy rủi ro sang người tiếp nhận</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="9" t="inlineStr">
-        <is>
-          <t>GĐ10 · Vận hành &amp; bảo trì</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
+          <t>N-095</t>
+        </is>
+      </c>
+      <c r="B75" s="10" t="inlineStr">
+        <is>
+          <t>GĐ9 · Nghiệm thu &amp; phát hành</t>
+        </is>
+      </c>
+      <c r="C75" s="10" t="inlineStr">
+        <is>
+          <t>Sinh tài liệu thiết kế của chính dự án</t>
+        </is>
+      </c>
+      <c r="D75" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E75" s="12" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F75" s="10" t="inlineStr">
+        <is>
+          <t>eaa/docmodel.py (một bản vẽ, nhiều định dạng) + eaa/designdoc.py (URD/SRS/SDD, chức năng, luồng, rút TỪ HỒ SƠ chứ không hỏi mô hình) + eaa/office.py (docx/pptx/xlsx/md/pdf, không thêm phụ thuộc) + lệnh eaa design list/gen · SL-105, TC-82</t>
+        </is>
+      </c>
+      <c r="G75" s="10" t="inlineStr">
+        <is>
+          <t>Tài liệu viết tay tách khỏi mã ngay từ ngày thứ hai, và không ai biết bản nào đúng</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="9" t="inlineStr">
+        <is>
+          <t>GĐ10 · Vận hành &amp; bảo trì</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
           <t>N-100</t>
         </is>
       </c>
-      <c r="B75" s="10" t="inlineStr">
+      <c r="B77" s="10" t="inlineStr">
         <is>
           <t>GĐ10 · Vận hành &amp; bảo trì</t>
         </is>
       </c>
-      <c r="C75" s="10" t="inlineStr">
+      <c r="C77" s="10" t="inlineStr">
         <is>
           <t>Đánh giá ảnh hưởng khi tài liệu đổi</t>
         </is>
       </c>
-      <c r="D75" s="15" t="inlineStr">
+      <c r="D77" s="15" t="inlineStr">
         <is>
           <t>MỘT PHẦN</t>
         </is>
       </c>
-      <c r="E75" s="12" t="inlineStr">
+      <c r="E77" s="12" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="F75" s="10" t="inlineStr">
+      <c r="F77" s="10" t="inlineStr">
         <is>
           <t>eaa/lifecycle.py StaleSet · TC-29
 ⚠ Cùng gốc với N-036: sửa một datasheet hiện KHÔNG có lệnh nào trả lời 'mã nào bị ảnh hưởng'. Cần một lệnh (vd `eaa knowledge stale`) nối StaleSet vào đường người dùng</t>
         </is>
       </c>
-      <c r="G75" s="10" t="inlineStr">
+      <c r="G77" s="10" t="inlineStr">
         <is>
           <t>Không truy ngược được thì tài liệu đổi mà mã đứng yên</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="10" t="inlineStr">
-        <is>
-          <t>N-101</t>
-        </is>
-      </c>
-      <c r="B76" s="10" t="inlineStr">
-        <is>
-          <t>GĐ10 · Vận hành &amp; bảo trì</t>
-        </is>
-      </c>
-      <c r="C76" s="10" t="inlineStr">
-        <is>
-          <t>Đánh giá ảnh hưởng khi linh kiện đổi</t>
-        </is>
-      </c>
-      <c r="D76" s="11" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E76" s="12" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="F76" s="10" t="inlineStr">
-        <is>
-          <t>eaa/handover.py SwapAnalysis · TC-59c,d</t>
-        </is>
-      </c>
-      <c r="G76" s="10" t="inlineStr">
-        <is>
-          <t>Linh kiện 'tương đương' thường khác ở đúng chỗ dự án đang dùng</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="10" t="inlineStr">
-        <is>
-          <t>N-102</t>
-        </is>
-      </c>
-      <c r="B77" s="10" t="inlineStr">
-        <is>
-          <t>GĐ10 · Vận hành &amp; bảo trì</t>
-        </is>
-      </c>
-      <c r="C77" s="10" t="inlineStr">
-        <is>
-          <t>Chẩn đoán sự cố ngoài hiện trường</t>
-        </is>
-      </c>
-      <c r="D77" s="11" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E77" s="12" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="F77" s="10" t="inlineStr">
-        <is>
-          <t>eaa/diagnostics.py FieldCase · TC-59e,f</t>
-        </is>
-      </c>
-      <c r="G77" s="10" t="inlineStr">
-        <is>
-          <t>Kết luận vội cho sự cố không dựng lại được thường sửa nhầm chỗ</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>N-103</t>
+          <t>N-101</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>Cập nhật firmware cho thiết bị đã triển khai</t>
+          <t>Đánh giá ảnh hưởng khi linh kiện đổi</t>
         </is>
       </c>
       <c r="D78" s="11" t="inlineStr">
@@ -5644,105 +5644,105 @@
       </c>
       <c r="E78" s="12" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="F78" s="10" t="inlineStr">
         <is>
-          <t>eaa/handover.py RolloutPlan · TC-59g,h</t>
+          <t>eaa/handover.py SwapAnalysis · TC-59c,d</t>
         </is>
       </c>
       <c r="G78" s="10" t="inlineStr">
         <is>
-          <t>Cập nhật hỏng trên thiết bị ở xa là thiết bị mất luôn</t>
+          <t>Linh kiện 'tương đương' thường khác ở đúng chỗ dự án đang dùng</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="9" t="inlineStr">
-        <is>
-          <t>XS · Xuyên suốt</t>
+      <c r="A79" s="10" t="inlineStr">
+        <is>
+          <t>N-102</t>
+        </is>
+      </c>
+      <c r="B79" s="10" t="inlineStr">
+        <is>
+          <t>GĐ10 · Vận hành &amp; bảo trì</t>
+        </is>
+      </c>
+      <c r="C79" s="10" t="inlineStr">
+        <is>
+          <t>Chẩn đoán sự cố ngoài hiện trường</t>
+        </is>
+      </c>
+      <c r="D79" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E79" s="12" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F79" s="10" t="inlineStr">
+        <is>
+          <t>eaa/diagnostics.py FieldCase · TC-59e,f</t>
+        </is>
+      </c>
+      <c r="G79" s="10" t="inlineStr">
+        <is>
+          <t>Kết luận vội cho sự cố không dựng lại được thường sửa nhầm chỗ</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>N-900</t>
+          <t>N-103</t>
         </is>
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
+          <t>GĐ10 · Vận hành &amp; bảo trì</t>
+        </is>
+      </c>
+      <c r="C80" s="10" t="inlineStr">
+        <is>
+          <t>Cập nhật firmware cho thiết bị đã triển khai</t>
+        </is>
+      </c>
+      <c r="D80" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E80" s="12" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="F80" s="10" t="inlineStr">
+        <is>
+          <t>eaa/handover.py RolloutPlan · TC-59g,h</t>
+        </is>
+      </c>
+      <c r="G80" s="10" t="inlineStr">
+        <is>
+          <t>Cập nhật hỏng trên thiết bị ở xa là thiết bị mất luôn</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
+        <is>
           <t>XS · Xuyên suốt</t>
-        </is>
-      </c>
-      <c r="C80" s="10" t="inlineStr">
-        <is>
-          <t>Giữ ranh giới tổng quát / nền tảng / dự án</t>
-        </is>
-      </c>
-      <c r="D80" s="11" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E80" s="12" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
-      <c r="F80" s="10" t="inlineStr">
-        <is>
-          <t>TC-38 (quét mỗi commit) + TC-47a (không rẽ nhánh theo pack)</t>
-        </is>
-      </c>
-      <c r="G80" s="10" t="inlineStr">
-        <is>
-          <t>Mất ranh giới thì sản phẩm thành công cụ cho đúng một con chip</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="10" t="inlineStr">
-        <is>
-          <t>N-901</t>
-        </is>
-      </c>
-      <c r="B81" s="10" t="inlineStr">
-        <is>
-          <t>XS · Xuyên suốt</t>
-        </is>
-      </c>
-      <c r="C81" s="10" t="inlineStr">
-        <is>
-          <t>Bảo vệ khóa và bí mật</t>
-        </is>
-      </c>
-      <c r="D81" s="11" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E81" s="12" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
-      <c r="F81" s="10" t="inlineStr">
-        <is>
-          <t>eaa/llm/base.py mask_secrets · TC-14 + tests/conftest.py</t>
-        </is>
-      </c>
-      <c r="G81" s="10" t="inlineStr">
-        <is>
-          <t>Khóa lọt vào kho Git là sự cố không thu hồi được</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>N-902</t>
+          <t>N-900</t>
         </is>
       </c>
       <c r="B82" s="10" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="C82" s="10" t="inlineStr">
         <is>
-          <t>Không bao giờ hành động ngoài ý muốn người</t>
+          <t>Giữ ranh giới tổng quát / nền tảng / dự án</t>
         </is>
       </c>
       <c r="D82" s="11" t="inlineStr">
@@ -5762,24 +5762,24 @@
       </c>
       <c r="E82" s="12" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
-          <t>eaa/gates.py, doctor, flash — không cờ bỏ qua · TC-01, TC-42c</t>
+          <t>eaa/platform.py là interface DUY NHẤT engine gọi toolchain qua đó (FR-PLT-02, ADR-09) · TC-38 (quét mỗi commit) + TC-47a (không rẽ nhánh theo pack)</t>
         </is>
       </c>
       <c r="G82" s="10" t="inlineStr">
         <is>
-          <t>Một cờ bỏ qua tồn tại là một cờ sẽ được dùng lúc vội</t>
+          <t>Mất ranh giới thì sản phẩm thành công cụ cho đúng một con chip</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>N-903</t>
+          <t>N-901</t>
         </is>
       </c>
       <c r="B83" s="10" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>Nói rõ mức tin cậy của mọi điều mình nói</t>
+          <t>Bảo vệ khóa và bí mật</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
@@ -5804,19 +5804,19 @@
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
-          <t>eaa/confidence.py + Judged · TC-60a-c, TC-63a-e</t>
+          <t>eaa/llm/base.py mask_secrets · TC-14 + tests/conftest.py</t>
         </is>
       </c>
       <c r="G83" s="10" t="inlineStr">
         <is>
-          <t>Một dòng 'không khớp' sai tệ hơn một dòng 'không nhận diện được' đúng</t>
+          <t>Khóa lọt vào kho Git là sự cố không thu hồi được</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>N-904</t>
+          <t>N-902</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>Quản lý chi phí gọi mô hình</t>
+          <t>Không bao giờ hành động ngoài ý muốn người</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr">
@@ -5836,24 +5836,24 @@
       </c>
       <c r="E84" s="12" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="F84" s="10" t="inlineStr">
         <is>
-          <t>eaa/budget.py TokenBudget · TC-53e,f</t>
+          <t>eaa/gates.py, doctor, flash — không cờ bỏ qua · TC-01, TC-42c</t>
         </is>
       </c>
       <c r="G84" s="10" t="inlineStr">
         <is>
-          <t>Chi phí không đo được thì không tối ưu được, và dễ vượt ngoài dự tính</t>
+          <t>Một cờ bỏ qua tồn tại là một cờ sẽ được dùng lúc vội</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>N-905</t>
+          <t>N-903</t>
         </is>
       </c>
       <c r="B85" s="10" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="C85" s="10" t="inlineStr">
         <is>
-          <t>Ghi nhận mọi sai lệch so với thiết kế</t>
+          <t>Nói rõ mức tin cậy của mọi điều mình nói</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
@@ -5873,24 +5873,24 @@
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
-          <t>eaa/deviation.py + eaa deviations · TC-60d,e,f</t>
+          <t>eaa/confidence.py + Judged · TC-60a-c, TC-63a-e</t>
         </is>
       </c>
       <c r="G85" s="10" t="inlineStr">
         <is>
-          <t>Lệch ngầm làm tài liệu và mã kể hai câu chuyện khác nhau</t>
+          <t>Một dòng 'không khớp' sai tệ hơn một dòng 'không nhận diện được' đúng</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>N-906</t>
+          <t>N-904</t>
         </is>
       </c>
       <c r="B86" s="10" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="C86" s="10" t="inlineStr">
         <is>
-          <t>Tự đánh giá và cải tiến quy trình</t>
+          <t>Quản lý chi phí gọi mô hình</t>
         </is>
       </c>
       <c r="D86" s="11" t="inlineStr">
@@ -5910,24 +5910,24 @@
       </c>
       <c r="E86" s="12" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t>kpi.weak_points + eaa report review · TC-60g,h,i</t>
+          <t>eaa/budget.py TokenBudget · TC-53e,f</t>
         </is>
       </c>
       <c r="G86" s="10" t="inlineStr">
         <is>
-          <t>Không đo thì mọi cải tiến chỉ là cảm giác</t>
+          <t>Chi phí không đo được thì không tối ưu được, và dễ vượt ngoài dự tính</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>N-907</t>
+          <t>N-905</t>
         </is>
       </c>
       <c r="B87" s="10" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>Khôi phục sau gián đoạn</t>
+          <t>Ghi nhận mọi sai lệch so với thiết kế</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
@@ -5947,24 +5947,24 @@
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
-          <t>eaa/state.py ghi nguyên tử + eaa resume · TC-03</t>
+          <t>eaa/deviation.py + eaa deviations · TC-60d,e,f</t>
         </is>
       </c>
       <c r="G87" s="10" t="inlineStr">
         <is>
-          <t>Mất trạng thái giữa chừng làm hỏng cả chuỗi dấu vết</t>
+          <t>Lệch ngầm làm tài liệu và mã kể hai câu chuyện khác nhau</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
         <is>
-          <t>N-908</t>
+          <t>N-906</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
@@ -5974,12 +5974,12 @@
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>Phân biệt 'mã tôi sai' với 'bài kiểm tôi sai'</t>
-        </is>
-      </c>
-      <c r="D88" s="16" t="inlineStr">
-        <is>
-          <t>CHƯA</t>
+          <t>Tự đánh giá và cải tiến quy trình</t>
+        </is>
+      </c>
+      <c r="D88" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
         </is>
       </c>
       <c r="E88" s="12" t="inlineStr">
@@ -5989,216 +5989,364 @@
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t>Chưa có gì. Bốn cổng đo mã CÓ CHẠY KHÔNG, không đo mã có ĐANG ĐO ĐÚNG THỨ nó nhận không. Bằng chứng: 3/12 lần từ chối G3 (drv_imu, logic_pid, app_balance) · §3.1</t>
+          <t>kpi.weak_points + eaa report review · TC-60g,h,i</t>
         </is>
       </c>
       <c r="G88" s="10" t="inlineStr">
         <is>
-          <t>Ba trong 12 lần từ chối G3 là mã tự chỉnh cho vừa đồ đo của chính nó, và cả ba qua sạch bốn cổng</t>
+          <t>Không đo thì mọi cải tiến chỉ là cảm giác</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
+          <t>N-907</t>
+        </is>
+      </c>
+      <c r="B89" s="10" t="inlineStr">
+        <is>
+          <t>XS · Xuyên suốt</t>
+        </is>
+      </c>
+      <c r="C89" s="10" t="inlineStr">
+        <is>
+          <t>Khôi phục sau gián đoạn</t>
+        </is>
+      </c>
+      <c r="D89" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E89" s="12" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="F89" s="10" t="inlineStr">
+        <is>
+          <t>eaa/state.py ghi nguyên tử + eaa resume · TC-03</t>
+        </is>
+      </c>
+      <c r="G89" s="10" t="inlineStr">
+        <is>
+          <t>Mất trạng thái giữa chừng làm hỏng cả chuỗi dấu vết</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="10" t="inlineStr">
+        <is>
+          <t>N-914</t>
+        </is>
+      </c>
+      <c r="B90" s="10" t="inlineStr">
+        <is>
+          <t>XS · Xuyên suốt</t>
+        </is>
+      </c>
+      <c r="C90" s="10" t="inlineStr">
+        <is>
+          <t>Người chọn mô hình, hệ không tự chọn</t>
+        </is>
+      </c>
+      <c r="D90" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E90" s="12" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F90" s="10" t="inlineStr">
+        <is>
+          <t>eaa/llm/catalog.py CATALOG + KHUYEN_NGHI (là LỜI KHUYÊN in ra, không có mã nào đọc nó để quyết định) + lệnh eaa models; mặc định ghim trong Project State, cờ --model đổi tại chỗ dùng · SL-103, SL-170, TC-80, TC-130</t>
+        </is>
+      </c>
+      <c r="G90" s="10" t="inlineStr">
+        <is>
+          <t>Tự đổi model giữa chừng phá tính tái lập: hai lần chạy cùng một lệnh rơi vào hai model, và lúc kết quả lệch thì không biết lệch vì model hay vì đầu vào</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="10" t="inlineStr">
+        <is>
+          <t>N-915</t>
+        </is>
+      </c>
+      <c r="B91" s="10" t="inlineStr">
+        <is>
+          <t>XS · Xuyên suốt</t>
+        </is>
+      </c>
+      <c r="C91" s="10" t="inlineStr">
+        <is>
+          <t>Hoán đổi nhà cung cấp mô hình mà hành vi không đổi</t>
+        </is>
+      </c>
+      <c r="D91" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E91" s="12" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="F91" s="10" t="inlineStr">
+        <is>
+          <t>eaa/llm/base.py là giao diện chung; ba adapter eaa/llm/gemini.py, mock.py và ReplayClient trong calllog.py — bản phát lại cố ý KHÔNG bịa phản hồi khi trượt băm · TC-11, TC-15</t>
+        </is>
+      </c>
+      <c r="G91" s="10" t="inlineStr">
+        <is>
+          <t>Khóa vào một nhà cung cấp là đặt cả đề án vào tay một bảng giá và một lịch ngừng dịch vụ</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="10" t="inlineStr">
+        <is>
+          <t>N-908</t>
+        </is>
+      </c>
+      <c r="B92" s="10" t="inlineStr">
+        <is>
+          <t>XS · Xuyên suốt</t>
+        </is>
+      </c>
+      <c r="C92" s="10" t="inlineStr">
+        <is>
+          <t>Phân biệt 'mã tôi sai' với 'bài kiểm tôi sai'</t>
+        </is>
+      </c>
+      <c r="D92" s="16" t="inlineStr">
+        <is>
+          <t>CHƯA</t>
+        </is>
+      </c>
+      <c r="E92" s="12" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="F92" s="10" t="inlineStr">
+        <is>
+          <t>Chưa có gì. Bốn cổng đo mã CÓ CHẠY KHÔNG, không đo mã có ĐANG ĐO ĐÚNG THỨ nó nhận không. Bằng chứng: 3/12 lần từ chối G3 (drv_imu, logic_pid, app_balance) · §3.1</t>
+        </is>
+      </c>
+      <c r="G92" s="10" t="inlineStr">
+        <is>
+          <t>Ba trong 12 lần từ chối G3 là mã tự chỉnh cho vừa đồ đo của chính nó, và cả ba qua sạch bốn cổng</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="10" t="inlineStr">
+        <is>
           <t>N-909</t>
         </is>
       </c>
-      <c r="B89" s="10" t="inlineStr">
+      <c r="B93" s="10" t="inlineStr">
         <is>
           <t>XS · Xuyên suốt</t>
         </is>
       </c>
-      <c r="C89" s="10" t="inlineStr">
+      <c r="C93" s="10" t="inlineStr">
         <is>
           <t>Phát hiện bài kiểm KHÔNG chứng minh điều nó nhận là mình chứng minh</t>
         </is>
       </c>
-      <c r="D89" s="15" t="inlineStr">
+      <c r="D93" s="15" t="inlineStr">
         <is>
           <t>MỘT PHẦN</t>
         </is>
       </c>
-      <c r="E89" s="12" t="inlineStr">
+      <c r="E93" s="12" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="F89" s="10" t="inlineStr">
+      <c r="F93" s="10" t="inlineStr">
         <is>
           <t>eaa/sensitivity.py chạy bộ kiểm MỚI trên mã CŨ trong bản sao tạm; kết quả vào nhật ký, KPI test_sensitivity, và đầu checklist G3 (SL-168, TC-128, 28 bài)
 ⚠ Bắt được hạng NHẸ HƠN hạng đã sinh ra nó: bài kiểm không phân biệt được gì. Ca deadband vẫn đỏ trên mã cũ vì lý do khác nên vẫn QUA được phép đo — phần ấy còn cần người đọc ở G3</t>
         </is>
       </c>
-      <c r="G89" s="10" t="inlineStr">
+      <c r="G93" s="10" t="inlineStr">
         <is>
           <t>Bài kiểm đỏ đúng lúc rồi xanh đúng lúc — vì một lý do khác — nguy hiểm hơn bài kiểm đỏ, vì lần sau không ai đọc lại nó nữa (§3.8)</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="10" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="10" t="inlineStr">
         <is>
           <t>N-910</t>
         </is>
       </c>
-      <c r="B90" s="10" t="inlineStr">
+      <c r="B94" s="10" t="inlineStr">
         <is>
           <t>XS · Xuyên suốt</t>
         </is>
       </c>
-      <c r="C90" s="10" t="inlineStr">
+      <c r="C94" s="10" t="inlineStr">
         <is>
           <t>Canh thoái lui giữa các lượt sinh của cùng một module</t>
         </is>
       </c>
-      <c r="D90" s="11" t="inlineStr">
-        <is>
-          <t>ĐỦ</t>
-        </is>
-      </c>
-      <c r="E90" s="12" t="inlineStr">
+      <c r="D94" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
+        </is>
+      </c>
+      <c r="E94" s="12" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="F90" s="10" t="inlineStr">
+      <c r="F94" s="10" t="inlineStr">
         <is>
           <t>eaa/contract.py: pha_vo_hop_dong so chữ ký header (SL-163, TC-124) + mat_loi_goi so tập lời gọi LIÊN MODULE của tệp .c với bản đã merge (SL-167, TC-127, 33 bài)</t>
         </is>
       </c>
-      <c r="G90" s="10" t="inlineStr">
+      <c r="G94" s="10" t="inlineStr">
         <is>
           <t>app_init() mất bốn lời gọi khởi tạo driver sau một vòng vá → firmware câm, 33 bài kiểm vẫn xanh</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="10" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="10" t="inlineStr">
         <is>
           <t>N-911</t>
         </is>
       </c>
-      <c r="B91" s="10" t="inlineStr">
+      <c r="B95" s="10" t="inlineStr">
         <is>
           <t>XS · Xuyên suốt</t>
         </is>
       </c>
-      <c r="C91" s="10" t="inlineStr">
+      <c r="C95" s="10" t="inlineStr">
         <is>
           <t>Kiểm chú thích số học có đúng thứ nguyên không</t>
         </is>
       </c>
-      <c r="D91" s="16" t="inlineStr">
+      <c r="D95" s="16" t="inlineStr">
         <is>
           <t>CHƯA</t>
         </is>
       </c>
-      <c r="E91" s="12" t="inlineStr">
+      <c r="E95" s="12" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="F91" s="10" t="inlineStr">
+      <c r="F95" s="10" t="inlineStr">
         <is>
           <t>Chưa có gì. Hồ sơ phần cứng đã khai đơn vị của từng đại lượng, nên dữ liệu để làm thì có sẵn. Bằng chứng: chú thích '4ms / 0.000031s = 129' · §3.4</t>
         </is>
       </c>
-      <c r="G91" s="10" t="inlineStr">
+      <c r="G95" s="10" t="inlineStr">
         <is>
           <t>'4ms per step / 0.000031s per sample = 129' chia chu kỳ cho một hệ số ĐỘ TRÊN LSB. Con số vô nghĩa, chú thích nghe hợp lý, và nó là nguyên nhân robot không lấy đủ mẫu</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="10" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="10" t="inlineStr">
         <is>
           <t>N-912</t>
         </is>
       </c>
-      <c r="B92" s="10" t="inlineStr">
+      <c r="B96" s="10" t="inlineStr">
         <is>
           <t>XS · Xuyên suốt</t>
         </is>
       </c>
-      <c r="C92" s="10" t="inlineStr">
+      <c r="C96" s="10" t="inlineStr">
         <is>
           <t>Thiết kế khả quan sát — làm cho lỗi kêu lên được</t>
         </is>
       </c>
-      <c r="D92" s="16" t="inlineStr">
+      <c r="D96" s="16" t="inlineStr">
         <is>
           <t>CHƯA</t>
         </is>
       </c>
-      <c r="E92" s="12" t="inlineStr">
+      <c r="E96" s="12" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="F92" s="10" t="inlineStr">
+      <c r="F96" s="10" t="inlineStr">
         <is>
           <t>Chưa có gì. eaa/decompose.py chưa đòi module khai dấu hiệu sống/hỏng; eaa/propose.py AcceptanceProposal chưa sinh tiêu chí quan sát được bằng mắt/tai · §3.6</t>
         </is>
       </c>
-      <c r="G92" s="10" t="inlineStr">
+      <c r="G96" s="10" t="inlineStr">
         <is>
           <t>Ba lượt nạp đầu robot chỉ 'im' hoặc 'ngã', không phân biệt được với chip chết. Mọi cải tiến quan sát — nhịp bíp, nút thoát, watchdog mất mẫu — đều do người thêm</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="10" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="10" t="inlineStr">
         <is>
           <t>N-913</t>
         </is>
       </c>
-      <c r="B93" s="10" t="inlineStr">
+      <c r="B97" s="10" t="inlineStr">
         <is>
           <t>XS · Xuyên suốt</t>
         </is>
       </c>
-      <c r="C93" s="10" t="inlineStr">
+      <c r="C97" s="10" t="inlineStr">
         <is>
           <t>Đưa số đo từ phần cứng ngược vào prompt</t>
         </is>
       </c>
-      <c r="D93" s="16" t="inlineStr">
+      <c r="D97" s="16" t="inlineStr">
         <is>
           <t>CHƯA</t>
         </is>
       </c>
-      <c r="E93" s="12" t="inlineStr">
+      <c r="E97" s="12" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="F93" s="10" t="inlineStr">
+      <c r="F97" s="10" t="inlineStr">
         <is>
           <t>Chưa có gì. measurements.jsonl và kết quả DS-xx nằm NGOÀI eaa/composer.py. Đây là mục đắt nhất trong sáu mục, vì nó đụng vào bộ ghép prompt và vào gate tri thức · §3.7</t>
         </is>
       </c>
-      <c r="G93" s="10" t="inlineStr">
+      <c r="G97" s="10" t="inlineStr">
         <is>
           <t>Bài học từ bo hiện chỉ tới mô hình qua LÝ DO TỪ CHỐI kỹ sư gõ tay — mất là mất hẳn</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G93"/>
+  <autoFilter ref="A1:G97"/>
   <mergeCells count="12">
-    <mergeCell ref="A68:G68"/>
-    <mergeCell ref="A74:G74"/>
+    <mergeCell ref="A61:G61"/>
     <mergeCell ref="A18:G18"/>
     <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A79:G79"/>
-    <mergeCell ref="A53:G53"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A69:G69"/>
+    <mergeCell ref="A48:G48"/>
     <mergeCell ref="A24:G24"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A38:G38"/>
-    <mergeCell ref="A60:G60"/>
-    <mergeCell ref="A33:G33"/>
-    <mergeCell ref="A47:G47"/>
+    <mergeCell ref="A54:G54"/>
+    <mergeCell ref="A81:G81"/>
+    <mergeCell ref="A76:G76"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/EAA_Bang_nang_luc.xlsx
+++ b/docs/EAA_Bang_nang_luc.xlsx
@@ -827,7 +827,7 @@
       <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Nó không chạy thử năng lực nào — nó đối chiếu khung với mã. Câu 'nó chạy đúng không' thuộc về bộ test (2248 hàm test trong 120 tệp) và scripts/kiem_on_dinh.py.</t>
+          <t>Nó không chạy thử năng lực nào — nó đối chiếu khung với mã. Câu 'nó chạy đúng không' thuộc về bộ test (2273 hàm test trong 121 tệp) và scripts/kiem_on_dinh.py.</t>
         </is>
       </c>
     </row>
@@ -6125,9 +6125,9 @@
           <t>Phân biệt 'mã tôi sai' với 'bài kiểm tôi sai'</t>
         </is>
       </c>
-      <c r="D92" s="16" t="inlineStr">
-        <is>
-          <t>CHƯA</t>
+      <c r="D92" s="15" t="inlineStr">
+        <is>
+          <t>MỘT PHẦN</t>
         </is>
       </c>
       <c r="E92" s="12" t="inlineStr">
@@ -6137,7 +6137,8 @@
       </c>
       <c r="F92" s="10" t="inlineStr">
         <is>
-          <t>Chưa có gì. Bốn cổng đo mã CÓ CHẠY KHÔNG, không đo mã có ĐANG ĐO ĐÚNG THỨ nó nhận không. Bằng chứng: 3/12 lần từ chối G3 (drv_imu, logic_pid, app_balance) · §3.1</t>
+          <t>eaa/instrument.py dò ba DẤU VẾT trên mỗi bản vá: hằng số trong hàm mang // ref: bị đổi; mã vừa mọc nhánh nhận đúng con số của bài kiểm; chú thích tự khai. Thấy dấu vết thì DỪNG vòng vá và đưa câu hỏi về cho người (SL-171, TC-131, 25 bài)
+⚠ Dò DẤU VẾT, không kiểm vật lý. Câu 'con số nào mới đúng' đòi biết bài toán, và chỗ ấy vẫn là người phân xử — đúng mức tự chủ T1 mà nghiệp vụ này khai</t>
         </is>
       </c>
       <c r="G92" s="10" t="inlineStr">
@@ -6422,14 +6423,14 @@
           <t>Phân biệt 'mã tôi sai' với 'bài kiểm tôi sai'</t>
         </is>
       </c>
-      <c r="E2" s="16" t="inlineStr">
-        <is>
-          <t>CHƯA</t>
+      <c r="E2" s="15" t="inlineStr">
+        <is>
+          <t>MỘT PHẦN</t>
         </is>
       </c>
       <c r="F2" s="10" t="inlineStr">
         <is>
-          <t>Chưa có gì. Bốn cổng đo mã CÓ CHẠY KHÔNG, không đo mã có ĐANG ĐO ĐÚNG THỨ nó nhận không. Bằng chứng: 3/12 lần từ chối G3 (drv_imu, logic_pid, app_balance) · §3.1</t>
+          <t>Dò DẤU VẾT, không kiểm vật lý. Câu 'con số nào mới đúng' đòi biết bài toán, và chỗ ấy vẫn là người phân xử — đúng mức tự chủ T1 mà nghiệp vụ này khai</t>
         </is>
       </c>
     </row>

--- a/docs/EAA_Bang_nang_luc.xlsx
+++ b/docs/EAA_Bang_nang_luc.xlsx
@@ -16,8 +16,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Năng lực nền'!$A$1:$G$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Năng lực nhúng'!$A$1:$G$97</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Khoảng trống'!$A$1:$F$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Bản đồ lệnh'!$A$1:$E$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Khoảng trống'!$A$1:$F$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Bản đồ lệnh'!$A$1:$E$86</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -827,7 +827,7 @@
       <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Nó không chạy thử năng lực nào — nó đối chiếu khung với mã. Câu 'nó chạy đúng không' thuộc về bộ test (2273 hàm test trong 121 tệp) và scripts/kiem_on_dinh.py.</t>
+          <t>Nó không chạy thử năng lực nào — nó đối chiếu khung với mã. Câu 'nó chạy đúng không' thuộc về bộ test (2286 hàm test trong 122 tệp) và scripts/kiem_on_dinh.py.</t>
         </is>
       </c>
     </row>
@@ -4105,9 +4105,9 @@
           <t>Quản lý vòng đời tri thức</t>
         </is>
       </c>
-      <c r="D31" s="15" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
@@ -4117,8 +4117,7 @@
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
-          <t>eaa/lifecycle.py KnowledgeLifecycle (3 đường truy ngược) · TC-29
-⚠ Rà soát 04/09: KHÔNG module nào trong eaa/ import lifecycle, và không lệnh CLI nào gọi tới. `eaa docs regen` đi qua registry, không qua vòng đời tri thức. Cơ chế đúng, đường chạy chưa có</t>
+          <t>eaa/lifecycle.py KnowledgeLifecycle (3 đường truy ngược) + lệnh eaa knowledge supersede/deprecate — đòi quyết định G2, hạ module xuống 'stale' trong cùng lệnh, KHÔNG tự mở vòng sinh lại · TC-29, SL-172, TC-132</t>
         </is>
       </c>
       <c r="G31" s="10" t="inlineStr">
@@ -5599,9 +5598,9 @@
           <t>Đánh giá ảnh hưởng khi tài liệu đổi</t>
         </is>
       </c>
-      <c r="D77" s="15" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
+      <c r="D77" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
         </is>
       </c>
       <c r="E77" s="12" t="inlineStr">
@@ -5611,8 +5610,7 @@
       </c>
       <c r="F77" s="10" t="inlineStr">
         <is>
-          <t>eaa/lifecycle.py StaleSet · TC-29
-⚠ Cùng gốc với N-036: sửa một datasheet hiện KHÔNG có lệnh nào trả lời 'mã nào bị ảnh hưởng'. Cần một lệnh (vd `eaa knowledge stale`) nối StaleSet vào đường người dùng</t>
+          <t>eaa knowledge stale &lt;chunk&gt; — CHỈ ĐỌC, hợp ba đường (đồ thị · trích dẫn // ref: trong mã · chunk-ids của commit), gắn nhãn SUY RA vì đường đồ thị mù khi khai báo uses thiếu. Có trong TOOLBOX ở nhóm chỉ đọc · SL-172, TC-132</t>
         </is>
       </c>
       <c r="G77" s="10" t="inlineStr">
@@ -6359,7 +6357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -6474,7 +6472,7 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>N-036</t>
+          <t>N-911</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
@@ -6484,17 +6482,17 @@
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>Quản lý vòng đời tri thức</t>
-        </is>
-      </c>
-      <c r="E4" s="15" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
+          <t>Kiểm chú thích số học có đúng thứ nguyên không</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>CHƯA</t>
         </is>
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
-          <t>Rà soát 04/09: KHÔNG module nào trong eaa/ import lifecycle, và không lệnh CLI nào gọi tới. `eaa docs regen` đi qua registry, không qua vòng đời tri thức. Cơ chế đúng, đường chạy chưa có</t>
+          <t>Chưa có gì. Hồ sơ phần cứng đã khai đơn vị của từng đại lượng, nên dữ liệu để làm thì có sẵn. Bằng chứng: chú thích '4ms / 0.000031s = 129' · §3.4</t>
         </is>
       </c>
     </row>
@@ -6506,7 +6504,7 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>N-100</t>
+          <t>N-912</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
@@ -6516,17 +6514,17 @@
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>Đánh giá ảnh hưởng khi tài liệu đổi</t>
-        </is>
-      </c>
-      <c r="E5" s="15" t="inlineStr">
-        <is>
-          <t>MỘT PHẦN</t>
+          <t>Thiết kế khả quan sát — làm cho lỗi kêu lên được</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>CHƯA</t>
         </is>
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
-          <t>Cùng gốc với N-036: sửa một datasheet hiện KHÔNG có lệnh nào trả lời 'mã nào bị ảnh hưởng'. Cần một lệnh (vd `eaa knowledge stale`) nối StaleSet vào đường người dùng</t>
+          <t>Chưa có gì. eaa/decompose.py chưa đòi module khai dấu hiệu sống/hỏng; eaa/propose.py AcceptanceProposal chưa sinh tiêu chí quan sát được bằng mắt/tai · §3.6</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6536,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>N-911</t>
+          <t>N-913</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -6548,7 +6546,7 @@
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>Kiểm chú thích số học có đúng thứ nguyên không</t>
+          <t>Đưa số đo từ phần cứng ngược vào prompt</t>
         </is>
       </c>
       <c r="E6" s="16" t="inlineStr">
@@ -6558,76 +6556,12 @@
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
-          <t>Chưa có gì. Hồ sơ phần cứng đã khai đơn vị của từng đại lượng, nên dữ liệu để làm thì có sẵn. Bằng chứng: chú thích '4ms / 0.000031s = 129' · §3.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>Vừa</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>N-912</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>nhúng</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>Thiết kế khả quan sát — làm cho lỗi kêu lên được</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>CHƯA</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>Chưa có gì. eaa/decompose.py chưa đòi module khai dấu hiệu sống/hỏng; eaa/propose.py AcceptanceProposal chưa sinh tiêu chí quan sát được bằng mắt/tai · §3.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>Vừa</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>N-913</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>nhúng</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>Đưa số đo từ phần cứng ngược vào prompt</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>CHƯA</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
           <t>Chưa có gì. measurements.jsonl và kết quả DS-xx nằm NGOÀI eaa/composer.py. Đây là mục đắt nhất trong sáu mục, vì nó đụng vào bộ ghép prompt và vào gate tri thức · §3.7</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F8"/>
+  <autoFilter ref="A1:F6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6638,7 +6572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E85"/>
+  <dimension ref="A1:E86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7322,7 +7256,7 @@
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>ledger list</t>
+          <t>knowledge stale</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
@@ -7345,7 +7279,7 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>memory add</t>
+          <t>ledger list</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
@@ -7355,12 +7289,12 @@
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E31" s="10" t="inlineStr"/>
@@ -7368,7 +7302,7 @@
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>memory list</t>
+          <t>memory add</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
@@ -7378,7 +7312,7 @@
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>có</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
@@ -7391,7 +7325,7 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>models</t>
+          <t>memory list</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
@@ -7406,7 +7340,7 @@
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr"/>
@@ -7414,7 +7348,7 @@
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>models</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
@@ -7429,7 +7363,7 @@
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr"/>
@@ -7437,7 +7371,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>plan add</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
@@ -7447,12 +7381,12 @@
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E35" s="10" t="inlineStr"/>
@@ -7460,7 +7394,7 @@
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>plan list</t>
+          <t>plan add</t>
         </is>
       </c>
       <c r="B36" s="11" t="inlineStr">
@@ -7470,7 +7404,7 @@
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>có</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
@@ -7483,7 +7417,7 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>playbook list</t>
+          <t>plan list</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
@@ -7498,7 +7432,7 @@
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E37" s="10" t="inlineStr"/>
@@ -7506,7 +7440,7 @@
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>playbook lookup</t>
+          <t>playbook list</t>
         </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
@@ -7529,7 +7463,7 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>playbook record</t>
+          <t>playbook lookup</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
@@ -7539,7 +7473,7 @@
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
@@ -7552,7 +7486,7 @@
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>policy</t>
+          <t>playbook record</t>
         </is>
       </c>
       <c r="B40" s="11" t="inlineStr">
@@ -7562,7 +7496,7 @@
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>có</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
@@ -7575,7 +7509,7 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>propose acceptance</t>
+          <t>policy</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
@@ -7590,7 +7524,7 @@
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E41" s="10" t="inlineStr"/>
@@ -7598,7 +7532,7 @@
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>propose constraints</t>
+          <t>propose acceptance</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
@@ -7621,7 +7555,7 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>propose pinmap</t>
+          <t>propose constraints</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
@@ -7644,7 +7578,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>propose plant</t>
+          <t>propose pinmap</t>
         </is>
       </c>
       <c r="B44" s="11" t="inlineStr">
@@ -7667,7 +7601,7 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>propose scope</t>
+          <t>propose plant</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
@@ -7677,7 +7611,7 @@
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
@@ -7690,7 +7624,7 @@
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>propose scope</t>
         </is>
       </c>
       <c r="B46" s="11" t="inlineStr">
@@ -7700,12 +7634,12 @@
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>có</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E46" s="10" t="inlineStr"/>
@@ -7713,7 +7647,7 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>read</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
@@ -7728,7 +7662,7 @@
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E47" s="10" t="inlineStr"/>
@@ -7736,7 +7670,7 @@
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>report kpi</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="B48" s="11" t="inlineStr">
@@ -7759,7 +7693,7 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>report retrieval</t>
+          <t>report kpi</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
@@ -7782,7 +7716,7 @@
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>report review</t>
+          <t>report retrieval</t>
         </is>
       </c>
       <c r="B50" s="11" t="inlineStr">
@@ -7805,7 +7739,7 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>report versions</t>
+          <t>report review</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
@@ -7828,7 +7762,7 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>report versions</t>
         </is>
       </c>
       <c r="B52" s="11" t="inlineStr">
@@ -7843,7 +7777,7 @@
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E52" s="10" t="inlineStr"/>
@@ -7851,7 +7785,7 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>resolve</t>
+          <t>research</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
@@ -7861,12 +7795,12 @@
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E53" s="10" t="inlineStr"/>
@@ -7874,7 +7808,7 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>safety propose</t>
+          <t>resolve</t>
         </is>
       </c>
       <c r="B54" s="11" t="inlineStr">
@@ -7897,7 +7831,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>safety show</t>
+          <t>safety propose</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
@@ -7907,7 +7841,7 @@
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>có</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
@@ -7920,7 +7854,7 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>scratch</t>
+          <t>safety show</t>
         </is>
       </c>
       <c r="B56" s="11" t="inlineStr">
@@ -7930,12 +7864,12 @@
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E56" s="10" t="inlineStr"/>
@@ -7943,7 +7877,7 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>sim run</t>
+          <t>scratch</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
@@ -7953,12 +7887,12 @@
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>có</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E57" s="10" t="inlineStr"/>
@@ -7966,7 +7900,7 @@
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>skill list</t>
+          <t>sim run</t>
         </is>
       </c>
       <c r="B58" s="11" t="inlineStr">
@@ -7981,7 +7915,7 @@
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E58" s="10" t="inlineStr"/>
@@ -7989,7 +7923,7 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>skill mine</t>
+          <t>skill list</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
@@ -8012,7 +7946,7 @@
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>skill run</t>
+          <t>skill mine</t>
         </is>
       </c>
       <c r="B60" s="11" t="inlineStr">
@@ -8022,7 +7956,7 @@
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D60" s="12" t="inlineStr">
@@ -8035,7 +7969,7 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>skill verify</t>
+          <t>skill run</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
@@ -8058,7 +7992,7 @@
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>sources need</t>
+          <t>skill verify</t>
         </is>
       </c>
       <c r="B62" s="11" t="inlineStr">
@@ -8068,12 +8002,12 @@
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>có</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E62" s="10" t="inlineStr"/>
@@ -8081,7 +8015,7 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>sources pages</t>
+          <t>sources need</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
@@ -8104,7 +8038,7 @@
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>sources pages</t>
         </is>
       </c>
       <c r="B64" s="11" t="inlineStr">
@@ -8119,7 +8053,7 @@
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E64" s="10" t="inlineStr"/>
@@ -8127,7 +8061,7 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>suggest</t>
+          <t>status</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
@@ -8142,7 +8076,7 @@
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E65" s="10" t="inlineStr"/>
@@ -8150,7 +8084,7 @@
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>survey</t>
+          <t>suggest</t>
         </is>
       </c>
       <c r="B66" s="11" t="inlineStr">
@@ -8173,7 +8107,7 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>tool doc</t>
+          <t>survey</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
@@ -8188,7 +8122,7 @@
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E67" s="10" t="inlineStr"/>
@@ -8196,7 +8130,7 @@
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>tool list</t>
+          <t>tool doc</t>
         </is>
       </c>
       <c r="B68" s="11" t="inlineStr">
@@ -8219,7 +8153,7 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>tool propose</t>
+          <t>tool list</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
@@ -8229,7 +8163,7 @@
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
@@ -8242,7 +8176,7 @@
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>tool rollback</t>
+          <t>tool propose</t>
         </is>
       </c>
       <c r="B70" s="11" t="inlineStr">
@@ -8265,7 +8199,7 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>tool run</t>
+          <t>tool rollback</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
@@ -8288,7 +8222,7 @@
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>tool verify</t>
+          <t>tool run</t>
         </is>
       </c>
       <c r="B72" s="11" t="inlineStr">
@@ -8311,30 +8245,30 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>brief</t>
-        </is>
-      </c>
-      <c r="B73" s="14" t="inlineStr">
-        <is>
-          <t>KHÔNG</t>
-        </is>
-      </c>
-      <c r="C73" s="12" t="inlineStr"/>
+          <t>tool verify</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C73" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E73" s="10" t="inlineStr">
-        <is>
-          <t>Lệnh này hỏi bạn trực tiếp — tôi gọi hộ thì mất đúng phần hỏi.</t>
-        </is>
-      </c>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E73" s="10" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>build</t>
+          <t>brief</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
@@ -8350,14 +8284,14 @@
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>Ráp firmware là bước trước khi nạp; bạn chạy để còn kiểm ảnh sinh ra.</t>
+          <t>Lệnh này hỏi bạn trực tiếp — tôi gọi hộ thì mất đúng phần hỏi.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>chat</t>
+          <t>build</t>
         </is>
       </c>
       <c r="B75" s="14" t="inlineStr">
@@ -8371,12 +8305,16 @@
           <t>có</t>
         </is>
       </c>
-      <c r="E75" s="10" t="inlineStr"/>
+      <c r="E75" s="10" t="inlineStr">
+        <is>
+          <t>Ráp firmware là bước trước khi nạp; bạn chạy để còn kiểm ảnh sinh ra.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>decide</t>
+          <t>chat</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
@@ -8390,16 +8328,12 @@
           <t>có</t>
         </is>
       </c>
-      <c r="E76" s="10" t="inlineStr">
-        <is>
-          <t>Trình phương án để BẠN chọn; tôi gọi hộ thì mất đúng chỗ bạn chọn.</t>
-        </is>
-      </c>
+      <c r="E76" s="10" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>endurance</t>
+          <t>decide</t>
         </is>
       </c>
       <c r="B77" s="14" t="inlineStr">
@@ -8415,14 +8349,14 @@
       </c>
       <c r="E77" s="10" t="inlineStr">
         <is>
-          <t>Lệnh này chiếm cổng nối tiếp và chạy hàng giờ; bạn nên tự bố trí.</t>
+          <t>Trình phương án để BẠN chọn; tôi gọi hộ thì mất đúng chỗ bạn chọn.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>gen</t>
+          <t>endurance</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
@@ -8438,14 +8372,14 @@
       </c>
       <c r="E78" s="10" t="inlineStr">
         <is>
-          <t>Vòng sinh mã ghi số liệu vào kpi_log.csv, và những dòng ấy là DỮ LIỆU THÍ NGHIỆM của Chương 3. Tôi tự khởi động nó sẽ chèn vào bảng số liệu những lượt chạy mà người làm thí nghiệm không định chạy — nên bạn là người bấm nút.</t>
+          <t>Lệnh này chiếm cổng nối tiếp và chạy hàng giờ; bạn nên tự bố trí.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>init</t>
+          <t>gen</t>
         </is>
       </c>
       <c r="B79" s="14" t="inlineStr">
@@ -8461,14 +8395,14 @@
       </c>
       <c r="E79" s="10" t="inlineStr">
         <is>
-          <t>Khởi tạo dự án là quyết định mở đầu, không nên nằm giữa một câu hỏi.</t>
+          <t>Vòng sinh mã ghi số liệu vào kpi_log.csv, và những dòng ấy là DỮ LIỆU THÍ NGHIỆM của Chương 3. Tôi tự khởi động nó sẽ chèn vào bảng số liệu những lượt chạy mà người làm thí nghiệm không định chạy — nên bạn là người bấm nút.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>ports</t>
+          <t>init</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
@@ -8484,14 +8418,14 @@
       </c>
       <c r="E80" s="10" t="inlineStr">
         <is>
-          <t>Đọc cổng nối tiếp là việc chạm tới máy của bạn.</t>
+          <t>Khởi tạo dự án là quyết định mở đầu, không nên nằm giữa một câu hỏi.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>resume</t>
+          <t>ports</t>
         </is>
       </c>
       <c r="B81" s="14" t="inlineStr">
@@ -8505,12 +8439,16 @@
           <t>có</t>
         </is>
       </c>
-      <c r="E81" s="10" t="inlineStr"/>
+      <c r="E81" s="10" t="inlineStr">
+        <is>
+          <t>Đọc cổng nối tiếp là việc chạm tới máy của bạn.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>rollback</t>
+          <t>resume</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
@@ -8524,16 +8462,12 @@
           <t>có</t>
         </is>
       </c>
-      <c r="E82" s="10" t="inlineStr">
-        <is>
-          <t>Quay lui đổi mã đang chạy trên thiết bị — quyết định của bạn.</t>
-        </is>
-      </c>
+      <c r="E82" s="10" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>scope-image</t>
+          <t>rollback</t>
         </is>
       </c>
       <c r="B83" s="14" t="inlineStr">
@@ -8549,14 +8483,14 @@
       </c>
       <c r="E83" s="10" t="inlineStr">
         <is>
-          <t>Cần bạn đối chiếu ảnh gốc rồi chốt số đo.</t>
+          <t>Quay lui đổi mã đang chạy trên thiết bị — quyết định của bạn.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>telemetry</t>
+          <t>scope-image</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
@@ -8572,14 +8506,14 @@
       </c>
       <c r="E84" s="10" t="inlineStr">
         <is>
-          <t>Lệnh này chiếm cổng nối tiếp của thiết bị; bạn nên tự cắm và chạy.</t>
+          <t>Cần bạn đối chiếu ảnh gốc rồi chốt số đo.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>tune</t>
+          <t>telemetry</t>
         </is>
       </c>
       <c r="B85" s="14" t="inlineStr">
@@ -8595,12 +8529,35 @@
       </c>
       <c r="E85" s="10" t="inlineStr">
         <is>
+          <t>Lệnh này chiếm cổng nối tiếp của thiết bị; bạn nên tự cắm và chạy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="10" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="B86" s="14" t="inlineStr">
+        <is>
+          <t>KHÔNG</t>
+        </is>
+      </c>
+      <c r="C86" s="12" t="inlineStr"/>
+      <c r="D86" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E86" s="10" t="inlineStr">
+        <is>
           <t>Phong hạng hw-verified là một khẳng định về phần cứng. Nó chỉ được đặt bởi người vừa cầm thiết bị và đọc số đo.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E85"/>
+  <autoFilter ref="A1:E86"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/EAA_Bang_nang_luc.xlsx
+++ b/docs/EAA_Bang_nang_luc.xlsx
@@ -16,8 +16,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Năng lực nền'!$A$1:$G$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Năng lực nhúng'!$A$1:$G$97</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Khoảng trống'!$A$1:$F$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Bản đồ lệnh'!$A$1:$E$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Khoảng trống'!$A$1:$F$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Bản đồ lệnh'!$A$1:$E$88</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -827,7 +827,7 @@
       <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Nó không chạy thử năng lực nào — nó đối chiếu khung với mã. Câu 'nó chạy đúng không' thuộc về bộ test (2286 hàm test trong 122 tệp) và scripts/kiem_on_dinh.py.</t>
+          <t>Nó không chạy thử năng lực nào — nó đối chiếu khung với mã. Câu 'nó chạy đúng không' thuộc về bộ test (2307 hàm test trong 123 tệp) và scripts/kiem_on_dinh.py.</t>
         </is>
       </c>
     </row>
@@ -6310,9 +6310,9 @@
           <t>Đưa số đo từ phần cứng ngược vào prompt</t>
         </is>
       </c>
-      <c r="D97" s="16" t="inlineStr">
-        <is>
-          <t>CHƯA</t>
+      <c r="D97" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
         </is>
       </c>
       <c r="E97" s="12" t="inlineStr">
@@ -6322,7 +6322,7 @@
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t>Chưa có gì. measurements.jsonl và kết quả DS-xx nằm NGOÀI eaa/composer.py. Đây là mục đắt nhất trong sáu mục, vì nó đụng vào bộ ghép prompt và vào gate tri thức · §3.7</t>
+          <t>eaa/measured.py — sổ nối tiếp board_facts.jsonl + lớp ngữ cảnh K8 board_facts trong eaa/composer.py (đứng TRƯỚC lớp trích đoạn tài liệu) + lệnh eaa measured list/add/approve. Agent đề xuất, người chốt; chỉ số ĐÃ DUYỆT mới vào prompt · SL-173, TC-133, 21 bài</t>
         </is>
       </c>
       <c r="G97" s="10" t="inlineStr">
@@ -6357,7 +6357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -6528,40 +6528,8 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>Vừa</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>N-913</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>nhúng</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>Đưa số đo từ phần cứng ngược vào prompt</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>CHƯA</t>
-        </is>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>Chưa có gì. measurements.jsonl và kết quả DS-xx nằm NGOÀI eaa/composer.py. Đây là mục đắt nhất trong sáu mục, vì nó đụng vào bộ ghép prompt và vào gate tri thức · §3.7</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F6"/>
+  <autoFilter ref="A1:F5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6572,7 +6540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E86"/>
+  <dimension ref="A1:E88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7302,7 +7270,7 @@
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>memory add</t>
+          <t>measured add</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
@@ -7317,7 +7285,7 @@
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr"/>
@@ -7325,7 +7293,7 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>memory list</t>
+          <t>measured list</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
@@ -7340,7 +7308,7 @@
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr"/>
@@ -7348,7 +7316,7 @@
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>models</t>
+          <t>memory add</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
@@ -7358,12 +7326,12 @@
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>có</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr"/>
@@ -7371,7 +7339,7 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>memory list</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
@@ -7394,7 +7362,7 @@
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>plan add</t>
+          <t>models</t>
         </is>
       </c>
       <c r="B36" s="11" t="inlineStr">
@@ -7404,7 +7372,7 @@
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
@@ -7417,7 +7385,7 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>plan list</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
@@ -7432,7 +7400,7 @@
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E37" s="10" t="inlineStr"/>
@@ -7440,7 +7408,7 @@
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>playbook list</t>
+          <t>plan add</t>
         </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
@@ -7450,12 +7418,12 @@
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>có</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E38" s="10" t="inlineStr"/>
@@ -7463,7 +7431,7 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>playbook lookup</t>
+          <t>plan list</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
@@ -7478,7 +7446,7 @@
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E39" s="10" t="inlineStr"/>
@@ -7486,7 +7454,7 @@
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>playbook record</t>
+          <t>playbook list</t>
         </is>
       </c>
       <c r="B40" s="11" t="inlineStr">
@@ -7496,7 +7464,7 @@
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
@@ -7509,7 +7477,7 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>policy</t>
+          <t>playbook lookup</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
@@ -7532,7 +7500,7 @@
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>propose acceptance</t>
+          <t>playbook record</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
@@ -7542,12 +7510,12 @@
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>có</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E42" s="10" t="inlineStr"/>
@@ -7555,7 +7523,7 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>propose constraints</t>
+          <t>policy</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
@@ -7570,7 +7538,7 @@
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E43" s="10" t="inlineStr"/>
@@ -7578,7 +7546,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>propose pinmap</t>
+          <t>propose acceptance</t>
         </is>
       </c>
       <c r="B44" s="11" t="inlineStr">
@@ -7601,7 +7569,7 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>propose plant</t>
+          <t>propose constraints</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
@@ -7624,7 +7592,7 @@
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>propose scope</t>
+          <t>propose pinmap</t>
         </is>
       </c>
       <c r="B46" s="11" t="inlineStr">
@@ -7634,7 +7602,7 @@
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
@@ -7647,7 +7615,7 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>propose plant</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
@@ -7662,7 +7630,7 @@
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E47" s="10" t="inlineStr"/>
@@ -7670,7 +7638,7 @@
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>propose scope</t>
         </is>
       </c>
       <c r="B48" s="11" t="inlineStr">
@@ -7680,7 +7648,7 @@
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>có</t>
         </is>
       </c>
       <c r="D48" s="12" t="inlineStr">
@@ -7693,7 +7661,7 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>report kpi</t>
+          <t>read</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
@@ -7708,7 +7676,7 @@
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E49" s="10" t="inlineStr"/>
@@ -7716,7 +7684,7 @@
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>report retrieval</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="B50" s="11" t="inlineStr">
@@ -7739,7 +7707,7 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>report review</t>
+          <t>report kpi</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
@@ -7762,7 +7730,7 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>report versions</t>
+          <t>report retrieval</t>
         </is>
       </c>
       <c r="B52" s="11" t="inlineStr">
@@ -7785,7 +7753,7 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>report review</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
@@ -7800,7 +7768,7 @@
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E53" s="10" t="inlineStr"/>
@@ -7808,7 +7776,7 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>resolve</t>
+          <t>report versions</t>
         </is>
       </c>
       <c r="B54" s="11" t="inlineStr">
@@ -7818,7 +7786,7 @@
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
@@ -7831,7 +7799,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>safety propose</t>
+          <t>research</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
@@ -7841,12 +7809,12 @@
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E55" s="10" t="inlineStr"/>
@@ -7854,7 +7822,7 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>safety show</t>
+          <t>resolve</t>
         </is>
       </c>
       <c r="B56" s="11" t="inlineStr">
@@ -7864,7 +7832,7 @@
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>có</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
@@ -7877,7 +7845,7 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>scratch</t>
+          <t>safety propose</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
@@ -7892,7 +7860,7 @@
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E57" s="10" t="inlineStr"/>
@@ -7900,7 +7868,7 @@
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>sim run</t>
+          <t>safety show</t>
         </is>
       </c>
       <c r="B58" s="11" t="inlineStr">
@@ -7923,7 +7891,7 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>skill list</t>
+          <t>scratch</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
@@ -7933,7 +7901,7 @@
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>có</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
@@ -7946,7 +7914,7 @@
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>skill mine</t>
+          <t>sim run</t>
         </is>
       </c>
       <c r="B60" s="11" t="inlineStr">
@@ -7961,7 +7929,7 @@
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E60" s="10" t="inlineStr"/>
@@ -7969,7 +7937,7 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>skill run</t>
+          <t>skill list</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
@@ -7979,7 +7947,7 @@
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
@@ -7992,7 +7960,7 @@
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>skill verify</t>
+          <t>skill mine</t>
         </is>
       </c>
       <c r="B62" s="11" t="inlineStr">
@@ -8002,7 +7970,7 @@
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
@@ -8015,7 +7983,7 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>sources need</t>
+          <t>skill run</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
@@ -8025,12 +7993,12 @@
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>có</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E63" s="10" t="inlineStr"/>
@@ -8038,7 +8006,7 @@
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>sources pages</t>
+          <t>skill verify</t>
         </is>
       </c>
       <c r="B64" s="11" t="inlineStr">
@@ -8048,12 +8016,12 @@
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>có</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E64" s="10" t="inlineStr"/>
@@ -8061,7 +8029,7 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>sources need</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
@@ -8076,7 +8044,7 @@
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E65" s="10" t="inlineStr"/>
@@ -8084,7 +8052,7 @@
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>suggest</t>
+          <t>sources pages</t>
         </is>
       </c>
       <c r="B66" s="11" t="inlineStr">
@@ -8107,7 +8075,7 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>survey</t>
+          <t>status</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
@@ -8122,7 +8090,7 @@
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E67" s="10" t="inlineStr"/>
@@ -8130,7 +8098,7 @@
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>tool doc</t>
+          <t>suggest</t>
         </is>
       </c>
       <c r="B68" s="11" t="inlineStr">
@@ -8145,7 +8113,7 @@
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E68" s="10" t="inlineStr"/>
@@ -8153,7 +8121,7 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>tool list</t>
+          <t>survey</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
@@ -8168,7 +8136,7 @@
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E69" s="10" t="inlineStr"/>
@@ -8176,7 +8144,7 @@
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>tool propose</t>
+          <t>tool doc</t>
         </is>
       </c>
       <c r="B70" s="11" t="inlineStr">
@@ -8186,7 +8154,7 @@
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D70" s="12" t="inlineStr">
@@ -8199,7 +8167,7 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>tool rollback</t>
+          <t>tool list</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
@@ -8209,7 +8177,7 @@
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
@@ -8222,7 +8190,7 @@
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>tool run</t>
+          <t>tool propose</t>
         </is>
       </c>
       <c r="B72" s="11" t="inlineStr">
@@ -8245,7 +8213,7 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>tool verify</t>
+          <t>tool rollback</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
@@ -8268,53 +8236,53 @@
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>brief</t>
-        </is>
-      </c>
-      <c r="B74" s="14" t="inlineStr">
-        <is>
-          <t>KHÔNG</t>
-        </is>
-      </c>
-      <c r="C74" s="12" t="inlineStr"/>
+          <t>tool run</t>
+        </is>
+      </c>
+      <c r="B74" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C74" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E74" s="10" t="inlineStr">
-        <is>
-          <t>Lệnh này hỏi bạn trực tiếp — tôi gọi hộ thì mất đúng phần hỏi.</t>
-        </is>
-      </c>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E74" s="10" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>build</t>
-        </is>
-      </c>
-      <c r="B75" s="14" t="inlineStr">
-        <is>
-          <t>KHÔNG</t>
-        </is>
-      </c>
-      <c r="C75" s="12" t="inlineStr"/>
+          <t>tool verify</t>
+        </is>
+      </c>
+      <c r="B75" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C75" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E75" s="10" t="inlineStr">
-        <is>
-          <t>Ráp firmware là bước trước khi nạp; bạn chạy để còn kiểm ảnh sinh ra.</t>
-        </is>
-      </c>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E75" s="10" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>chat</t>
+          <t>brief</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
@@ -8328,12 +8296,16 @@
           <t>có</t>
         </is>
       </c>
-      <c r="E76" s="10" t="inlineStr"/>
+      <c r="E76" s="10" t="inlineStr">
+        <is>
+          <t>Lệnh này hỏi bạn trực tiếp — tôi gọi hộ thì mất đúng phần hỏi.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>decide</t>
+          <t>build</t>
         </is>
       </c>
       <c r="B77" s="14" t="inlineStr">
@@ -8349,14 +8321,14 @@
       </c>
       <c r="E77" s="10" t="inlineStr">
         <is>
-          <t>Trình phương án để BẠN chọn; tôi gọi hộ thì mất đúng chỗ bạn chọn.</t>
+          <t>Ráp firmware là bước trước khi nạp; bạn chạy để còn kiểm ảnh sinh ra.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>endurance</t>
+          <t>chat</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
@@ -8370,16 +8342,12 @@
           <t>có</t>
         </is>
       </c>
-      <c r="E78" s="10" t="inlineStr">
-        <is>
-          <t>Lệnh này chiếm cổng nối tiếp và chạy hàng giờ; bạn nên tự bố trí.</t>
-        </is>
-      </c>
+      <c r="E78" s="10" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>gen</t>
+          <t>decide</t>
         </is>
       </c>
       <c r="B79" s="14" t="inlineStr">
@@ -8395,14 +8363,14 @@
       </c>
       <c r="E79" s="10" t="inlineStr">
         <is>
-          <t>Vòng sinh mã ghi số liệu vào kpi_log.csv, và những dòng ấy là DỮ LIỆU THÍ NGHIỆM của Chương 3. Tôi tự khởi động nó sẽ chèn vào bảng số liệu những lượt chạy mà người làm thí nghiệm không định chạy — nên bạn là người bấm nút.</t>
+          <t>Trình phương án để BẠN chọn; tôi gọi hộ thì mất đúng chỗ bạn chọn.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>init</t>
+          <t>endurance</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
@@ -8418,14 +8386,14 @@
       </c>
       <c r="E80" s="10" t="inlineStr">
         <is>
-          <t>Khởi tạo dự án là quyết định mở đầu, không nên nằm giữa một câu hỏi.</t>
+          <t>Lệnh này chiếm cổng nối tiếp và chạy hàng giờ; bạn nên tự bố trí.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>ports</t>
+          <t>gen</t>
         </is>
       </c>
       <c r="B81" s="14" t="inlineStr">
@@ -8441,14 +8409,14 @@
       </c>
       <c r="E81" s="10" t="inlineStr">
         <is>
-          <t>Đọc cổng nối tiếp là việc chạm tới máy của bạn.</t>
+          <t>Vòng sinh mã ghi số liệu vào kpi_log.csv, và những dòng ấy là DỮ LIỆU THÍ NGHIỆM của Chương 3. Tôi tự khởi động nó sẽ chèn vào bảng số liệu những lượt chạy mà người làm thí nghiệm không định chạy — nên bạn là người bấm nút.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>resume</t>
+          <t>init</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
@@ -8462,12 +8430,16 @@
           <t>có</t>
         </is>
       </c>
-      <c r="E82" s="10" t="inlineStr"/>
+      <c r="E82" s="10" t="inlineStr">
+        <is>
+          <t>Khởi tạo dự án là quyết định mở đầu, không nên nằm giữa một câu hỏi.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>rollback</t>
+          <t>ports</t>
         </is>
       </c>
       <c r="B83" s="14" t="inlineStr">
@@ -8483,14 +8455,14 @@
       </c>
       <c r="E83" s="10" t="inlineStr">
         <is>
-          <t>Quay lui đổi mã đang chạy trên thiết bị — quyết định của bạn.</t>
+          <t>Đọc cổng nối tiếp là việc chạm tới máy của bạn.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>scope-image</t>
+          <t>resume</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
@@ -8504,16 +8476,12 @@
           <t>có</t>
         </is>
       </c>
-      <c r="E84" s="10" t="inlineStr">
-        <is>
-          <t>Cần bạn đối chiếu ảnh gốc rồi chốt số đo.</t>
-        </is>
-      </c>
+      <c r="E84" s="10" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>telemetry</t>
+          <t>rollback</t>
         </is>
       </c>
       <c r="B85" s="14" t="inlineStr">
@@ -8529,14 +8497,14 @@
       </c>
       <c r="E85" s="10" t="inlineStr">
         <is>
-          <t>Lệnh này chiếm cổng nối tiếp của thiết bị; bạn nên tự cắm và chạy.</t>
+          <t>Quay lui đổi mã đang chạy trên thiết bị — quyết định của bạn.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>tune</t>
+          <t>scope-image</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
@@ -8552,12 +8520,58 @@
       </c>
       <c r="E86" s="10" t="inlineStr">
         <is>
+          <t>Cần bạn đối chiếu ảnh gốc rồi chốt số đo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="10" t="inlineStr">
+        <is>
+          <t>telemetry</t>
+        </is>
+      </c>
+      <c r="B87" s="14" t="inlineStr">
+        <is>
+          <t>KHÔNG</t>
+        </is>
+      </c>
+      <c r="C87" s="12" t="inlineStr"/>
+      <c r="D87" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E87" s="10" t="inlineStr">
+        <is>
+          <t>Lệnh này chiếm cổng nối tiếp của thiết bị; bạn nên tự cắm và chạy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="B88" s="14" t="inlineStr">
+        <is>
+          <t>KHÔNG</t>
+        </is>
+      </c>
+      <c r="C88" s="12" t="inlineStr"/>
+      <c r="D88" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E88" s="10" t="inlineStr">
+        <is>
           <t>Phong hạng hw-verified là một khẳng định về phần cứng. Nó chỉ được đặt bởi người vừa cầm thiết bị và đọc số đo.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E86"/>
+  <autoFilter ref="A1:E88"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/EAA_Bang_nang_luc.xlsx
+++ b/docs/EAA_Bang_nang_luc.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Năng lực nền'!$A$1:$G$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Năng lực nhúng'!$A$1:$G$97</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Khoảng trống'!$A$1:$F$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Khoảng trống'!$A$1:$F$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Bản đồ lệnh'!$A$1:$E$88</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -827,7 +827,7 @@
       <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Nó không chạy thử năng lực nào — nó đối chiếu khung với mã. Câu 'nó chạy đúng không' thuộc về bộ test (2307 hàm test trong 123 tệp) và scripts/kiem_on_dinh.py.</t>
+          <t>Nó không chạy thử năng lực nào — nó đối chiếu khung với mã. Câu 'nó chạy đúng không' thuộc về bộ test (2327 hàm test trong 124 tệp) và scripts/kiem_on_dinh.py.</t>
         </is>
       </c>
     </row>
@@ -6236,9 +6236,9 @@
           <t>Kiểm chú thích số học có đúng thứ nguyên không</t>
         </is>
       </c>
-      <c r="D95" s="16" t="inlineStr">
-        <is>
-          <t>CHƯA</t>
+      <c r="D95" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
         </is>
       </c>
       <c r="E95" s="12" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
-          <t>Chưa có gì. Hồ sơ phần cứng đã khai đơn vị của từng đại lượng, nên dữ liệu để làm thì có sẵn. Bằng chứng: chú thích '4ms / 0.000031s = 129' · §3.4</t>
+          <t>eaa/dimension.py, nối vào StaticGate ở mức CẢNH BÁO. Hai phép soi: đơn vị khai trong chú thích chọi với đơn vị trong sổ số đo (cần N-913), và phép tính không ra kết quả nó khai (tự chứa, có quy đổi tiền tố) · SL-174, TC-134, 20 bài</t>
         </is>
       </c>
       <c r="G95" s="10" t="inlineStr">
@@ -6357,7 +6357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>N-911</t>
+          <t>N-912</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>Kiểm chú thích số học có đúng thứ nguyên không</t>
+          <t>Thiết kế khả quan sát — làm cho lỗi kêu lên được</t>
         </is>
       </c>
       <c r="E4" s="16" t="inlineStr">
@@ -6492,44 +6492,12 @@
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
-          <t>Chưa có gì. Hồ sơ phần cứng đã khai đơn vị của từng đại lượng, nên dữ liệu để làm thì có sẵn. Bằng chứng: chú thích '4ms / 0.000031s = 129' · §3.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>Vừa</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>N-912</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>nhúng</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="inlineStr">
-        <is>
-          <t>Thiết kế khả quan sát — làm cho lỗi kêu lên được</t>
-        </is>
-      </c>
-      <c r="E5" s="16" t="inlineStr">
-        <is>
-          <t>CHƯA</t>
-        </is>
-      </c>
-      <c r="F5" s="10" t="inlineStr">
-        <is>
           <t>Chưa có gì. eaa/decompose.py chưa đòi module khai dấu hiệu sống/hỏng; eaa/propose.py AcceptanceProposal chưa sinh tiêu chí quan sát được bằng mắt/tai · §3.6</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F5"/>
+  <autoFilter ref="A1:F4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/EAA_Bang_nang_luc.xlsx
+++ b/docs/EAA_Bang_nang_luc.xlsx
@@ -16,8 +16,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Năng lực nền'!$A$1:$G$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Năng lực nhúng'!$A$1:$G$97</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Khoảng trống'!$A$1:$F$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Bản đồ lệnh'!$A$1:$E$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Khoảng trống'!$A$1:$F$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Bản đồ lệnh'!$A$1:$E$89</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -124,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -167,9 +167,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -827,7 +824,7 @@
       <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Nó không chạy thử năng lực nào — nó đối chiếu khung với mã. Câu 'nó chạy đúng không' thuộc về bộ test (2327 hàm test trong 124 tệp) và scripts/kiem_on_dinh.py.</t>
+          <t>Nó không chạy thử năng lực nào — nó đối chiếu khung với mã. Câu 'nó chạy đúng không' thuộc về bộ test (2350 hàm test trong 125 tệp) và scripts/kiem_on_dinh.py.</t>
         </is>
       </c>
     </row>
@@ -6273,9 +6270,9 @@
           <t>Thiết kế khả quan sát — làm cho lỗi kêu lên được</t>
         </is>
       </c>
-      <c r="D96" s="16" t="inlineStr">
-        <is>
-          <t>CHƯA</t>
+      <c r="D96" s="11" t="inlineStr">
+        <is>
+          <t>ĐỦ</t>
         </is>
       </c>
       <c r="E96" s="12" t="inlineStr">
@@ -6285,7 +6282,7 @@
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t>Chưa có gì. eaa/decompose.py chưa đòi module khai dấu hiệu sống/hỏng; eaa/propose.py AcceptanceProposal chưa sinh tiêu chí quan sát được bằng mắt/tai · §3.6</t>
+          <t>eaa/observability.py + hai trường dau_hieu_song/dau_hieu_hong trong mục backlog + lệnh eaa observe (báo cáo) và observe set (khai) + một dòng checklist ở hồ sơ G3. Kênh quan sát đọc từ cờ observable của hồ sơ dự án — engine coi là chuỗi mờ · SL-175, TC-135, 23 bài</t>
         </is>
       </c>
       <c r="G96" s="10" t="inlineStr">
@@ -6357,7 +6354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -6401,7 +6398,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Cao</t>
         </is>
@@ -6433,7 +6430,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Cao</t>
         </is>
@@ -6464,40 +6461,8 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>Vừa</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>N-912</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>nhúng</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>Thiết kế khả quan sát — làm cho lỗi kêu lên được</t>
-        </is>
-      </c>
-      <c r="E4" s="16" t="inlineStr">
-        <is>
-          <t>CHƯA</t>
-        </is>
-      </c>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t>Chưa có gì. eaa/decompose.py chưa đòi module khai dấu hiệu sống/hỏng; eaa/propose.py AcceptanceProposal chưa sinh tiêu chí quan sát được bằng mắt/tai · §3.6</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F4"/>
+  <autoFilter ref="A1:F3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6508,7 +6473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E88"/>
+  <dimension ref="A1:E89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7353,7 +7318,7 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>packs</t>
+          <t>observe</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
@@ -7368,7 +7333,7 @@
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E37" s="10" t="inlineStr"/>
@@ -7376,7 +7341,7 @@
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>plan add</t>
+          <t>packs</t>
         </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
@@ -7386,12 +7351,12 @@
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E38" s="10" t="inlineStr"/>
@@ -7399,7 +7364,7 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>plan list</t>
+          <t>plan add</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
@@ -7409,7 +7374,7 @@
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>có</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
@@ -7422,7 +7387,7 @@
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>playbook list</t>
+          <t>plan list</t>
         </is>
       </c>
       <c r="B40" s="11" t="inlineStr">
@@ -7437,7 +7402,7 @@
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr"/>
@@ -7445,7 +7410,7 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>playbook lookup</t>
+          <t>playbook list</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
@@ -7468,7 +7433,7 @@
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>playbook record</t>
+          <t>playbook lookup</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
@@ -7478,7 +7443,7 @@
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
@@ -7491,7 +7456,7 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>policy</t>
+          <t>playbook record</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
@@ -7501,7 +7466,7 @@
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>có</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
@@ -7514,7 +7479,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>propose acceptance</t>
+          <t>policy</t>
         </is>
       </c>
       <c r="B44" s="11" t="inlineStr">
@@ -7529,7 +7494,7 @@
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E44" s="10" t="inlineStr"/>
@@ -7537,7 +7502,7 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>propose constraints</t>
+          <t>propose acceptance</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
@@ -7560,7 +7525,7 @@
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>propose pinmap</t>
+          <t>propose constraints</t>
         </is>
       </c>
       <c r="B46" s="11" t="inlineStr">
@@ -7583,7 +7548,7 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>propose plant</t>
+          <t>propose pinmap</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
@@ -7606,7 +7571,7 @@
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>propose scope</t>
+          <t>propose plant</t>
         </is>
       </c>
       <c r="B48" s="11" t="inlineStr">
@@ -7616,7 +7581,7 @@
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D48" s="12" t="inlineStr">
@@ -7629,7 +7594,7 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>propose scope</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
@@ -7639,12 +7604,12 @@
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>có</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E49" s="10" t="inlineStr"/>
@@ -7652,7 +7617,7 @@
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>read</t>
         </is>
       </c>
       <c r="B50" s="11" t="inlineStr">
@@ -7667,7 +7632,7 @@
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E50" s="10" t="inlineStr"/>
@@ -7675,7 +7640,7 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>report kpi</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
@@ -7698,7 +7663,7 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>report retrieval</t>
+          <t>report kpi</t>
         </is>
       </c>
       <c r="B52" s="11" t="inlineStr">
@@ -7721,7 +7686,7 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>report review</t>
+          <t>report retrieval</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
@@ -7744,7 +7709,7 @@
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>report versions</t>
+          <t>report review</t>
         </is>
       </c>
       <c r="B54" s="11" t="inlineStr">
@@ -7767,7 +7732,7 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>report versions</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
@@ -7782,7 +7747,7 @@
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E55" s="10" t="inlineStr"/>
@@ -7790,7 +7755,7 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>resolve</t>
+          <t>research</t>
         </is>
       </c>
       <c r="B56" s="11" t="inlineStr">
@@ -7800,12 +7765,12 @@
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E56" s="10" t="inlineStr"/>
@@ -7813,7 +7778,7 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>safety propose</t>
+          <t>resolve</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
@@ -7836,7 +7801,7 @@
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>safety show</t>
+          <t>safety propose</t>
         </is>
       </c>
       <c r="B58" s="11" t="inlineStr">
@@ -7846,7 +7811,7 @@
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>có</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
@@ -7859,7 +7824,7 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>scratch</t>
+          <t>safety show</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
@@ -7869,12 +7834,12 @@
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E59" s="10" t="inlineStr"/>
@@ -7882,7 +7847,7 @@
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>sim run</t>
+          <t>scratch</t>
         </is>
       </c>
       <c r="B60" s="11" t="inlineStr">
@@ -7892,12 +7857,12 @@
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>có</t>
         </is>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E60" s="10" t="inlineStr"/>
@@ -7905,7 +7870,7 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>skill list</t>
+          <t>sim run</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
@@ -7920,7 +7885,7 @@
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E61" s="10" t="inlineStr"/>
@@ -7928,7 +7893,7 @@
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>skill mine</t>
+          <t>skill list</t>
         </is>
       </c>
       <c r="B62" s="11" t="inlineStr">
@@ -7951,7 +7916,7 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>skill run</t>
+          <t>skill mine</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
@@ -7961,7 +7926,7 @@
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
@@ -7974,7 +7939,7 @@
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>skill verify</t>
+          <t>skill run</t>
         </is>
       </c>
       <c r="B64" s="11" t="inlineStr">
@@ -7997,7 +7962,7 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>sources need</t>
+          <t>skill verify</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
@@ -8007,12 +7972,12 @@
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>có</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E65" s="10" t="inlineStr"/>
@@ -8020,7 +7985,7 @@
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>sources pages</t>
+          <t>sources need</t>
         </is>
       </c>
       <c r="B66" s="11" t="inlineStr">
@@ -8043,7 +8008,7 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>sources pages</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
@@ -8058,7 +8023,7 @@
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E67" s="10" t="inlineStr"/>
@@ -8066,7 +8031,7 @@
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>suggest</t>
+          <t>status</t>
         </is>
       </c>
       <c r="B68" s="11" t="inlineStr">
@@ -8081,7 +8046,7 @@
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>không</t>
         </is>
       </c>
       <c r="E68" s="10" t="inlineStr"/>
@@ -8089,7 +8054,7 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>survey</t>
+          <t>suggest</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
@@ -8112,7 +8077,7 @@
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>tool doc</t>
+          <t>survey</t>
         </is>
       </c>
       <c r="B70" s="11" t="inlineStr">
@@ -8127,7 +8092,7 @@
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>không</t>
+          <t>có</t>
         </is>
       </c>
       <c r="E70" s="10" t="inlineStr"/>
@@ -8135,7 +8100,7 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>tool list</t>
+          <t>tool doc</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
@@ -8158,7 +8123,7 @@
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>tool propose</t>
+          <t>tool list</t>
         </is>
       </c>
       <c r="B72" s="11" t="inlineStr">
@@ -8168,7 +8133,7 @@
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>có</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr">
@@ -8181,7 +8146,7 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>tool rollback</t>
+          <t>tool propose</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
@@ -8204,7 +8169,7 @@
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>tool run</t>
+          <t>tool rollback</t>
         </is>
       </c>
       <c r="B74" s="11" t="inlineStr">
@@ -8227,7 +8192,7 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>tool verify</t>
+          <t>tool run</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
@@ -8250,30 +8215,30 @@
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>brief</t>
-        </is>
-      </c>
-      <c r="B76" s="14" t="inlineStr">
-        <is>
-          <t>KHÔNG</t>
-        </is>
-      </c>
-      <c r="C76" s="12" t="inlineStr"/>
+          <t>tool verify</t>
+        </is>
+      </c>
+      <c r="B76" s="11" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C76" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>có</t>
-        </is>
-      </c>
-      <c r="E76" s="10" t="inlineStr">
-        <is>
-          <t>Lệnh này hỏi bạn trực tiếp — tôi gọi hộ thì mất đúng phần hỏi.</t>
-        </is>
-      </c>
+          <t>không</t>
+        </is>
+      </c>
+      <c r="E76" s="10" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>build</t>
+          <t>brief</t>
         </is>
       </c>
       <c r="B77" s="14" t="inlineStr">
@@ -8289,14 +8254,14 @@
       </c>
       <c r="E77" s="10" t="inlineStr">
         <is>
-          <t>Ráp firmware là bước trước khi nạp; bạn chạy để còn kiểm ảnh sinh ra.</t>
+          <t>Lệnh này hỏi bạn trực tiếp — tôi gọi hộ thì mất đúng phần hỏi.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>chat</t>
+          <t>build</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
@@ -8310,12 +8275,16 @@
           <t>có</t>
         </is>
       </c>
-      <c r="E78" s="10" t="inlineStr"/>
+      <c r="E78" s="10" t="inlineStr">
+        <is>
+          <t>Ráp firmware là bước trước khi nạp; bạn chạy để còn kiểm ảnh sinh ra.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>decide</t>
+          <t>chat</t>
         </is>
       </c>
       <c r="B79" s="14" t="inlineStr">
@@ -8329,16 +8298,12 @@
           <t>có</t>
         </is>
       </c>
-      <c r="E79" s="10" t="inlineStr">
-        <is>
-          <t>Trình phương án để BẠN chọn; tôi gọi hộ thì mất đúng chỗ bạn chọn.</t>
-        </is>
-      </c>
+      <c r="E79" s="10" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>endurance</t>
+          <t>decide</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
@@ -8354,14 +8319,14 @@
       </c>
       <c r="E80" s="10" t="inlineStr">
         <is>
-          <t>Lệnh này chiếm cổng nối tiếp và chạy hàng giờ; bạn nên tự bố trí.</t>
+          <t>Trình phương án để BẠN chọn; tôi gọi hộ thì mất đúng chỗ bạn chọn.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>gen</t>
+          <t>endurance</t>
         </is>
       </c>
       <c r="B81" s="14" t="inlineStr">
@@ -8377,14 +8342,14 @@
       </c>
       <c r="E81" s="10" t="inlineStr">
         <is>
-          <t>Vòng sinh mã ghi số liệu vào kpi_log.csv, và những dòng ấy là DỮ LIỆU THÍ NGHIỆM của Chương 3. Tôi tự khởi động nó sẽ chèn vào bảng số liệu những lượt chạy mà người làm thí nghiệm không định chạy — nên bạn là người bấm nút.</t>
+          <t>Lệnh này chiếm cổng nối tiếp và chạy hàng giờ; bạn nên tự bố trí.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>init</t>
+          <t>gen</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
@@ -8400,14 +8365,14 @@
       </c>
       <c r="E82" s="10" t="inlineStr">
         <is>
-          <t>Khởi tạo dự án là quyết định mở đầu, không nên nằm giữa một câu hỏi.</t>
+          <t>Vòng sinh mã ghi số liệu vào kpi_log.csv, và những dòng ấy là DỮ LIỆU THÍ NGHIỆM của Chương 3. Tôi tự khởi động nó sẽ chèn vào bảng số liệu những lượt chạy mà người làm thí nghiệm không định chạy — nên bạn là người bấm nút.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>ports</t>
+          <t>init</t>
         </is>
       </c>
       <c r="B83" s="14" t="inlineStr">
@@ -8423,14 +8388,14 @@
       </c>
       <c r="E83" s="10" t="inlineStr">
         <is>
-          <t>Đọc cổng nối tiếp là việc chạm tới máy của bạn.</t>
+          <t>Khởi tạo dự án là quyết định mở đầu, không nên nằm giữa một câu hỏi.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>resume</t>
+          <t>ports</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
@@ -8444,12 +8409,16 @@
           <t>có</t>
         </is>
       </c>
-      <c r="E84" s="10" t="inlineStr"/>
+      <c r="E84" s="10" t="inlineStr">
+        <is>
+          <t>Đọc cổng nối tiếp là việc chạm tới máy của bạn.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>rollback</t>
+          <t>resume</t>
         </is>
       </c>
       <c r="B85" s="14" t="inlineStr">
@@ -8463,16 +8432,12 @@
           <t>có</t>
         </is>
       </c>
-      <c r="E85" s="10" t="inlineStr">
-        <is>
-          <t>Quay lui đổi mã đang chạy trên thiết bị — quyết định của bạn.</t>
-        </is>
-      </c>
+      <c r="E85" s="10" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>scope-image</t>
+          <t>rollback</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
@@ -8488,14 +8453,14 @@
       </c>
       <c r="E86" s="10" t="inlineStr">
         <is>
-          <t>Cần bạn đối chiếu ảnh gốc rồi chốt số đo.</t>
+          <t>Quay lui đổi mã đang chạy trên thiết bị — quyết định của bạn.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>telemetry</t>
+          <t>scope-image</t>
         </is>
       </c>
       <c r="B87" s="14" t="inlineStr">
@@ -8511,14 +8476,14 @@
       </c>
       <c r="E87" s="10" t="inlineStr">
         <is>
-          <t>Lệnh này chiếm cổng nối tiếp của thiết bị; bạn nên tự cắm và chạy.</t>
+          <t>Cần bạn đối chiếu ảnh gốc rồi chốt số đo.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
         <is>
-          <t>tune</t>
+          <t>telemetry</t>
         </is>
       </c>
       <c r="B88" s="14" t="inlineStr">
@@ -8534,12 +8499,35 @@
       </c>
       <c r="E88" s="10" t="inlineStr">
         <is>
+          <t>Lệnh này chiếm cổng nối tiếp của thiết bị; bạn nên tự cắm và chạy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="10" t="inlineStr">
+        <is>
+          <t>tune</t>
+        </is>
+      </c>
+      <c r="B89" s="14" t="inlineStr">
+        <is>
+          <t>KHÔNG</t>
+        </is>
+      </c>
+      <c r="C89" s="12" t="inlineStr"/>
+      <c r="D89" s="12" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="E89" s="10" t="inlineStr">
+        <is>
           <t>Phong hạng hw-verified là một khẳng định về phần cứng. Nó chỉ được đặt bởi người vừa cầm thiết bị và đọc số đo.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E88"/>
+  <autoFilter ref="A1:E89"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>